--- a/Documentation/Program_Map.xlsx
+++ b/Documentation/Program_Map.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>303 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
+          <t>301 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>751</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>جدول‌های کالیبراسیون بنچ ChangeOver (LUT جریان، مقسم‌ها، نسبت مقسم و ثابت‌های VDDA). ---------------------------------------------------------------------------- [EN] All bench calibration tables in ONE place (included ONLY by measurement.c; the arrays are static). HOW TO EXTEND (all three tables): 1) append the anchor to BOTH arrays (chain AND battery - equal lengths, host-test enforced); 2) keep each axis strictly increasing (the point count derives itself via sizeof); 3) tables are keyed on MEASURED chain current, never duty. [FA] همهٔ جدول‌های کالیبراسیون بنچ یک‌جا (فقط measurement.c اینکلود می‌کند؛ آرایه‌ها static). راهنمای بزرگ‌کردن (هر سه جدول): 1) لنگر را به «هر دو» آرایه اضافه کن (طول برابر - تست هاست قفل می‌کند)؛ 2) محورها اکیداً صعودی بمانند (تعداد نقاط از sizeof)؛ 3) کلید جدول «جریان زنجیرهٔ اندازه‌گیری‌شده» است، هرگز دیوتی. ============================================================================</t>
+          <t>ثابت‌های کالیبراسیون زمان بیلد ChangeOver (مرجع ADC). ---------------------------------------------------------------------------- [EN] (2026-10-10) The battery CURRENT tables are NO LONGER compiled in. They are made on the panel from the bench data and stored in flash (CalLut). Until the first calibration the board reads through the gain and offset in the BSP, which start at the MAXIMUM gain and zero offset (safe direction: a high reading only slows the charge). [FA] جدول‌های جریان باتری دیگر در کد کامپایل نمی‌شوند. روی پنل از داده‌های بنچ ساخته و در فلش (CalLut) ذخیره می‌شوند. تا اولین کالیبراسیون، برد با گین و آفست BSP کار می‌کند که از بیشترین گین و آفست صفر شروع می‌کنند (جهت امن: خوانش بالا فقط شارژ را کند می‌کند). ============================================================================</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>373</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>618</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>366</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -4430,7 +4430,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_ConvertCurrent</t>
+          <t>func__BspMeasurement_ChainDeltaMa</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4445,19 +4445,19 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>508</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>قالب فرمول مشترک هر دو کانال، یک مرحله برای هر المان شماتیک: شمارش -&gt; mV پایه ADC -&gt; خنثی‌کردن تقسیم ‎R41/R42 -&gt;‎ خنثی‌کردن گین LM358 -&gt; خنثی‌کردن mΩ شانت -&gt; mA، سپس آفست صفر پر-کانال و گین پرمیل بنچ. هر ضرب مرحلهٔ صورت/مخرج خودش را جابه‌جا می‌کند و فقط یک تقسیم در انتها اجرا می‌شود. رژیم فلش: پنج مرحله در یک ضرب+تقسیم 32بیتی با نتیجهٔ بیت‌به‌بیت یکسان جمع شد (اثبات برای هر 4096 شمارش؛ تقسیم 64بیتی ~1KB می‌خواست). اگر مقاومتی عوض شد دوباره اشتقاق بگیر (تست هاست از همین دیفاین‌ها بازمحاسبه می‌کند).</t>
+          <t>round(BSPfull(high) - BSPfull(low)) in mA, one rounding. The difference is taken on the exact numerators, so it is exact. [‎FA] round(BSPfull(high) - BSPfull(low))‎ بر حسب mA با یک رُند. تفاضل روی صورت‌های دقیق گرفته می‌شود، پس دقیق است.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_CountsToMv</t>
+          <t>func__BspMeasurement_ChainNumerator</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4467,24 +4467,24 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>444</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>شمارش استاندارد ADC را به ولتاژ روی پایهٔ ADC تبدیل می‌کند.</t>
+          <t>قالب فرمول مشترک هر دو کانال، یک مرحله برای هر المان شماتیک: شمارش -&gt; mV پایه ADC -&gt; خنثی‌کردن تقسیم ‎R41/R42 -&gt;‎ خنثی‌کردن گین LM358 -&gt; خنثی‌کردن mΩ شانت -&gt; mA، سپس آفست صفر پر-کانال و گین پرمیل بنچ. هر ضرب مرحلهٔ صورت/مخرج خودش را جابه‌جا می‌کند و فقط یک تقسیم در انتها اجرا می‌شود. رژیم فلش: پنج مرحله در یک ضرب+تقسیم 32بیتی با نتیجهٔ بیت‌به‌بیت یکسان جمع شد (اثبات برای هر 4096 شمارش؛ تقسیم 64بیتی ~1KB می‌خواست). اگر مقاومتی عوض شد دوباره اشتقاق بگیر (تست هاست از همین دیفاین‌ها بازمحاسبه می‌کند). رُند: تقسیم جمع‌شده همان قاعدهٔ رُند به نزدیکِ پنل و لنگرهای جدول بنچ را دارد (نصف مقسوم‌علیه پیش از تقسیم)، چون زنجیرهٔ برشی، کم‌خوانی یک‌طرفهٔ جریان اندازه‌گیری‌شده است.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_Current1CountsToMa</t>
+          <t>func__BspMeasurement_ConvertCurrent</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -4494,24 +4494,24 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>529</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>کانال جریان 1 را با کالیبراسیون مستقل به mA تبدیل می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_Current2CountsToMa</t>
+          <t>func__BspMeasurement_CountsToMv</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>کانال جریان 2 را با کالیبراسیون بنچ تأییدشده به mA تبدیل می‌کند.</t>
+          <t>شمارش استاندارد ADC را به ولتاژ روی پایهٔ ADC تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_CurrentCountsToMa</t>
+          <t>func__BspMeasurement_Current1CountsToMa</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>مبدل عمومی قدیمی که دقیقاً همان تابع کانال 2 است، چون از جفت کالیبراسیون کانال 2 استفاده می‌کند. فقط برای این نگه داشته شده که فراخوان‌های قدیمی لینک شوند؛ کد جدید باید تابع پر-کانال را بردارد (دستور کاربر 2026-09-20: شارژر 1 دیگر روی کالیبراسیون شارژر 2 سوار نیست).</t>
+          <t>کانال جریان 1 را با کالیبراسیون مستقل به mA تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_CurrentCountsToShuntUv</t>
+          <t>func__BspMeasurement_Current1DeltaMa</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -4580,19 +4580,19 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>545</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فقط-سخت‌افزاری (مرجع + مقسم ‎R41/R42‎ + گین تقویت‌کننده، بدون آفست و اصلاح) از شمارش خام جریان به ولتاژ شانت بر حسب uV - دیاگ زندهٔ بررسی زنجیرهٔ جریان، دستور کاربر 2026-09-22.</t>
+          <t>تفاضل زنجیرهٔ کانال 1 (برای برون‌یابی بالای آخرین لنگر جدول): ‎round(BSPfull(high) - BSPfull(low))‎ بر حسب mA. /</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_GetCurrentGainPermille</t>
+          <t>func__BspMeasurement_Current2CountsToMa</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -4607,19 +4607,19 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>591</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>ضریب گین بنچ زندهٔ یک کانال.</t>
+          <t>کانال جریان 2 را با کالیبراسیون بنچ تأییدشده به mA تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_GetCurrentOffsetCounts</t>
+          <t>func__BspMeasurement_Current2DeltaMa</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -4634,19 +4634,19 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>555</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>آفست جریان صفر زندهٔ یک کانال.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_SetCurrentGainPermille</t>
+          <t>func__BspMeasurement_CurrentCountsToMa</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4661,19 +4661,19 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>ضریب گین بنچ یک کانال در زمان اجرا، گیرهٔ 100..3000؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
+          <t>مبدل عمومی قدیمی که دقیقاً همان تابع کانال 2 است، چون از جفت کالیبراسیون کانال 2 استفاده می‌کند. فقط برای این نگه داشته شده که فراخوان‌های قدیمی لینک شوند؛ کد جدید باید تابع پر-کانال را بردارد (دستور کاربر 2026-09-20: شارژر 1 دیگر روی کالیبراسیون شارژر 2 سوار نیست).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_SetCurrentOffsetCounts</t>
+          <t>func__BspMeasurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -4688,19 +4688,19 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>آفست جریان صفر یک کانال در زمان اجرا، گیرهٔ 0..255؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
+          <t>زنجیرهٔ فقط-سخت‌افزاری (مرجع + مقسم ‎R41/R42‎ + گین تقویت‌کننده، بدون آفست و اصلاح) از شمارش خام جریان به ولتاژ شانت بر حسب uV - دیاگ زندهٔ بررسی زنجیرهٔ جریان، دستور کاربر 2026-09-22.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_V12CountsToMv</t>
+          <t>func__BspMeasurement_GetCurrentGainPermille</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4715,19 +4715,19 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>694</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
+          <t>ضریب گین بنچ زندهٔ یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_V24CountsToMv</t>
+          <t>func__BspMeasurement_GetCurrentOffsetCounts</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -4742,19 +4742,19 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>678</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
+          <t>آفست جریان صفر زندهٔ یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_VddaMv</t>
+          <t>func__BspMeasurement_ScaleRoundMa</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4764,159 +4764,159 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>485</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>مرجع واقعی ADC یعنی VDDA را از کانال داخلی 1٫20 ولتی VREFINT اندازه می‌گیرد: چون ولتاژ VREFINT معلوم است، شمارشی که تولید می‌کند می‌گوید مقیاس کامل چقدر می‌ارزد. مقدار مرجع از بیرون داده می‌شود تا این لایهٔ برد به هدرهای کالیبراسیون بنچ وابسته نشود. اگر نتیجه بیرون از چیزی باشد که یک ریل 3٫3 ولت فیزیکاً می‌تواند باشد، صفر برمی‌گردد تا کانال گیرکرده یا فعال‌نشده هرگز بی‌صدا همهٔ خوانش‌های محصول را بازمقیاس نکند.</t>
+          <t>رُند(صورت ‎x 24200 / 27573000)‎ با یک رُند و بدون تقسیم 64بیتی.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_GetCompareCounts</t>
+          <t>func__BspMeasurement_SetCurrentGainPermille</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ compare ی CH1 (پهنای ON گیت) بر حسب تیک تایمر. پورت ADC برد با آن تریگر وسط ON را روی پالس‌های کوتاه (compare 1..7) رد می‌کند: دهانهٔ ADC (625ns) پهن‌تر از چنان پنجره‌ای است، پس نمونهٔ سنکرون آشغال می‌شود و جایگزین اسکن غیرهمزمان مقدار درست است.</t>
+          <t>ضریب گین بنچ یک کانال در زمان اجرا، گیرهٔ 100..3000؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_GetTimer</t>
+          <t>func__BspMeasurement_SetCurrentOffsetCounts</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>613</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>کانال منطقی را به تایمر و کانال فیزیکی برد تبدیل می‌کند.</t>
+          <t>آفست جریان صفر یک کانال در زمان اجرا، گیرهٔ 0..255؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_Init</t>
+          <t>func__BspMeasurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>387</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>هر دو کانال تایمر را یک‌بار شروع می‌کند و گیت‌ها ابتدا پایین‌اند. شمارنده‌ها همیشه می‌چرخند و «خاموش» یعنی ‎compare=0‎. فاز سوئیچ کامپایل است (BSP_PWM_TIM3_PHASE_OFFSET_IN_PHASE): 1u = هم‌فاز (آزمایش میز از 2026-09-24، دستور کاربر)، 0u = درهم‌گذاری نیم‌دورهٔ ثابت (10µs در 50kHz) طرح تولید. /</t>
+          <t>کانال استاندارد 12 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_InitSamplingPulse</t>
+          <t>func__BspMeasurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>کانال داخلی CH2 یک تایمر شارژر را به‌عنوان تریگر نمونه‌برداری سنکرون تنظیم می‌کند: PWM mode 2، قطبیت high، compare صفر در بوت. مرحلهٔ خروجی فعال می‌شود تا OC2 داخلی به مالتی‌پلکس تریگر ADC برسد، اما پایه‌های ‎CH2 (PA1/PA7)‎ آنالوگ می‌مانند. باید قبل از استارت تایمرها و وقتی شمارنده متوقف است اجرا شود.</t>
+          <t>کانال استاندارد 24 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_IsGatePulsing</t>
+          <t>func__BspMeasurement_VddaMv</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>وقتی گیت شارژر منطقی پالس می‌زند true است (‎compare &gt; 0)‎. پورت ADC برد با آن می‌داند لبهٔ تریگر سنکرونِ وسط ON می‌آید یا نه؛ گیت پارک‌شده یعنی جریان اولیه صفر است.</t>
+          <t>مرجع واقعی ADC یعنی VDDA را از کانال داخلی 1٫20 ولتی VREFINT اندازه می‌گیرد: چون ولتاژ VREFINT معلوم است، شمارشی که تولید می‌کند می‌گوید مقیاس کامل چقدر می‌ارزد. مقدار مرجع از بیرون داده می‌شود تا این لایهٔ برد به هدرهای کالیبراسیون بنچ وابسته نشود. اگر نتیجه بیرون از چیزی باشد که یک ریل 3٫3 ولت فیزیکاً می‌تواند باشد، صفر برمی‌گردد تا کانال گیرکرده یا فعال‌نشده هرگز بی‌صدا همهٔ خوانش‌های محصول را بازمقیاس نکند.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_SetDutyPermille</t>
+          <t>func__BspPwm_GetCompareCounts</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4931,19 +4931,19 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>347</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>وظیفهٔ یک شارژر را در بازهٔ 0 تا 1000 پرمیل تنظیم می‌کند. مقدار بالاتر از 1000 محدود و صفر باعث توقف خروجی می‌شود.</t>
+          <t>مقدار زندهٔ compare ی CH1 (پهنای ON گیت) بر حسب تیک تایمر. پورت ADC برد با آن تریگر وسط ON را روی پالس‌های کوتاه (compare 1..7) رد می‌کند: دهانهٔ ADC (625ns) پهن‌تر از چنان پنجره‌ای است، پس نمونهٔ سنکرون آشغال می‌شود و جایگزین اسکن غیرهمزمان مقدار درست است.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_SetOneDuty</t>
+          <t>func__BspPwm_GetTimer</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4958,19 +4958,19 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>وظیفهٔ محدودشدهٔ یک کانال را فقط به‌صورت compare اعمال می‌کند - شمارنده دست نمی‌خورد (هر دو از Init پیوسته با آفست نیم‌دوره می‌چرخند). ‎permille=0‎ یعنی compare صفر و گیت پایین. تریگر داخلی CH2 هم در همین فراخوانی به وسط پنجرهٔ ON جدید می‌رود (‎CCR2 = CCR1/2)‎.</t>
+          <t>کانال منطقی را به تایمر و کانال فیزیکی برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_StopAll</t>
+          <t>func__BspPwm_Init</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4985,186 +4985,186 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>هر دو گیت را پایین می‌آورد (compare صفر)؛ شمارنده‌ها به چرخش می‌مانند تا آفست درهم‌گذاری حفظ شود. تریگرهای داخلی CH2 هم پارک می‌شوند (بدون لبهٔ وسط ON). /</t>
+          <t>هر دو کانال تایمر را یک‌بار شروع می‌کند و گیت‌ها ابتدا پایین‌اند. شمارنده‌ها همیشه می‌چرخند و «خاموش» یعنی ‎compare=0‎. فاز سوئیچ کامپایل است (BSP_PWM_TIM3_PHASE_OFFSET_IN_PHASE): 1u = هم‌فاز (آزمایش میز از 2026-09-24، دستور کاربر)، 0u = درهم‌گذاری نیم‌دورهٔ ثابت (10µs در 50kHz) طرح تولید. /</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_Init</t>
+          <t>func__BspPwm_InitSamplingPulse</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_uart.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>backend UART مقداردهی‌شدهٔ برد را برای ‎ESP-Link‎ انتخاب می‌کند. /</t>
+          <t>کانال داخلی CH2 یک تایمر شارژر را به‌عنوان تریگر نمونه‌برداری سنکرون تنظیم می‌کند: PWM mode 2، قطبیت high، compare صفر در بوت. مرحلهٔ خروجی فعال می‌شود تا OC2 داخلی به مالتی‌پلکس تریگر ADC برسد، اما پایه‌های ‎CH2 (PA1/PA7)‎ آنالوگ می‌مانند. باید قبل از استارت تایمرها و وقتی شمارنده متوقف است اجرا شود.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_PumpTx</t>
+          <t>func__BspPwm_IsGatePulsing</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_uart.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>قطعهٔ پیوستهٔ بعدی حلقهٔ TX را داخل موتور DMA می‌برد؛ از زمینهٔ تسک و از کال‌بک DMA امن است (گارد TxDmaActive)؛ اگر HAL رد کند، داده در حلقه می‌ماند و پمپ بعدی دوباره می‌کوشد. /</t>
+          <t>وقتی گیت شارژر منطقی پالس می‌زند true است (‎compare &gt; 0)‎. پورت ADC برد با آن می‌داند لبهٔ تریگر سنکرونِ وسط ON می‌آید یا نه؛ گیت پارک‌شده یعنی جریان اولیه صفر است.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_ReadByte</t>
+          <t>func__BspPwm_SetDutyPermille</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_uart.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>یک بایت دریافتی ‎ESP-Link‎ را بدون بلوکه‌کردن poll می‌کند؛ بایت از بافر حلقوی RX که DMA پر کرده می‌آید (سخت‌افزار نوشته، CPU فقط آن را بیرون کپی می‌کند).</t>
+          <t>وظیفهٔ یک شارژر را در بازهٔ 0 تا 1000 پرمیل تنظیم می‌کند. مقدار بالاتر از 1000 محدود و صفر باعث توقف خروجی می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_Write</t>
+          <t>func__BspPwm_SetOneDuty</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_uart.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>یک بافر بایت را در UART منطقی ‎ESP-Link‎ صف می‌کند (غیربلوکه).</t>
+          <t>وظیفهٔ محدودشدهٔ یک کانال را فقط به‌صورت compare اعمال می‌کند - شمارنده دست نمی‌خورد (هر دو از Init پیوسته با آفست نیم‌دوره می‌چرخند). ‎permille=0‎ یعنی compare صفر و گیت پایین. تریگر داخلی CH2 هم در همین فراخوانی به وسط پنجرهٔ ON جدید می‌رود (‎CCR2 = CCR1/2)‎.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Active</t>
+          <t>func__BspPwm_StopAll</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>آیا برای این کانال جدول فلش فعال است؟ /</t>
+          <t>هر دو گیت را پایین می‌آورد (compare صفر)؛ شمارنده‌ها به چرخش می‌مانند تا آفست درهم‌گذاری حفظ شود. تریگرهای داخلی CH2 هم پارک می‌شوند (بدون لبهٔ وسط ON). /</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ActiveCrc32</t>
+          <t>func__BspUart_Init</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Bsp/Src/bsp_uart.c</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>CRC32 رکورد فعلی فلش (0 اگر نباشد). /</t>
+          <t>backend UART مقداردهی‌شدهٔ برد را برای ‎ESP-Link‎ انتخاب می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ChannelCheck</t>
+          <t>func__BspUart_PumpTx</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Bsp/Src/bsp_uart.c</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5174,73 +5174,73 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>قانونی‌بودن محورهای یک کانال: 0 نقطه یعنی «جایگزین نشده» و مجاز است؛ در کامیت عمداً override فلش قبلی همان کانال را حذف می‌کند. وگرنه 2..سقف نقطه، محور زنجیرهٔ اکیداً صعودی و محور توان بدون افت (تفریق بدون‌علامت در درون‌یابی، افت را به ~4e9 می‌پیچاند). /</t>
+          <t>قطعهٔ پیوستهٔ بعدی حلقهٔ TX را داخل موتور DMA می‌برد؛ از زمینهٔ تسک و از کال‌بک DMA امن است (گارد TxDmaActive)؛ اگر HAL رد کند، داده در حلقه می‌ماند و پمپ بعدی دوباره می‌کوشد. /</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Commit</t>
+          <t>func__BspUart_ReadByte</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Bsp/Src/bsp_uart.c</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>414</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>اعتبارسنجی و نوشتن جدول چیده‌شده. در موفقیت، نسخهٔ RAM از «خود فلش» دوباره خوانده می‌شود.</t>
+          <t>یک بایت دریافتی ‎ESP-Link‎ را بدون بلوکه‌کردن poll می‌کند؛ بایت از بافر حلقوی RX که DMA پر کرده می‌آید (سخت‌افزار نوشته، CPU فقط آن را بیرون کپی می‌کند).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Crc32</t>
+          <t>func__BspUart_Write</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Bsp/Src/bsp_uart.c</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>CRC32 بازتابیده (استاندارد zip) که جاوااسکریپت پنل هم دارد. /</t>
+          <t>یک بافر بایت را در UART منطقی ‎ESP-Link‎ صف می‌کند (غیربلوکه).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Crc32Byte</t>
+          <t>func__CalLut_Active</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5250,24 +5250,24 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>375</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>افزودن یک بایت به CRC32 در حال اجرا. جدا شد تا جدول چیده‌شده «جریانی» CRC شود: پشتهٔ تسک ارتباط 1KB است و بافر 386 بایتی روی آن دقیقاً همان سرریز بی‌صدایی است که هیچ‌چیز گزارشش نمی‌کند. /</t>
+          <t>آیا برای این کانال جدول فلش فعال است؟ /</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Index</t>
+          <t>func__CalLut_ActiveCrc32</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -5277,24 +5277,24 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>424</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>تبدیل شمارهٔ کانال به اندیس آرایه. /</t>
+          <t>CRC32 رکورد فعلی فلش (0 اگر نباشد). /</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Init</t>
+          <t>func__CalLut_ChannelCheck</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5304,24 +5304,24 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>بارگذاری بوت (قرارداد هدر). /</t>
+          <t>قانونی‌بودن محورهای یک کانال: 0 نقطه یعنی «جایگزین نشده» و مجاز است؛ در کامیت عمداً override فلش قبلی همان کانال را حذف می‌کند. وگرنه 2..سقف نقطه، محور زنجیرهٔ اکیداً صعودی و محور توان بدون افت (تفریق بدون‌علامت در درون‌یابی، افت را به ~4e9 می‌پیچاند). /</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Points</t>
+          <t>func__CalLut_Commit</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5336,19 +5336,19 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>567</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>تعداد نقاط / محور زنجیره / محور توانِ کانال فعال. /</t>
+          <t>اعتبارسنجی و نوشتن جدول چیده‌شده. در موفقیت، نسخهٔ RAM از «خود فلش» دوباره خوانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_RecordValidate</t>
+          <t>func__CalLut_Crc32</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5363,19 +5363,19 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>اعتبارسنجی رکورد نامزد (قرارداد هدر). /</t>
+          <t>CRC32 بازتابیده (استاندارد zip) که جاوااسکریپت پنل هم دارد. /</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_RequestReset</t>
+          <t>func__CalLut_Crc32Byte</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -5385,24 +5385,24 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>مسلح‌کردن ریست بعد از دست‌دادن: ریست داخل هندلر لینک گرفته نمی‌شود؛ فریم تمام می‌شود، شارژر بیکار می‌شود و چند اجرا بعد func__CalLut_Tick() ماشه را می‌کشد. /</t>
+          <t>افزودن یک بایت به CRC32 در حال اجرا. جدا شد تا جدول چیده‌شده «جریانی» CRC شود: پشتهٔ تسک ارتباط 1KB است و بافر 386 بایتی روی آن دقیقاً همان سرریز بی‌صدایی است که هیچ‌چیز گزارشش نمی‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ResumeCharger</t>
+          <t>func__CalLut_Index</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -5417,19 +5417,19 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>362</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تبدیل شمارهٔ کانال به اندیس آرایه. /</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_SeqCompare</t>
+          <t>func__CalLut_Init</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -5439,24 +5439,24 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>مقایسهٔ ترتیب با در نظر گرفتن چرخش شمارنده. /</t>
+          <t>بارگذاری بوت (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_StageBegin</t>
+          <t>func__CalLut_Points</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -5471,19 +5471,19 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>شروع چیدن جدول جدید؛ جدول «فعال» تا موفقیت کامیت سر کار می‌ماند، پس ارسال نیمه‌کاره هیچ‌چیز را خراب نمی‌کند. تعداد صفر مجاز است و کامیت موفق override فلش قبلی همان کانال را حذف می‌کند.</t>
+          <t>تعداد نقاط / محور شمارش / محور mA کانال فعال. /</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_StagePoint</t>
+          <t>func__CalLut_RecordValidate</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -5498,19 +5498,19 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>201</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>ذخیرهٔ یک نقطه در ناحیهٔ چیدن. /</t>
+          <t>اعتبارسنجی رکورد نامزد (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_SuspendCharger</t>
+          <t>func__CalLut_RequestReset</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -5520,24 +5520,24 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>بیکارکردن شارژر دور استال فلش (همان قانون NVM پارامترها). /</t>
+          <t>مسلح‌کردن ریست بعد از دست‌دادن: ریست داخل هندلر لینک گرفته نمی‌شود؛ فریم تمام می‌شود، شارژر بیکار می‌شود و چند اجرا بعد func__CalLut_Tick() ماشه را می‌کشد. /</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Tick</t>
+          <t>func__CalLut_ResumeCharger</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -5547,110 +5547,110 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>555</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط: ریست مسلح‌شده را انجام می‌دهد. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>func__Changeover_Evaluate</t>
+          <t>func__CalLut_SeqCompare</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>حالت بعدی سیستم را از نمونه و خطا حساب می‌کند.</t>
+          <t>مقایسهٔ ترتیب با در نظر گرفتن چرخش شمارنده. /</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>func__Changeover_Init</t>
+          <t>func__CalLut_StageBegin</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.h</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>433</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>از حالت BOOT شروع می‌کند. /</t>
+          <t>شروع چیدن جدول جدید؛ جدول «فعال» تا موفقیت کامیت سر کار می‌ماند، پس ارسال نیمه‌کاره هیچ‌چیز را خراب نمی‌کند. تعداد صفر مجاز است و کامیت موفق override فلش قبلی همان کانال را حذف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ActiveCurrentLimitMa</t>
+          <t>func__CalLut_StagePoint</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ذخیرهٔ یک نقطه در ناحیهٔ چیدن. /</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ApplyDuty</t>
+          <t>func__CalLut_SuspendCharger</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -5660,100 +5660,100 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بیکارکردن شارژر دور استال فلش (همان قانون NVM پارامترها). /</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BatteryVoltageIsValid</t>
+          <t>func__CalLut_Tick</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نگهداری تسک ارتباط: ریست مسلح‌شده را انجام می‌دهد. /</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BringupRegulateChannel</t>
+          <t>func__Changeover_Evaluate</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/Changeover/changeover.c</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Changeover/changeover.h</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>حالت بعدی سیستم را از نمونه و خطا حساب می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BulkStartSettled</t>
+          <t>func__Changeover_Init</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/Changeover/changeover.c</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Changeover/changeover.h</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>فقط وقتی اتصال به‌طور پیوسته حداقل 15 ثانیه معتبر دیده شده اجازهٔ شروع بالک می‌دهد (دستور کاربر: اول ثبات، بعد شارژ).</t>
+          <t>از حالت BOOT شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_CaptureDiag</t>
+          <t>func__Charger_ActiveCurrentLimitMa</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -5768,19 +5768,19 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>513</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>آرایهٔ دیاگ زنده و آرایهٔ برگهٔ کالیبراسیون را با همهٔ مقادیر تصمیم به‌روز می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ChannelCurrentMa</t>
+          <t>func__Charger_ApplyDuty</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>531</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ChannelVoltageMv</t>
+          <t>func__Charger_BatteryVoltageIsValid</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -5834,7 +5834,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampAlarms</t>
+          <t>func__Charger_BringupRegulateChannel</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>843</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampPid</t>
+          <t>func__Charger_BulkStartSettled</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -5876,19 +5876,19 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>فقط وقتی اتصال به‌طور پیوسته حداقل 15 ثانیه معتبر دیده شده اجازهٔ شروع بالک می‌دهد (دستور کاربر: اول ثبات، بعد شارژ).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampProfile</t>
+          <t>func__Charger_CaptureDiag</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آرایهٔ دیاگ زنده و آرایهٔ برگهٔ کالیبراسیون را با همهٔ مقادیر تصمیم به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClearAbsorbWindow</t>
+          <t>func__Charger_ChannelCurrentMa</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -5930,19 +5930,19 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>پاک‌کردن دفترچهٔ پنجرهٔ ابزورب یک کانال (شمارندهٔ شستشو، مهر تیپر و دو مهر پنجره). هر مسیر ری‌استارت/ورود مجدد این را صدا می‌زند تا شستشوی 10 دقیقه همیشه از صفر شروع شود؛ مسیر ورود به ABSORB به‌جای صفر، مهر «اکنون» می‌زند و جدا می‌ماند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBatteryTick</t>
+          <t>func__Charger_ChannelVoltageMv</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -5957,19 +5957,19 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>یک پاس سناریوی 6 برای یک کانال.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBeepPattern</t>
+          <t>func__Charger_ClampAlarms</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBlocksOutput</t>
+          <t>func__Charger_ClampPid</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -6006,24 +6006,24 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>آیا قفلِ باتری خراب باید خروجی را هم ببندد.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadElapsedSeconds</t>
+          <t>func__Charger_ClampProfile</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -6033,24 +6033,24 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>زمان شارژ پیوستهٔ همین کانال بر حسب ثانیه. شمارش از ابتدا هم جداگانه بود، ولی فقط بزرگ‌ترین مقدار از برد بیرون می‌رفت؛ حالا هر کانال جدا گزارش می‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadFaceShape</t>
+          <t>func__Charger_ClearAbsorbWindow</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -6060,24 +6060,24 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>شکل چهرهٔ سناریوی 6 را به ماژول UI می‌دهد.</t>
+          <t>پاک‌کردن دفترچهٔ پنجرهٔ ابزورب یک کانال (شمارندهٔ شستشو، مهر تیپر و دو مهر پنجره). هر مسیر ری‌استارت/ورود مجدد این را صدا می‌زند تا شستشوی 10 دقیقه همیشه از صفر شروع شود؛ مسیر ورود به ABSORB به‌جای صفر، مهر «اکنون» می‌زند و جدا می‌ماند.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadMask</t>
+          <t>func__Charger_DeadBatteryTick</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -6087,24 +6087,24 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>قضاوت قفل‌شده: بیت 0 شارژر 1، بیت 1 شارژر 2.</t>
+          <t>یک پاس سناریوی 6 برای یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadTakePersistFlag</t>
+          <t>func__Charger_DeadBeepPattern</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -6119,19 +6119,19 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>پرچم «قضاوت ماندگار عوض شد» را می‌گیرد و پاک می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadlineElapsed</t>
+          <t>func__Charger_DeadBlocksOutput</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -6141,24 +6141,24 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آیا قفلِ باتری خراب باید خروجی را هم ببندد.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DipResetAbsorbWindow</t>
+          <t>func__Charger_DeadElapsedSeconds</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -6168,24 +6168,24 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>زمان شارژ پیوستهٔ همین کانال بر حسب ثانیه. شمارش از ابتدا هم جداگانه بود، ولی فقط بزرگ‌ترین مقدار از برد بیرون می‌رفت؛ حالا هر کانال جدا گزارش می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DurationTicks</t>
+          <t>func__Charger_DeadFaceShape</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -6195,24 +6195,24 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>شکل چهرهٔ سناریوی 6 را به ماژول UI می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_EnterManualTestMode</t>
+          <t>func__Charger_DeadMask</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -6222,24 +6222,24 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>مود تست دستی را برمی‌دارد: مهر ددمنِ لینک و پاک‌کردن بیت خطای قطع باتری تا آلارمش حین تست بنچ نیفتد (fault.c تا وقتی مود فعال است تشخیص را فریز می‌کند). درایو کانال در همان پاس Evaluate پایین‌تر انجام می‌شود.</t>
+          <t>قضاوت قفل‌شده: بیت 0 شارژر 1، بیت 1 شارژر 2.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Evaluate</t>
+          <t>func__Charger_DeadTakePersistFlag</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -6254,19 +6254,19 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>الگوریتم یکسان کنترل و حفاظت را برای هر کانال نصب‌شدهٔ 12 ولت مستقل اجرا می‌کند. ولتاژ ورودی از مقدار واقعی ADC mV بررسی می‌شود، نه فقط سیگنال دیجیتال PB4. جریان کم درخواست افزایش duty است، نه fault.</t>
+          <t>پرچم «قضاوت ماندگار عوض شد» را می‌گیرد و پاک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_EvaluateTechnicalFault</t>
+          <t>func__Charger_DeadlineElapsed</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -6276,24 +6276,24 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>621</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>خطای فنی سناریوی 7 را از snapshot تازه و JIT اجراشده ارزیابی می‌کند؛ پس از تشخیص بیت خطا و قفل خروجی را تا ریست نگه می‌دارد. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ExitManualTestMode</t>
+          <t>func__Charger_DipResetAbsorbWindow</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -6308,19 +6308,19 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>362</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>خروج از مود تست دستی (کلید خاموش پنل یا ددمن لینک): هر دو duty صفر و هر کانال شارژر خودکار را از OFF با دفترچهٔ تمیز ری‌استارت می‌کند (ثبات اتصال دوباره اعمال می‌شود). قفل FINAL_FAULT هرگز اینجا آزاد نمی‌شود؛ لچ‌های JIT کانال‌های پارک‌شده پاک می‌شوند تا کمپریتور دوباره شلیک کند. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_FinalDisconnect</t>
+          <t>func__Charger_DurationTicks</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -6335,19 +6335,19 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>قطع نهایی fault: بعد از سومین JIT همان کانال، هر دو PWM قبلاً متوقف شده‌اند؛ سپس رله NC باز می‌شود تا ورودی ترانس واقعاً قطع شود. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_FinalDisconnectIdle</t>
+          <t>func__Charger_EnterManualTestMode</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -6362,19 +6362,19 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>standby خطای نهایی وقتی ورودی قطع است: قفل خطا باقی می‌ماند ولی کویل رله رها می‌شود تا باتری را خالی نکند (~50mA). با برگشت ورودی، کویل دوباره به‌صورت خودکار وصل می‌شود. /</t>
+          <t>مود تست دستی را برمی‌دارد: مهر ددمنِ لینک و پاک‌کردن بیت خطای قطع باتری تا آلارمش حین تست بنچ نیفتد (fault.c تا وقتی مود فعال است تشخیص را فریز می‌کند). درایو کانال در همان پاس Evaluate پایین‌تر انجام می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetAlarmParam</t>
+          <t>func__Charger_Evaluate</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -6389,19 +6389,19 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر آلارم شارژر (لینک ESP).</t>
+          <t>الگوریتم یکسان کنترل و حفاظت را برای هر کانال نصب‌شدهٔ 12 ولت مستقل اجرا می‌کند. ولتاژ ورودی از مقدار واقعی ADC mV بررسی می‌شود، نه فقط سیگنال دیجیتال PB4. جریان کم درخواست افزایش duty است، نه fault.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetAppliedDutyPermille</t>
+          <t>func__Charger_EvaluateTechnicalFault</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -6416,19 +6416,19 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>duty واقعی اعمال‌شده به یک کانال را بر حسب پرمیل می‌خواند؛ آشکارساز خطای فنی باید خروجیِ رسیده به سخت‌افزار را ببیند. /</t>
+          <t>خطای فنی سناریوی 7 را از snapshot تازه و JIT اجراشده ارزیابی می‌کند؛ پس از تشخیص بیت خطا و قفل خروجی را تا ریست نگه می‌دارد. /</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetChannelEspEnable</t>
+          <t>func__Charger_ExitManualTestMode</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -6438,24 +6438,24 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>گیت فعال‌سازی ESP یک کانال شارژر را می‌خواند.</t>
+          <t>خروج از مود تست دستی (کلید خاموش پنل یا ددمن لینک): هر دو duty صفر و هر کانال شارژر خودکار را از OFF با دفترچهٔ تمیز ری‌استارت می‌کند (ثبات اتصال دوباره اعمال می‌شود). قفل FINAL_FAULT هرگز اینجا آزاد نمی‌شود؛ لچ‌های JIT کانال‌های پارک‌شده پاک می‌شوند تا کمپریتور دوباره شلیک کند. /</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDeadParam</t>
+          <t>func__Charger_FinalDisconnect</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -6465,24 +6465,24 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>خواندن پارامتر سناریوی 6 یا اسلات قضاوت.</t>
+          <t>قطع نهایی fault: بعد از سومین JIT همان کانال، هر دو PWM قبلاً متوقف شده‌اند؛ سپس رله NC باز می‌شود تا ورودی ترانس واقعاً قطع شود. /</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyCeilingPermille</t>
+          <t>func__Charger_FinalDisconnectIdle</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -6492,24 +6492,24 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>439</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>سقف زندهٔ duty ی PWM یک کانال.</t>
+          <t>standby خطای نهایی وقتی ورودی قطع است: قفل خطا باقی می‌ماند ولی کویل رله رها می‌شود تا باتری را خالی نکند (~50mA). با برگشت ورودی، کویل دوباره به‌صورت خودکار وصل می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyFixedEnable</t>
+          <t>func__Charger_GetAlarmParam</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -6524,19 +6524,19 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>کلید مود duty فیکس یک کانال.</t>
+          <t>خواندن یک پارامتر آلارم شارژر (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyFixedPermille</t>
+          <t>func__Charger_GetAppliedDutyPermille</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -6551,19 +6551,19 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>مقدار ذخیره‌شدهٔ duty فیکس یک کانال.</t>
+          <t>duty واقعی اعمال‌شده به یک کانال را بر حسب پرمیل می‌خواند؛ آشکارساز خطای فنی باید خروجیِ رسیده به سخت‌افزار را ببیند. /</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetEfficiencyPermille</t>
+          <t>func__Charger_GetChannelEspEnable</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -6578,19 +6578,19 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>بازدهی flyback زندهٔ یک کانال را می‌خواند.</t>
+          <t>گیت فعال‌سازی ESP یک کانال شارژر را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetLimitParam</t>
+          <t>func__Charger_GetDeadParam</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک حد یا گین پشتیبان شارژر (لینک ESP).</t>
+          <t>خواندن پارامتر سناریوی 6 یا اسلات قضاوت.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetManualTestMode</t>
+          <t>func__Charger_GetDutyCeilingPermille</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -6632,19 +6632,19 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>پرچم «درخواست‌شدهٔ» مود دستی (مقدار پارامتری که پنل نوشته؛ حداکثر یک دورهٔ کنترل با وضعیت فعال اختلاف دارد).</t>
+          <t>سقف زندهٔ duty ی PWM یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetPidParam</t>
+          <t>func__Charger_GetDutyFixedEnable</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -6659,19 +6659,19 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر PID دوحلقه‌ای (لینک ESP).</t>
+          <t>کلید مود duty فیکس یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetProfileParam</t>
+          <t>func__Charger_GetDutyFixedPermille</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -6686,19 +6686,19 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر پروفایل شارژ (لینک ESP).</t>
+          <t>مقدار ذخیره‌شدهٔ duty فیکس یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_HandleJitTrip</t>
+          <t>func__Charger_GetLimitParam</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -6708,24 +6708,24 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>خواندن یک حد یا گین پشتیبان شارژر (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Init</t>
+          <t>func__Charger_GetManualTestMode</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -6740,19 +6740,19 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>state سیاست را مقداردهی اولیه می‌کند، همه PWMها را متوقف و وضعیت ‎safe-idle‎ قطعی را اعمال می‌کند. با ‎CHG_MASTER_ENABLE=0‎ این تنها رفتار فعال باقی می‌ماند. /</t>
+          <t>پرچم «درخواست‌شدهٔ» مود دستی (مقدار پارامتری که پنل نوشته؛ حداکثر یک دورهٔ کنترل با وضعیت فعال اختلاف دارد).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsAnyChannelActive</t>
+          <t>func__Charger_GetPidParam</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -6767,19 +6767,19 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>true وقتی دست‌کم یک کانال نصب‌شده واقعاً در حال شارژ است (بالک/ابزورب؛ فلوت پارک‌شده یعنی کار تمام شده و فعال حساب نمی‌شود - چهرهٔ فول با IsChargeComplete می‌آید و آشکارساز قطع باتری هم آنجا مسلح نیست).</t>
+          <t>خواندن یک پارامتر PID دوحلقه‌ای (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelActive</t>
+          <t>func__Charger_GetProfileParam</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -6794,19 +6794,19 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
+          <t>خواندن یک پارامتر پروفایل شارژ (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelInstalled</t>
+          <t>func__Charger_HandleJitTrip</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -6833,7 +6833,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChargeComplete</t>
+          <t>func__Charger_Init</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -6848,19 +6848,19 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
+          <t>state سیاست را مقداردهی اولیه می‌کند، همه PWMها را متوقف و وضعیت ‎safe-idle‎ قطعی را اعمال می‌کند. با ‎CHG_MASTER_ENABLE=0‎ این تنها رفتار فعال باقی می‌ماند. /</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsManualTestModeActive</t>
+          <t>func__Charger_IsAnyChannelActive</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -6875,19 +6875,19 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
+          <t>true وقتی دست‌کم یک کانال نصب‌شده واقعاً در حال شارژ است (بالک/ابزورب؛ فلوت پارک‌شده یعنی کار تمام شده و فعال حساب نمی‌شود - چهرهٔ فول با IsChargeComplete می‌آید و آشکارساز قطع باتری هم آنجا مسلح نیست).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsRelayOpen</t>
+          <t>func__Charger_IsChannelActive</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -6902,19 +6902,19 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
+          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsSuspended</t>
+          <t>func__Charger_IsChannelInstalled</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -6924,24 +6924,24 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsTechnicalFaultLocked</t>
+          <t>func__Charger_IsChargeComplete</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -6956,19 +6956,19 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
+          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_LatchFinalFault</t>
+          <t>func__Charger_IsManualTestModeActive</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -6978,24 +6978,24 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Limit</t>
+          <t>func__Charger_IsRelayOpen</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -7005,24 +7005,24 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
+          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ManualDriveChannel</t>
+          <t>func__Charger_IsSuspended</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -7032,24 +7032,24 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
+          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_MaxDutyPermille</t>
+          <t>func__Charger_IsTechnicalFaultLocked</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -7059,24 +7059,24 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_NotifyEspLinkActivity</t>
+          <t>func__Charger_LatchFinalFault</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -7086,24 +7086,24 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_OutputEstimateMa</t>
+          <t>func__Charger_Limit</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -7118,19 +7118,19 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>تخمین جریان سمت باتری. وقتی LUT باتری Measurement فعال است، جریان فیلترشدهٔ ورودی همین حالا جریان باتری است؛ بنابراین OutputEstimateMa حتی با ETA قدیمیِ مانده در NVM همانی است. بدون LUT، ETA صفر نیز همانی است و ETA غیرصفر تبدیل زندهٔ iest = I × Vin × eta ÷ (1000 × Vbat) را انجام می‌دهد؛ گاردهای ولتاژ پایین فقط روی همین مسیر legacy اعمال می‌شوند.</t>
+          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidCeilingMilli</t>
+          <t>func__Charger_ManualDriveChannel</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -7145,19 +7145,19 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidClampError</t>
+          <t>func__Charger_MaxDutyPermille</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidInvalidate</t>
+          <t>func__Charger_NotifyEspLinkActivity</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -7194,24 +7194,24 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidStep</t>
+          <t>func__Charger_PidCeilingMilli</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -7226,19 +7226,19 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>963</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PwmChannel</t>
+          <t>func__Charger_PidClampError</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>978</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7265,7 +7265,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RegulateChannel</t>
+          <t>func__Charger_PidInvalidate</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ResetChannelToOff</t>
+          <t>func__Charger_PidStep</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -7307,19 +7307,19 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RetryDuty</t>
+          <t>func__Charger_PwmChannel</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -7346,7 +7346,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SafeIdle</t>
+          <t>func__Charger_RegulateChannel</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -7373,7 +7373,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ServiceRetry</t>
+          <t>func__Charger_ResetChannelToOff</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>629</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -7400,7 +7400,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetAlarmParam</t>
+          <t>func__Charger_RetryDuty</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -7410,24 +7410,24 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>733</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetChannelEspEnable</t>
+          <t>func__Charger_SafeIdle</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -7437,24 +7437,24 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>370</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDeadParam</t>
+          <t>func__Charger_ServiceRetry</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -7464,24 +7464,24 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>764</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyCeilingPermille</t>
+          <t>func__Charger_SetAlarmParam</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -7496,19 +7496,19 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedEnable</t>
+          <t>func__Charger_SetChannelEspEnable</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -7523,19 +7523,19 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
+          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedPermille</t>
+          <t>func__Charger_SetDeadParam</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -7550,19 +7550,19 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetEfficiencyPermille</t>
+          <t>func__Charger_SetDutyCeilingPermille</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -7577,19 +7577,19 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>ضریب تبدیل زمان اجرای یک کانال، گیرهٔ 0..999 پرمیل (v1.3): صفر = همانی (پیش‌فرض)، غیرصفر = تبدیل زندهٔ ‎iest = I‎ × Vin × η ÷ (1000 × Vbat). کانال 0 = شارژر 1 (باتری بالا)، 1 = شارژر 2. روی فلش از v1.14 (شناسه 9/10)؛ از پنل ESP و CAL_REFERENCE.</t>
+          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetLimitParam</t>
+          <t>func__Charger_SetDutyFixedEnable</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -7604,19 +7604,19 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
+          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetManualTestMode</t>
+          <t>func__Charger_SetDutyFixedPermille</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -7631,19 +7631,19 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
+          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetPidParam</t>
+          <t>func__Charger_SetLimitParam</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -7658,19 +7658,19 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetProfileParam</t>
+          <t>func__Charger_SetManualTestMode</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -7685,19 +7685,19 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
+          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetSuspended</t>
+          <t>func__Charger_SetPidParam</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -7712,19 +7712,19 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
+          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_StopOneChannel</t>
+          <t>func__Charger_SetProfileParam</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -7734,56 +7734,56 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ApplyParam</t>
+          <t>func__Charger_SetSuspended</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
+          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ConsumeLutResetAuthorization</t>
+          <t>func__Charger_StopOneChannel</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -7805,7 +7805,7 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Crc16</t>
+          <t>func__EspLink_ApplyParam</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -7815,24 +7815,24 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
+          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetParam</t>
+          <t>func__EspLink_ConsumeLutResetAuthorization</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -7842,24 +7842,24 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetU32</t>
+          <t>func__EspLink_Crc16</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
@@ -7874,19 +7874,19 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>639</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
+          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleFrame</t>
+          <t>func__EspLink_GetParam</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -7896,24 +7896,24 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>440</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutFrame</t>
+          <t>func__EspLink_GetU32</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
@@ -7928,19 +7928,19 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
+          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutRead</t>
+          <t>func__EspLink_HandleFrame</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -7955,19 +7955,19 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_AcceptedFrames</t>
+          <t>func__EspLink_HandleLutFrame</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
@@ -7977,24 +7977,24 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_CrcErrors</t>
+          <t>func__EspLink_HandleLutRead</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -8004,24 +8004,24 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_FeedByte</t>
+          <t>func__EspLink_HostTest_AcceptedFrames</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_HandleLutFrame</t>
+          <t>func__EspLink_HostTest_CrcErrors</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_RecordCommitAck</t>
+          <t>func__EspLink_HostTest_FeedByte</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_Reset</t>
+          <t>func__EspLink_HostTest_HandleLutFrame</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -8129,7 +8129,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_TryReset</t>
+          <t>func__EspLink_HostTest_RecordCommitAck</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_VersionErrors</t>
+          <t>func__EspLink_HostTest_Reset</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Init</t>
+          <t>func__EspLink_HostTest_TryReset</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -8198,73 +8198,73 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmCrc32</t>
+          <t>func__EspLink_HostTest_VersionErrors</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmFlushForReset</t>
+          <t>func__EspLink_Init</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
+          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmInit</t>
+          <t>func__EspLink_NvmCrc32</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -8279,19 +8279,19 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
+          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmMarkDirty</t>
+          <t>func__EspLink_NvmFlushForReset</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -8306,19 +8306,19 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
+          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmParamPersisted</t>
+          <t>func__EspLink_NvmInit</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -8333,19 +8333,19 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
+          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordBuild</t>
+          <t>func__EspLink_NvmMarkDirty</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -8360,19 +8360,19 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>425</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
+          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordValidate</t>
+          <t>func__EspLink_NvmParamPersisted</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -8387,19 +8387,19 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
+          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmResumeCharger</t>
+          <t>func__EspLink_NvmRecordBuild</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -8409,24 +8409,24 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
+          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSaveNow</t>
+          <t>func__EspLink_NvmRecordValidate</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -8436,24 +8436,24 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSeqCompare</t>
+          <t>func__EspLink_NvmResumeCharger</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -8463,24 +8463,24 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
+          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSuspendCharger</t>
+          <t>func__EspLink_NvmSaveNow</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -8495,19 +8495,19 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmTick</t>
+          <t>func__EspLink_NvmSeqCompare</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -8522,24 +8522,24 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
+          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ParseByte</t>
+          <t>func__EspLink_NvmSuspendCharger</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -8549,46 +8549,46 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>480</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
+          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Power</t>
+          <t>func__EspLink_NvmTick</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>پایه CH_PD را می‌زند.</t>
+          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU16</t>
+          <t>func__EspLink_ParseByte</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -8603,19 +8603,19 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU32</t>
+          <t>func__EspLink_Power</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -8625,24 +8625,24 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>پایه CH_PD را می‌زند.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_RecordLutCommitAck</t>
+          <t>func__EspLink_PutU16</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -8657,19 +8657,19 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ResyncFromByte</t>
+          <t>func__EspLink_PutU32</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -8684,19 +8684,19 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Run</t>
+          <t>func__EspLink_RecordLutCommitAck</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -8706,24 +8706,24 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendFrame</t>
+          <t>func__EspLink_ResyncFromByte</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -8738,19 +8738,19 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutAck</t>
+          <t>func__EspLink_Run</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
@@ -8760,24 +8760,24 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
+          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutData</t>
+          <t>func__EspLink_SendFrame</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
@@ -8792,19 +8792,19 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>666</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
+          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamReport</t>
+          <t>func__EspLink_SendLutAck</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -8819,19 +8819,19 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
+          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamsBulk</t>
+          <t>func__EspLink_SendLutData</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -8846,19 +8846,19 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendTelemetry</t>
+          <t>func__EspLink_SendParamReport</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -8873,51 +8873,51 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
+          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Any</t>
+          <t>func__EspLink_SendParamsBulk</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>830</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>اگر هر بیتی روشن باشد true.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_ClampAlarms</t>
+          <t>func__EspLink_SendTelemetry</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -8927,19 +8927,19 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>901</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
+          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Clear</t>
+          <t>func__Fault_Any</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -8954,19 +8954,19 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>468</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را پاک می‌کند.</t>
+          <t>اگر هر بیتی روشن باشد true.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_DebounceDone</t>
+          <t>func__Fault_ClampAlarms</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
@@ -8981,19 +8981,19 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
+          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Evaluate</t>
+          <t>func__Fault_Clear</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -9008,19 +9008,19 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
+          <t>بیت‌ها را پاک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Get</t>
+          <t>func__Fault_DebounceDone</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
@@ -9030,24 +9030,24 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>ماسک فعلی را برمی‌گرداند.</t>
+          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_GetAlarmParam</t>
+          <t>func__Fault_Evaluate</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
@@ -9062,19 +9062,19 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>482</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
+          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Init</t>
+          <t>func__Fault_Get</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
@@ -9089,19 +9089,19 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>456</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
+          <t>ماسک فعلی را برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_OnSupervisionChange</t>
+          <t>func__Fault_GetAlarmParam</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -9116,19 +9116,19 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Set</t>
+          <t>func__Fault_Init</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
@@ -9143,19 +9143,19 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را قفل می‌کند (OR).</t>
+          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_SetAlarmParam</t>
+          <t>func__Fault_OnSupervisionChange</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -9170,73 +9170,73 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
+          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Evaluate</t>
+          <t>func__Fault_Set</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>410</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بیت‌ها را قفل می‌کند (OR).</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetOutputs</t>
+          <t>func__Fault_SetAlarmParam</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetParam</t>
+          <t>func__Imbalance_Evaluate</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Init</t>
+          <t>func__Imbalance_GetOutputs</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -9290,7 +9290,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamClamp</t>
+          <t>func__Imbalance_GetParam</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -9317,7 +9317,7 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamDefault</t>
+          <t>func__Imbalance_Init</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -9344,7 +9344,7 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ReadParam</t>
+          <t>func__Imbalance_ParamClamp</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SeedDefaultsOnce</t>
+          <t>func__Imbalance_ParamDefault</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SetParam</t>
+          <t>func__Imbalance_ReadParam</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -9425,61 +9425,61 @@
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ChannelTripped</t>
+          <t>func__Imbalance_SeedDefaultsOnce</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ClearChannel</t>
+          <t>func__Imbalance_SetParam</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Init</t>
+          <t>func__Jitter_ChannelTripped</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
@@ -9494,19 +9494,19 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
+          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Run</t>
+          <t>func__Jitter_ClearChannel</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
@@ -9521,73 +9521,73 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
+          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Init</t>
+          <t>func__Jitter_Init</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
+          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_OnInputIrq</t>
+          <t>func__Jitter_Run</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
+          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Run</t>
+          <t>func__McuPowerPath_Init</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
@@ -9602,73 +9602,73 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
+          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyCurrentFilters</t>
+          <t>func__McuPowerPath_OnInputIrq</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
+          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyVoltageOffsetMv</t>
+          <t>func__McuPowerPath_Run</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
+          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Battery12BenchCompensate</t>
+          <t>func__Measurement_ApplyCurrentFilters</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
@@ -9683,19 +9683,19 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>جبران V12 به باتری واقعی: کم‌کردن خطای ثابت کانال و افت مسیر I2×R؛ هرگز زیر 0mV نمی‌رود.</t>
+          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Battery24CountsToMv</t>
+          <t>func__Measurement_ApplyVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
@@ -9705,24 +9705,24 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>860</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
+          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_BenchLutInterp</t>
+          <t>func__Measurement_Battery24CountsToMv</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
@@ -9732,24 +9732,24 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>درون‌یابی خطی-تکه‌ای روی یک جدول بنچ: mA زنجیره ← توان باتری. هر دو کانال و «هر دو منبع» (جدول کامپایل‌تایم در calibration.h و جدول فلش که ارسال پنل ذخیره کرده - v1.66) از همین یک تابع می‌گذرند، پس جدول ارسال‌شده هرگز نمی‌تواند رفتار متفاوتی از جدول چسبانده‌شده داشته باشد؛ تنها تفاوت این است که کدام آرایه خوانده می‌شود.</t>
+          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CountsToMv</t>
+          <t>func__Measurement_BenchTableMa</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
@@ -9759,24 +9759,24 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>جستجوی جدول بر حسب شمارش؛ فراخوان‌کننده برون‌یابی بالای جدول (تفاضل BSPfull از آخرین لنگر، با یک رُند) را می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1BenchLut</t>
+          <t>func__Measurement_CountsToMv</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
@@ -9786,17 +9786,17 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>568</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>اصلاح خطی-تکه‌ای بنچ: mA زنجیرهٔ ADC کانال 1 → «توان باتری 1» بر حسب mW (انرژی هر سایکل DCM مستقل از ولتاژ باتری است؛ جریان = ‎P/Vbat‎، پس جدول توان را می‌دهد و صداکننده بر ولتاژ زنده تقسیم می‌کند). بین لنگرها درون‌یابی خطی؛ بالای آخرین لنگر شیب آخر ادامه می‌یابد؛ صفر به صفر.</t>
+          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
@@ -9818,19 +9818,19 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام کانال 1 به mA باتری: کالیبراسیون خطی BSP و بعد - با فعال بودن جدول بنچ - اصلاح خطی-تکه‌ای (زنجیرهٔ خطیِ تنها، Sشکل برابر DMM می‌خواند). جدول روی خروجی زنجیرهٔ قدیم می‌نشیند پس بدون فیلتر، فیلترشده و iest هر سه به mA واقعی باتری تبدیل می‌شوند؛ شمارش خام و uV شانت دست نمی‌خورند.</t>
+          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2BenchLut</t>
+          <t>func__Measurement_Current1CountsToMaLocked</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>شمارش کانال 1 به mA باتری 1. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
@@ -9872,19 +9872,19 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>799</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام کانال 2 به mA باتری: کالیبراسیون خطی BSP و بعد - با فعال بودن جدول بنچ - اصلاح خطی-تکه‌ای. جدول روی خروجی زنجیرهٔ قدیم می‌نشیند، پس بدون فیلتر، فیلترشده و iest هر سه به mA واقعی باتری تبدیل می‌شوند؛ شمارش خام و uV شانت دست نمی‌خورند.</t>
+          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToMa</t>
+          <t>func__Measurement_Current2CountsToMaLocked</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
@@ -9894,24 +9894,24 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>765</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToShuntUv</t>
+          <t>func__Measurement_CurrentCountsToMa</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -9926,19 +9926,19 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
+          <t>func__Measurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
@@ -9953,19 +9953,19 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>838</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>اعلام می‌کند که خروجی جریان کانال همین حالا با LUT توانی کالیبره و متعلق به سمت باتری است. وقتی true است، کد بعدی شارژر نباید تبدیل دوم Vin/Vbat را اعمال کند، حتی اگر ETA قدیمی در NVM مانده باشد.</t>
+          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMedian</t>
+          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -9975,24 +9975,24 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>807</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
+          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید تبدیل دوم ‎Vin/Vbat‎ را اعمال کند، حتی اگر ETA کند.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMovingAverage</t>
+          <t>func__Measurement_CurrentMedian</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
@@ -10007,19 +10007,19 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
+          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterAverageWindow</t>
+          <t>func__Measurement_CurrentMovingAverage</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -10029,24 +10029,24 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
+          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterMedianSize</t>
+          <t>func__Measurement_GetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
@@ -10061,19 +10061,19 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetSnapshot</t>
+          <t>func__Measurement_GetFilterMedianSize</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -10088,19 +10088,19 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetVoltageOffsetMv</t>
+          <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
@@ -10115,19 +10115,19 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
+          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_HostTest_MulDivU32</t>
+          <t>func__Measurement_GetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
@@ -10142,24 +10142,24 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>probeٔ دقیق arithmetic LUT، فقط برای تست هاست.</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Init</t>
+          <t>func__Measurement_HostTest_MulDivU32</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
@@ -10167,21 +10167,17 @@
           <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
-      <c r="D242" s="5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
+      <c r="D242" s="5" t="inlineStr"/>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
+          <t>probeٔ دقیق arithmetic LUT، فقط برای تست هاست.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_InterpU32Increasing</t>
+          <t>func__Measurement_Init</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -10191,17 +10187,17 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>509</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10258,7 @@
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_MulDivU32Saturating</t>
+          <t>func__Measurement_ResetCurrentFilters</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
@@ -10277,19 +10273,19 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>379</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_PowerMwToMa</t>
+          <t>func__Measurement_Run</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -10299,24 +10295,24 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>882</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ResetCurrentFilters</t>
+          <t>func__Measurement_SetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
@@ -10326,24 +10322,24 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
+          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Run</t>
+          <t>func__Measurement_SetFilterMedianSize</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -10358,19 +10354,19 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
+          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterAverageWindow</t>
+          <t>func__Measurement_SetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
@@ -10385,19 +10381,19 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterMedianSize</t>
+          <t>func__Measurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
@@ -10412,19 +10408,19 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
+          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetVoltageOffsetMv</t>
+          <t>func__Measurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
@@ -10439,127 +10435,127 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
+          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V12CountsToMv</t>
+          <t>func__Protection_Init</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V24CountsToMv</t>
+          <t>func__Protection_Run</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Init</t>
+          <t>func__Rtos_DelayMilliseconds</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
+          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Run</t>
+          <t>func__Rtos_Fatal</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
+          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_DelayMilliseconds</t>
+          <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -10574,19 +10570,19 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
+          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Fatal</t>
+          <t>func__Rtos_Start</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -10596,24 +10592,24 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_app.h</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
+          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_MillisecondsToTicks</t>
+          <t>func__Rtos_TicksToMilliseconds</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
@@ -10628,78 +10624,78 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
+          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Start</t>
+          <t>func__TaskComm</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Rtos/Src/task_comm.c</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_app.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
+          <t>تسک ‎UART/ESP‎.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_TicksToMilliseconds</t>
+          <t>func__TaskControl</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Rtos/Src/task_control.c</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
+          <t>تسک Changeover و شارژر.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>func__TaskComm</t>
+          <t>func__TaskMeasurement</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_comm.c</t>
+          <t>Firmware/Rtos/Src/task_measurement.c</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
@@ -10709,24 +10705,24 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>تسک ‎UART/ESP‎.</t>
+          <t>تسک نمونه‌برداری ADC.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>func__TaskControl</t>
+          <t>func__TaskProtection</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_control.c</t>
+          <t>Firmware/Rtos/Src/task_protection.c</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
@@ -10736,24 +10732,24 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>تسک Changeover و شارژر.</t>
+          <t>تسک حفاظت.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>func__TaskMeasurement</t>
+          <t>func__TaskUi</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_measurement.c</t>
+          <t>Firmware/Rtos/Src/task_ui.c</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -10763,73 +10759,73 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>تسک نمونه‌برداری ADC.</t>
+          <t>تسک LED و بازر. در این مرحله فعال است.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>func__TaskProtection</t>
+          <t>func__Ui_AlarmParamIndex</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_protection.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>تسک حفاظت.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>func__TaskUi</t>
+          <t>func__Ui_BatteryVoltageToPercent</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_ui.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>تسک LED و بازر. در این مرحله فعال است.</t>
+          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_AlarmParamIndex</t>
+          <t>func__Ui_BeepDutyPercent</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -10844,19 +10840,19 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BatteryVoltageToPercent</t>
+          <t>func__Ui_BoardTest_Start</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -10871,19 +10867,19 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
+          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BeepDutyPercent</t>
+          <t>func__Ui_Buzzer_Gated</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -10898,46 +10894,46 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>387</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
+          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BoardTest_Start</t>
+          <t>func__Ui_Buzzer_Tick</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
+          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Gated</t>
+          <t>func__Ui_ChargeVoltageToPercent</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -10947,51 +10943,51 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>650</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
+          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Tick</t>
+          <t>func__Ui_ClampAlarms</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>187</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
+          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ChargeVoltageToPercent</t>
+          <t>func__Ui_ClampPeriod</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -11001,24 +10997,24 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
+          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampAlarms</t>
+          <t>func__Ui_ClampWindow</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
@@ -11033,19 +11029,19 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
+          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampPeriod</t>
+          <t>func__Ui_GetAlarmParam</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
@@ -11055,24 +11051,24 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>532</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
+          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampWindow</t>
+          <t>func__Ui_Init</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -11082,24 +11078,24 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
+          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_GetAlarmParam</t>
+          <t>func__Ui_ResetBatteryCriticalBeep</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -11109,24 +11105,24 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
+          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Init</t>
+          <t>func__Ui_ResetBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
@@ -11136,24 +11132,24 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
+          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryCriticalBeep</t>
+          <t>func__Ui_ResetBatteryStablePercent</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -11168,19 +11164,19 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>896</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
+          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryRunGreenBlink</t>
+          <t>func__Ui_ResetChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -11195,19 +11191,19 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
+          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryStablePercent</t>
+          <t>func__Ui_ResetChargingStablePercent</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -11222,19 +11218,19 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>984</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
+          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingFullHysteresis</t>
+          <t>func__Ui_ResetChargingYellowBlink</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -11249,19 +11245,19 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
+          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingStablePercent</t>
+          <t>func__Ui_ScenarioBatLost_Tick</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -11271,24 +11267,24 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
+          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingYellowBlink</t>
+          <t>func__Ui_ScenarioBatteryRun_Tick</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -11298,24 +11294,24 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
+          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatLost_Tick</t>
+          <t>func__Ui_ScenarioCharging_Tick</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -11330,19 +11326,19 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
+          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatteryRun_Tick</t>
+          <t>func__Ui_ScenarioDeadBattery_Tick</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -11357,19 +11353,19 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
+          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioCharging_Tick</t>
+          <t>func__Ui_ScenarioImbalance_Tick</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -11384,19 +11380,19 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
+          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioDeadBattery_Tick</t>
+          <t>func__Ui_ScenarioInputOk</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -11411,19 +11407,19 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
+          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioImbalance_Tick</t>
+          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -11433,24 +11429,24 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
+          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOk</t>
+          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -11460,24 +11456,24 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
+          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
+          <t>func__Ui_SetAlarmParam</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -11487,24 +11483,24 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
+          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
+          <t>func__Ui_Tick</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -11514,24 +11510,24 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
+          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_SetAlarmParam</t>
+          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -11541,24 +11537,24 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
+          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Tick</t>
+          <t>func__Ui_UpdateBatteryStablePercent</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -11568,24 +11564,24 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>909</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
+          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
+          <t>func__Ui_UpdateChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -11600,19 +11596,19 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
+          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryStablePercent</t>
+          <t>func__Ui_UpdateChargingStablePercent</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -11627,19 +11623,19 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
+          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingFullHysteresis</t>
+          <t>func__Ui_UpdateChargingYellowBlink</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -11654,19 +11650,19 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
+          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingStablePercent</t>
+          <t>func__Ui_UpdateInputState</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -11681,19 +11677,19 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
+          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingYellowBlink</t>
+          <t>func__Ui_VoltageToPercentMap</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
@@ -11708,19 +11704,19 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>578</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
+          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateInputState</t>
+          <t>func__all_off</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
@@ -11735,19 +11731,19 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>699</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
+          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_VoltageToPercentMap</t>
+          <t>func__green</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
@@ -11762,19 +11758,19 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>func__all_off</t>
+          <t>func__red</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
@@ -11789,19 +11785,19 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>676</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
+          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>func__green</t>
+          <t>func__yellow</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
@@ -11816,64 +11812,10 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>688</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
-        <is>
-          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="5" t="inlineStr">
-        <is>
-          <t>func__red</t>
-        </is>
-      </c>
-      <c r="B304" s="5" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
-        </is>
-      </c>
-      <c r="C304" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D304" s="5" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="E304" s="5" t="inlineStr">
-        <is>
-          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="5" t="inlineStr">
-        <is>
-          <t>func__yellow</t>
-        </is>
-      </c>
-      <c r="B305" s="5" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
-        </is>
-      </c>
-      <c r="C305" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D305" s="5" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="E305" s="5" t="inlineStr">
         <is>
           <t>ال‌ای‌دی زرد را روشن/خاموش می‌کند.</t>
         </is>
@@ -11979,7 +11921,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -12021,7 +11963,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -12063,7 +12005,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -12105,7 +12047,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -12347,24 +12289,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>u32</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>permille</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>0..999</t>
-        </is>
-      </c>
+          <t>RESERVED: removed with the Vin/Vbat formula; get/set rejected</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>بله</t>
@@ -12389,24 +12319,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>u32</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>permille</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>0..999</t>
-        </is>
-      </c>
+          <t>RESERVED: removed with the Vin/Vbat formula; get/set rejected</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>بله</t>
@@ -19134,7 +19052,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>91 فایل · 303 تابع · 147 شناسه · 20 سیگنال</t>
+          <t>91 فایل · 301 تابع · 147 شناسه · 20 سیگنال</t>
         </is>
       </c>
     </row>

--- a/Documentation/Program_Map.xlsx
+++ b/Documentation/Program_Map.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>301 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
+          <t>298 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>190</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>735</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>پیاده‌سازی قفلِ پرچم تریپ LM393: پرچم‌های نرم‌افزاری EXTI لایهٔ برد را می‌خواند، برای هر کانال یک بولینِ چسبنده قفل می‌کند و پاک‌کردن تکی و کلی می‌دهد. هیچ HAL و شمارهٔ پایه‌ای اینجا نیست؛ اینکه کدام خط EXTI به کدام مقایسه‌گر می‌رود کار پورت برد است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
+          <t>پیاده‌سازی قفلِ پرچم تریپ LM393: پرچم‌های نرم‌افزاری EXTI لایهٔ برد را می‌خواند، برای هر کانال یک بولینِ چسبنده قفل می‌کند و پاک‌کردن تکی می‌دهد. هیچ HAL و شمارهٔ پایه‌ای اینجا نیست؛ اینکه کدام خط EXTI به کدام مقایسه‌گر می‌رود کار پورت برد است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>354</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>پل ‎ESP-Link‎ سمت ESP: تبادل فریم باینری با STM32 روی UART (921600 8N1، مطابق ESP_AGENT_SPEC.md نسخهٔ 1.4) و یک پنل وب دارک راست‌به‌چپ با فونت وزیرمتن و «دو» تب (کارت duty دستی از 1.10 در تب پنل؛ سقف duty، نمونه‌های نمودار، حذف صبر و مقسم پک هم در 1.10): 1) پنل: ولتاژهای مشترک (با کالیبراسیون آفست از مولتی‌متر)، فیلتر جریان (median 1..15، میانگین 1..300) و یک ستون برای هر شارژر: وضعیت زنده، زنجیرهٔ اندازه‌گیری با فرمول زنده، نمودار فیلتر و دکمهٔ قطع شارژر. 2) داده‌برداری بنچ (بخش ‎5.6): SOLO1/SOLO2/BOTH‎ با فهرست duty دلخواه و جلو رفتن فقط با دکمهٔ کاربر. اصلاح 1.7 (دستور کاربر 2026-09-25): پنجرهٔ آمار با باز شدن فرم مولتی‌متر صفر می‌شود و «همان لحظهٔ زدن ثبت» خوانده می‌شود تا ردیف CSV با عددهای واردشده هم‌لحظه باشد، نه یک پنجرهٔ کهنه؛ ستون sample_ms مدت واقعی همان پنجره است. یک ردیف 89ستونی برای هر مرحله در LittleFS به نام /benchlog.csv، دانلود با ‎GET /benchlog‎. اضافات نسخهٔ 1.6 (کارت CAL، تست‌های دستی ‎B/C/D‎، تب اصلاح/تحلیل، حالت مهندس) حذف شدند؛ هیچ کالیبراسیونی خودکار اعمال نمی‌شود و پروتکل سیمی (‎SET/GET/TLM)‎ دست‌نخورده و دوطرفه است.  @note    [EN] Wiring: STM32 PA9 (TX) -&gt; ESP RX, STM32 PA10 (RX) &lt;- ESP TX, common GND. STM32 PA8 drives ESP CH_PD/EN; this sketch never touches that line. Wi-Fi AP "ChangeOver-ESP", password "123456789", panel at http://192.168.4.1 No cloud: only MCU &lt;-&gt; ESP data exchange (flash is used only for the bench log file). Manual test mode (ID 19): a GET_PARAMS keepalive is sent every 1 s while manual mode is active (TLM flag b5 or param 19), also with a background tab (spec 5.2). Safety: if no browser has polled /t for 10 s (or none since the ESP booted), the ESP sends ID 19 = 0 every 1 s until the STM32 reports manual off, so a closed panel never leaves a channel on an unregulated duty; the STM32 3 s dead-man still covers an ESP hang or a broken link. [FA] سیم‌بندی: PA9 به RX ماژول، PA10 به TX ماژول، زمین مشترک. پایه ‎CH_PD/EN‎ را STM32 (PA8) کنترل می‌کند؛ این برنامه به آن دست نمی‌زند. وای‌فای "‎ChangeOver-ESP‎" با رمز "123456789"، پنل در http://192.168.4.1 بدون اینترنت: فقط تبادل داده بین MCU و ESP (فلش فقط برای فایل ثبت بنچ استفاده می‌شود). مود تست دستی (شناسه 19): تا وقتی مود دستی فعال است (پرچم b5 یا پارامتر 19) هر 1 ثانیه یک GET_PARAMS فرستاده می‌شود، حتی با تب پس‌زمینه (بخش 5.2 سند). ایمنی: اگر 10 ثانیه هیچ مرورگری /t را نخواند (یا از بوت ESP هنوز نخوانده باشد)، ESP هر 1 ثانیه شناسهٔ 19 = 0 را می‌فرستد تا STM32 خاموشی مود دستی را گزارش کند؛ پس پنل بسته هرگز کانال را روی duty بدون تنظیم رها نمی‌کند. هنگ ESP یا قطع لینک را ‎dead-man‎ سه‌ثانیه‌ای STM32 پوشش می‌دهد.</t>
+          <t>پل ‎ESP-Link‎ سمت ESP: تبادل فریم باینری با STM32 روی UART (921600 8N1، مطابق ESP_AGENT_SPEC.md نسخهٔ 1.4) و یک پنل وب دارک راست‌به‌چپ با فونت وزیرمتن و «دو» تب (کارت duty دستی از 1.10 در تب پنل؛ سقف duty، نمونه‌های نمودار، حذف صبر و مقسم پک هم در 1.10): 1) پنل: ولتاژهای مشترک (با کالیبراسیون آفست از مولتی‌متر)، فیلتر جریان (median 1..15، میانگین 1..300) و یک ستون برای هر شارژر: وضعیت زنده، زنجیرهٔ اندازه‌گیری با فرمول زنده، نمودار فیلتر و دکمهٔ قطع شارژر. 2) داده‌برداری بنچ (بخش ‎5.6): SOLO1/SOLO2/BOTH‎ با فهرست duty دلخواه و جلو رفتن فقط با دکمهٔ کاربر. اصلاح 1.7 (دستور کاربر 2026-09-25): پنجرهٔ آمار با باز شدن فرم مولتی‌متر صفر می‌شود و «همان لحظهٔ زدن ثبت» خوانده می‌شود تا ردیف CSV با عددهای واردشده هم‌لحظه باشد، نه یک پنجرهٔ کهنه؛ ستون sample_ms مدت واقعی همان پنجره است. یک ردیف 89ستونی برای هر مرحله در LittleFS به نام /benchlog.csv، دانلود با ‎GET /benchlog‎. اضافات نسخهٔ 1.6 (کارت CAL، تست‌های دستی ‎B/C/D‎، تب اصلاح/تحلیل، حالت مهندس) حذف شدند؛ هیچ کالیبراسیونی خودکار اعمال نمی‌شود و پروتکل سیمی (‎SET/GET/TLM)‎ دست‌نخورده و دوطرفه است.  @note    [EN] Wiring: STM32 PA9 (TX) -&gt; ESP RX, STM32 PA10 (RX) &lt;- ESP TX, common GND. STM32 PA8 drives ESP CH_PD/EN; this sketch never touches that line. Wi-Fi AP "ChangeOver-ESP", password "123456789", panel at http://192.168.4.1 No cloud: only MCU &lt;-&gt; ESP data exchange (flash is used only for the bench log file). Manual test mode (ID 19): a GET_PARAMS keepalive is sent every 1 s while manual mode is active (TLM flag b5 or param 19), also with a background tab (spec 5.2). Safety: if no browser has polled /t for 10 s (or none since the ESP booted), the ESP sends ID 19 = 0 every 1 s until the STM32 reports manual off, so a closed panel never leaves a channel on an unregulated duty; the STM32 3 s dead-man still covers an ESP hang or a broken link. [FA] سیم‌بندی: PA9 به RX ماژول، PA10 به TX ماژول، زمین مشترک. پایه ‎CH_PD/EN‎ را STM32 (PA8) کنترل می‌کند؛ این برنامه به آن دست نمی‌زند. وای‌فای "‎ChangeOver-ESP‎" با رمز "123456789"، پنل در http://192.168.4.1 بدون اینترنت: فقط تبادل داده بین MCU و ESP (فلش فقط برای فایل ثبت بنچ استفاده می‌شود). مود تست دستی (شناسه 19): تا وقتی مود دستی فعال است (پرچم b5 یا پارامتر 19) هر 1 ثانیه یک GET_PARAMS فرستاده می‌شود، حتی با تب پس‌زمینه (بخش 19 سند). ایمنی: اگر 10 ثانیه هیچ مرورگری /t را نخواند (یا از بوت ESP هنوز نخوانده باشد)، ESP هر 1 ثانیه شناسهٔ 19 = 0 را می‌فرستد تا STM32 خاموشی مود دستی را گزارش کند؛ پس پنل بسته هرگز کانال را روی duty بدون تنظیم رها نمی‌کند. هنگ ESP یا قطع لینک را ‎dead-man‎ سه‌ثانیه‌ای STM32 پوشش می‌دهد.</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4646,7 +4646,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_CurrentCountsToMa</t>
+          <t>func__BspMeasurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4661,19 +4661,19 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>731</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>مبدل عمومی قدیمی که دقیقاً همان تابع کانال 2 است، چون از جفت کالیبراسیون کانال 2 استفاده می‌کند. فقط برای این نگه داشته شده که فراخوان‌های قدیمی لینک شوند؛ کد جدید باید تابع پر-کانال را بردارد (دستور کاربر 2026-09-20: شارژر 1 دیگر روی کالیبراسیون شارژر 2 سوار نیست).</t>
+          <t>زنجیرهٔ فقط-سخت‌افزاری (مرجع + مقسم ‎R41/R42‎ + گین تقویت‌کننده، بدون آفست و اصلاح) از شمارش خام جریان به ولتاژ شانت بر حسب uV - دیاگ زندهٔ بررسی زنجیرهٔ جریان، دستور کاربر 2026-09-22.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_CurrentCountsToShuntUv</t>
+          <t>func__BspMeasurement_GetCurrentGainPermille</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -4688,19 +4688,19 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>694</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فقط-سخت‌افزاری (مرجع + مقسم ‎R41/R42‎ + گین تقویت‌کننده، بدون آفست و اصلاح) از شمارش خام جریان به ولتاژ شانت بر حسب uV - دیاگ زندهٔ بررسی زنجیرهٔ جریان، دستور کاربر 2026-09-22.</t>
+          <t>ضریب گین بنچ زندهٔ یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_GetCurrentGainPermille</t>
+          <t>func__BspMeasurement_GetCurrentOffsetCounts</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -4715,19 +4715,19 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>678</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>ضریب گین بنچ زندهٔ یک کانال.</t>
+          <t>آفست جریان صفر زندهٔ یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_GetCurrentOffsetCounts</t>
+          <t>func__BspMeasurement_ScaleRoundMa</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -4737,24 +4737,24 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>485</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>آفست جریان صفر زندهٔ یک کانال.</t>
+          <t>رُند(صورت ‎x 24200 / 27573000)‎ با یک رُند و بدون تقسیم 64بیتی.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_ScaleRoundMa</t>
+          <t>func__BspMeasurement_SetCurrentGainPermille</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4764,24 +4764,24 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>رُند(صورت ‎x 24200 / 27573000)‎ با یک رُند و بدون تقسیم 64بیتی.</t>
+          <t>ضریب گین بنچ یک کانال در زمان اجرا، گیرهٔ 100..3000؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_SetCurrentGainPermille</t>
+          <t>func__BspMeasurement_SetCurrentOffsetCounts</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4796,19 +4796,19 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>613</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>ضریب گین بنچ یک کانال در زمان اجرا، گیرهٔ 100..3000؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
+          <t>آفست جریان صفر یک کانال در زمان اجرا، گیرهٔ 0..255؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_SetCurrentOffsetCounts</t>
+          <t>func__BspMeasurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4823,19 +4823,19 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>387</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>آفست جریان صفر یک کانال در زمان اجرا، گیرهٔ 0..255؛ روی فلش می‌ماند (NVM نسخهٔ 1.14)، پنل ESP (دستور کاربر 2026-09-22).</t>
+          <t>کانال استاندارد 12 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_V12CountsToMv</t>
+          <t>func__BspMeasurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4850,19 +4850,19 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
+          <t>کانال استاندارد 24 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_V24CountsToMv</t>
+          <t>func__BspMeasurement_VddaMv</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4877,46 +4877,46 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را به ولتاژ منبع تبدیل می‌کند.</t>
+          <t>مرجع واقعی ADC یعنی VDDA را از کانال داخلی 1٫20 ولتی VREFINT اندازه می‌گیرد: چون ولتاژ VREFINT معلوم است، شمارشی که تولید می‌کند می‌گوید مقیاس کامل چقدر می‌ارزد. مقدار مرجع از بیرون داده می‌شود تا این لایهٔ برد به هدرهای کالیبراسیون بنچ وابسته نشود. اگر نتیجه بیرون از چیزی باشد که یک ریل 3٫3 ولت فیزیکاً می‌تواند باشد، صفر برمی‌گردد تا کانال گیرکرده یا فعال‌نشده هرگز بی‌صدا همهٔ خوانش‌های محصول را بازمقیاس نکند.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_VddaMv</t>
+          <t>func__BspPwm_GetCompareCounts</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_measurement.c</t>
+          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_measurement.h</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>347</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>مرجع واقعی ADC یعنی VDDA را از کانال داخلی 1٫20 ولتی VREFINT اندازه می‌گیرد: چون ولتاژ VREFINT معلوم است، شمارشی که تولید می‌کند می‌گوید مقیاس کامل چقدر می‌ارزد. مقدار مرجع از بیرون داده می‌شود تا این لایهٔ برد به هدرهای کالیبراسیون بنچ وابسته نشود. اگر نتیجه بیرون از چیزی باشد که یک ریل 3٫3 ولت فیزیکاً می‌تواند باشد، صفر برمی‌گردد تا کانال گیرکرده یا فعال‌نشده هرگز بی‌صدا همهٔ خوانش‌های محصول را بازمقیاس نکند.</t>
+          <t>مقدار زندهٔ compare ی CH1 (پهنای ON گیت) بر حسب تیک تایمر. پورت ADC برد با آن تریگر وسط ON را روی پالس‌های کوتاه (compare 1..7) رد می‌کند: دهانهٔ ADC (625ns) پهن‌تر از چنان پنجره‌ای است، پس نمونهٔ سنکرون آشغال می‌شود و جایگزین اسکن غیرهمزمان مقدار درست است.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_GetCompareCounts</t>
+          <t>func__BspPwm_GetTimer</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4926,24 +4926,24 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ compare ی CH1 (پهنای ON گیت) بر حسب تیک تایمر. پورت ADC برد با آن تریگر وسط ON را روی پالس‌های کوتاه (compare 1..7) رد می‌کند: دهانهٔ ADC (625ns) پهن‌تر از چنان پنجره‌ای است، پس نمونهٔ سنکرون آشغال می‌شود و جایگزین اسکن غیرهمزمان مقدار درست است.</t>
+          <t>کانال منطقی را به تایمر و کانال فیزیکی برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_GetTimer</t>
+          <t>func__BspPwm_Init</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4953,24 +4953,24 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>کانال منطقی را به تایمر و کانال فیزیکی برد تبدیل می‌کند.</t>
+          <t>هر دو کانال تایمر را یک‌بار شروع می‌کند و گیت‌ها ابتدا پایین‌اند. شمارنده‌ها همیشه می‌چرخند و «خاموش» یعنی ‎compare=0‎. فاز سوئیچ کامپایل است (BSP_PWM_TIM3_PHASE_OFFSET_IN_PHASE): 1u = هم‌فاز (آزمایش میز از 2026-09-24، دستور کاربر)، 0u = درهم‌گذاری نیم‌دورهٔ ثابت (10µs در 50kHz) طرح تولید. /</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_Init</t>
+          <t>func__BspPwm_InitSamplingPulse</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4980,24 +4980,24 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>هر دو کانال تایمر را یک‌بار شروع می‌کند و گیت‌ها ابتدا پایین‌اند. شمارنده‌ها همیشه می‌چرخند و «خاموش» یعنی ‎compare=0‎. فاز سوئیچ کامپایل است (BSP_PWM_TIM3_PHASE_OFFSET_IN_PHASE): 1u = هم‌فاز (آزمایش میز از 2026-09-24، دستور کاربر)، 0u = درهم‌گذاری نیم‌دورهٔ ثابت (10µs در 50kHz) طرح تولید. /</t>
+          <t>کانال داخلی CH2 یک تایمر شارژر را به‌عنوان تریگر نمونه‌برداری سنکرون تنظیم می‌کند: PWM mode 2، قطبیت high، compare صفر در بوت. مرحلهٔ خروجی فعال می‌شود تا OC2 داخلی به مالتی‌پلکس تریگر ADC برسد، اما پایه‌های ‎CH2 (PA1/PA7)‎ آنالوگ می‌مانند. باید قبل از استارت تایمرها و وقتی شمارنده متوقف است اجرا شود.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_InitSamplingPulse</t>
+          <t>func__BspPwm_IsGatePulsing</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -5007,24 +5007,24 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>کانال داخلی CH2 یک تایمر شارژر را به‌عنوان تریگر نمونه‌برداری سنکرون تنظیم می‌کند: PWM mode 2، قطبیت high، compare صفر در بوت. مرحلهٔ خروجی فعال می‌شود تا OC2 داخلی به مالتی‌پلکس تریگر ADC برسد، اما پایه‌های ‎CH2 (PA1/PA7)‎ آنالوگ می‌مانند. باید قبل از استارت تایمرها و وقتی شمارنده متوقف است اجرا شود.</t>
+          <t>وقتی گیت شارژر منطقی پالس می‌زند true است (‎compare &gt; 0)‎. پورت ADC برد با آن می‌داند لبهٔ تریگر سنکرونِ وسط ON می‌آید یا نه؛ گیت پارک‌شده یعنی جریان اولیه صفر است.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_IsGatePulsing</t>
+          <t>func__BspPwm_SetDutyPermille</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -5039,19 +5039,19 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>وقتی گیت شارژر منطقی پالس می‌زند true است (‎compare &gt; 0)‎. پورت ADC برد با آن می‌داند لبهٔ تریگر سنکرونِ وسط ON می‌آید یا نه؛ گیت پارک‌شده یعنی جریان اولیه صفر است.</t>
+          <t>وظیفهٔ یک شارژر را در بازهٔ 0 تا 1000 پرمیل تنظیم می‌کند. مقدار بالاتر از 1000 محدود و صفر باعث توقف خروجی می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_SetDutyPermille</t>
+          <t>func__BspPwm_SetOneDuty</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -5061,24 +5061,24 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>وظیفهٔ یک شارژر را در بازهٔ 0 تا 1000 پرمیل تنظیم می‌کند. مقدار بالاتر از 1000 محدود و صفر باعث توقف خروجی می‌شود.</t>
+          <t>وظیفهٔ محدودشدهٔ یک کانال را فقط به‌صورت compare اعمال می‌کند - شمارنده دست نمی‌خورد (هر دو از Init پیوسته با آفست نیم‌دوره می‌چرخند). ‎permille=0‎ یعنی compare صفر و گیت پایین. تریگر داخلی CH2 هم در همین فراخوانی به وسط پنجرهٔ ON جدید می‌رود (‎CCR2 = CCR1/2)‎.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_SetOneDuty</t>
+          <t>func__BspPwm_StopAll</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5088,51 +5088,51 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>وظیفهٔ محدودشدهٔ یک کانال را فقط به‌صورت compare اعمال می‌کند - شمارنده دست نمی‌خورد (هر دو از Init پیوسته با آفست نیم‌دوره می‌چرخند). ‎permille=0‎ یعنی compare صفر و گیت پایین. تریگر داخلی CH2 هم در همین فراخوانی به وسط پنجرهٔ ON جدید می‌رود (‎CCR2 = CCR1/2)‎.</t>
+          <t>هر دو گیت را پایین می‌آورد (compare صفر)؛ شمارنده‌ها به چرخش می‌مانند تا آفست درهم‌گذاری حفظ شود. تریگرهای داخلی CH2 هم پارک می‌شوند (بدون لبهٔ وسط ON). /</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>func__BspPwm_StopAll</t>
+          <t>func__BspUart_Init</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_pwm.c</t>
+          <t>Firmware/Bsp/Src/bsp_uart.c</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_pwm.h</t>
+          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>هر دو گیت را پایین می‌آورد (compare صفر)؛ شمارنده‌ها به چرخش می‌مانند تا آفست درهم‌گذاری حفظ شود. تریگرهای داخلی CH2 هم پارک می‌شوند (بدون لبهٔ وسط ON). /</t>
+          <t>backend UART مقداردهی‌شدهٔ برد را برای ‎ESP-Link‎ انتخاب می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_Init</t>
+          <t>func__BspUart_PumpTx</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -5142,24 +5142,24 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>backend UART مقداردهی‌شدهٔ برد را برای ‎ESP-Link‎ انتخاب می‌کند. /</t>
+          <t>قطعهٔ پیوستهٔ بعدی حلقهٔ TX را داخل موتور DMA می‌برد؛ از زمینهٔ تسک و از کال‌بک DMA امن است (گارد TxDmaActive)؛ اگر HAL رد کند، داده در حلقه می‌ماند و پمپ بعدی دوباره می‌کوشد. /</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_PumpTx</t>
+          <t>func__BspUart_ReadByte</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5169,24 +5169,24 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>414</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>قطعهٔ پیوستهٔ بعدی حلقهٔ TX را داخل موتور DMA می‌برد؛ از زمینهٔ تسک و از کال‌بک DMA امن است (گارد TxDmaActive)؛ اگر HAL رد کند، داده در حلقه می‌ماند و پمپ بعدی دوباره می‌کوشد. /</t>
+          <t>یک بایت دریافتی ‎ESP-Link‎ را بدون بلوکه‌کردن poll می‌کند؛ بایت از بافر حلقوی RX که DMA پر کرده می‌آید (سخت‌افزار نوشته، CPU فقط آن را بیرون کپی می‌کند).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_ReadByte</t>
+          <t>func__BspUart_Write</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5201,46 +5201,46 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>یک بایت دریافتی ‎ESP-Link‎ را بدون بلوکه‌کردن poll می‌کند؛ بایت از بافر حلقوی RX که DMA پر کرده می‌آید (سخت‌افزار نوشته، CPU فقط آن را بیرون کپی می‌کند).</t>
+          <t>یک بافر بایت را در UART منطقی ‎ESP-Link‎ صف می‌کند (غیربلوکه).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>func__BspUart_Write</t>
+          <t>func__CalLut_Active</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Src/bsp_uart.c</t>
+          <t>Firmware/Modules/CalLut/cal_lut.c</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Bsp/Inc/bsp_uart.h</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>375</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>یک بافر بایت را در UART منطقی ‎ESP-Link‎ صف می‌کند (غیربلوکه).</t>
+          <t>آیا برای این کانال جدول فلش فعال است؟ /</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Active</t>
+          <t>func__CalLut_ActiveCrc32</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5255,19 +5255,19 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>424</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>آیا برای این کانال جدول فلش فعال است؟ /</t>
+          <t>CRC32 رکورد فعلی فلش (0 اگر نباشد). /</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ActiveCrc32</t>
+          <t>func__CalLut_ChannelCheck</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -5277,24 +5277,24 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>CRC32 رکورد فعلی فلش (0 اگر نباشد). /</t>
+          <t>قانونی‌بودن محورهای یک کانال: 0 نقطه یعنی «جایگزین نشده» و مجاز است؛ در کامیت عمداً override فلش قبلی همان کانال را حذف می‌کند. وگرنه 2..سقف نقطه، محور زنجیرهٔ اکیداً صعودی و محور جریان بدون افت (تفریق بدون‌علامت در درون‌یابی، افت را به ~4e9 می‌پیچاند). /</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ChannelCheck</t>
+          <t>func__CalLut_Commit</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5304,24 +5304,24 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>567</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>قانونی‌بودن محورهای یک کانال: 0 نقطه یعنی «جایگزین نشده» و مجاز است؛ در کامیت عمداً override فلش قبلی همان کانال را حذف می‌کند. وگرنه 2..سقف نقطه، محور زنجیرهٔ اکیداً صعودی و محور توان بدون افت (تفریق بدون‌علامت در درون‌یابی، افت را به ~4e9 می‌پیچاند). /</t>
+          <t>اعتبارسنجی و نوشتن جدول چیده‌شده. در موفقیت، نسخهٔ RAM از «خود فلش» دوباره خوانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Commit</t>
+          <t>func__CalLut_Crc32</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5336,19 +5336,19 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>اعتبارسنجی و نوشتن جدول چیده‌شده. در موفقیت، نسخهٔ RAM از «خود فلش» دوباره خوانده می‌شود.</t>
+          <t>CRC32 بازتابیده یک بلوک بایت، بیت‌به‌بیت (بدون جدول در فلش). /</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Crc32</t>
+          <t>func__CalLut_Crc32Byte</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5358,24 +5358,24 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>CRC32 بازتابیده (استاندارد zip) که جاوااسکریپت پنل هم دارد. /</t>
+          <t>افزودن یک بایت به CRC32 در حال اجرا. جدا شد تا جدول چیده‌شده «جریانی» CRC شود: پشتهٔ تسک ارتباط 1KB است و بافر 386 بایتی روی آن دقیقاً همان سرریز بی‌صدایی است که هیچ‌چیز گزارشش نمی‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Crc32Byte</t>
+          <t>func__CalLut_Index</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -5390,19 +5390,19 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>362</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>افزودن یک بایت به CRC32 در حال اجرا. جدا شد تا جدول چیده‌شده «جریانی» CRC شود: پشتهٔ تسک ارتباط 1KB است و بافر 386 بایتی روی آن دقیقاً همان سرریز بی‌صدایی است که هیچ‌چیز گزارشش نمی‌کند. /</t>
+          <t>تبدیل شمارهٔ کانال به اندیس آرایه. /</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Index</t>
+          <t>func__CalLut_Init</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -5412,24 +5412,24 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>تبدیل شمارهٔ کانال به اندیس آرایه. /</t>
+          <t>بارگذاری بوت (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Init</t>
+          <t>func__CalLut_Points</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -5444,19 +5444,19 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>بارگذاری بوت (قرارداد هدر). /</t>
+          <t>تعداد نقاط / محور شمارش / محور mA کانال فعال. /</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Points</t>
+          <t>func__CalLut_RecordValidate</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -5471,19 +5471,19 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>201</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>تعداد نقاط / محور شمارش / محور mA کانال فعال. /</t>
+          <t>اعتبارسنجی رکورد نامزد (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_RecordValidate</t>
+          <t>func__CalLut_RequestReset</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -5498,19 +5498,19 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>اعتبارسنجی رکورد نامزد (قرارداد هدر). /</t>
+          <t>مسلح‌کردن ریست بعد از دست‌دادن: ریست داخل هندلر لینک گرفته نمی‌شود؛ فریم تمام می‌شود، شارژر بیکار می‌شود و چند اجرا بعد func__CalLut_Tick() ماشه را می‌کشد. /</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_RequestReset</t>
+          <t>func__CalLut_ResumeCharger</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -5520,24 +5520,24 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>555</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>مسلح‌کردن ریست بعد از دست‌دادن: ریست داخل هندلر لینک گرفته نمی‌شود؛ فریم تمام می‌شود، شارژر بیکار می‌شود و چند اجرا بعد func__CalLut_Tick() ماشه را می‌کشد. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_ResumeCharger</t>
+          <t>func__CalLut_SeqCompare</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -5552,19 +5552,19 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقایسهٔ ترتیب با در نظر گرفتن چرخش شمارنده. /</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_SeqCompare</t>
+          <t>func__CalLut_StageBegin</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -5574,24 +5574,24 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>433</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>مقایسهٔ ترتیب با در نظر گرفتن چرخش شمارنده. /</t>
+          <t>شروع چیدن جدول جدید؛ جدول «فعال» تا موفقیت کامیت سر کار می‌ماند، پس ارسال نیمه‌کاره هیچ‌چیز را خراب نمی‌کند. تعداد صفر مجاز است و کامیت موفق override فلش قبلی همان کانال را حذف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_StageBegin</t>
+          <t>func__CalLut_StagePoint</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -5606,19 +5606,19 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>شروع چیدن جدول جدید؛ جدول «فعال» تا موفقیت کامیت سر کار می‌ماند، پس ارسال نیمه‌کاره هیچ‌چیز را خراب نمی‌کند. تعداد صفر مجاز است و کامیت موفق override فلش قبلی همان کانال را حذف می‌کند.</t>
+          <t>ذخیرهٔ یک نقطه در ناحیهٔ چیدن. /</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_StagePoint</t>
+          <t>func__CalLut_SuspendCharger</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -5628,24 +5628,24 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>ذخیرهٔ یک نقطه در ناحیهٔ چیدن. /</t>
+          <t>بیکارکردن شارژر دور استال فلش (همان قانون NVM پارامترها). /</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_SuspendCharger</t>
+          <t>func__CalLut_Tick</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -5655,51 +5655,51 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/CalLut/cal_lut.h</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>بیکارکردن شارژر دور استال فلش (همان قانون NVM پارامترها). /</t>
+          <t>نگهداری تسک ارتباط: ریست مسلح‌شده را انجام می‌دهد. /</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>func__CalLut_Tick</t>
+          <t>func__Changeover_Evaluate</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.c</t>
+          <t>Firmware/Modules/Changeover/changeover.c</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/CalLut/cal_lut.h</t>
+          <t>Firmware/Modules/Changeover/changeover.h</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط: ریست مسلح‌شده را انجام می‌دهد. /</t>
+          <t>حالت بعدی سیستم را از نمونه و خطا حساب می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>func__Changeover_Evaluate</t>
+          <t>func__Changeover_Init</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -5714,46 +5714,46 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>حالت بعدی سیستم را از نمونه و خطا حساب می‌کند.</t>
+          <t>از حالت BOOT شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>func__Changeover_Init</t>
+          <t>func__Charger_ActiveCurrentLimitMa</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.c</t>
+          <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Changeover/changeover.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>513</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>از حالت BOOT شروع می‌کند. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ActiveCurrentLimitMa</t>
+          <t>func__Charger_ApplyDuty</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>531</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ApplyDuty</t>
+          <t>func__Charger_BatteryVoltageIsValid</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BatteryVoltageIsValid</t>
+          <t>func__Charger_BringupRegulateChannel</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>843</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -5834,7 +5834,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BringupRegulateChannel</t>
+          <t>func__Charger_BulkStartSettled</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -5849,19 +5849,19 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>فقط وقتی اتصال به‌طور پیوسته حداقل 15 ثانیه معتبر دیده شده اجازهٔ شروع بالک می‌دهد (دستور کاربر: اول ثبات، بعد شارژ).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_BulkStartSettled</t>
+          <t>func__Charger_CaptureDiag</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -5876,19 +5876,19 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>فقط وقتی اتصال به‌طور پیوسته حداقل 15 ثانیه معتبر دیده شده اجازهٔ شروع بالک می‌دهد (دستور کاربر: اول ثبات، بعد شارژ).</t>
+          <t>آرایهٔ دیاگ زنده و آرایهٔ برگهٔ کالیبراسیون را با همهٔ مقادیر تصمیم به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_CaptureDiag</t>
+          <t>func__Charger_ChannelCurrentMa</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>آرایهٔ دیاگ زنده و آرایهٔ برگهٔ کالیبراسیون را با همهٔ مقادیر تصمیم به‌روز می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ChannelCurrentMa</t>
+          <t>func__Charger_ChannelVoltageMv</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -5942,7 +5942,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ChannelVoltageMv</t>
+          <t>func__Charger_ClampAlarms</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampAlarms</t>
+          <t>func__Charger_ClampPid</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampPid</t>
+          <t>func__Charger_ClampProfile</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6023,7 +6023,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClampProfile</t>
+          <t>func__Charger_ClearAbsorbWindow</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -6038,19 +6038,19 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پاک‌کردن دفترچهٔ پنجرهٔ ابزورب یک کانال (شمارندهٔ شستشو، مهر تیپر و دو مهر پنجره). هر مسیر ری‌استارت/ورود مجدد این را صدا می‌زند تا شستشوی 10 دقیقه همیشه از صفر شروع شود؛ مسیر ورود به ABSORB به‌جای صفر، مهر «اکنون» می‌زند و جدا می‌ماند.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ClearAbsorbWindow</t>
+          <t>func__Charger_DeadBatteryTick</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -6065,19 +6065,19 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>پاک‌کردن دفترچهٔ پنجرهٔ ابزورب یک کانال (شمارندهٔ شستشو، مهر تیپر و دو مهر پنجره). هر مسیر ری‌استارت/ورود مجدد این را صدا می‌زند تا شستشوی 10 دقیقه همیشه از صفر شروع شود؛ مسیر ورود به ABSORB به‌جای صفر، مهر «اکنون» می‌زند و جدا می‌ماند.</t>
+          <t>یک پاس سناریوی 6 برای یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBatteryTick</t>
+          <t>func__Charger_DeadBeepPattern</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -6087,24 +6087,24 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>یک پاس سناریوی 6 برای یک کانال.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBeepPattern</t>
+          <t>func__Charger_DeadBlocksOutput</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -6119,19 +6119,19 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آیا قفلِ باتری خراب باید خروجی را هم ببندد.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadBlocksOutput</t>
+          <t>func__Charger_DeadElapsedSeconds</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -6146,19 +6146,19 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>آیا قفلِ باتری خراب باید خروجی را هم ببندد.</t>
+          <t>زمان شارژ پیوستهٔ همین کانال بر حسب ثانیه. شمارش از ابتدا هم جداگانه بود، ولی فقط بزرگ‌ترین مقدار از برد بیرون می‌رفت؛ حالا هر کانال جدا گزارش می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadElapsedSeconds</t>
+          <t>func__Charger_DeadFaceShape</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -6173,19 +6173,19 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>زمان شارژ پیوستهٔ همین کانال بر حسب ثانیه. شمارش از ابتدا هم جداگانه بود، ولی فقط بزرگ‌ترین مقدار از برد بیرون می‌رفت؛ حالا هر کانال جدا گزارش می‌شود.</t>
+          <t>شکل چهرهٔ سناریوی 6 را به ماژول UI می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadFaceShape</t>
+          <t>func__Charger_DeadMask</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -6200,19 +6200,19 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>شکل چهرهٔ سناریوی 6 را به ماژول UI می‌دهد.</t>
+          <t>قضاوت قفل‌شده: بیت 0 شارژر 1، بیت 1 شارژر 2.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadMask</t>
+          <t>func__Charger_DeadTakePersistFlag</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
@@ -6227,19 +6227,19 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>قضاوت قفل‌شده: بیت 0 شارژر 1، بیت 1 شارژر 2.</t>
+          <t>پرچم «قضاوت ماندگار عوض شد» را می‌گیرد و پاک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadTakePersistFlag</t>
+          <t>func__Charger_DeadlineElapsed</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -6249,24 +6249,24 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>621</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>پرچم «قضاوت ماندگار عوض شد» را می‌گیرد و پاک می‌کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DeadlineElapsed</t>
+          <t>func__Charger_DipResetAbsorbWindow</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>362</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -6293,7 +6293,7 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DipResetAbsorbWindow</t>
+          <t>func__Charger_DurationTicks</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -6320,7 +6320,7 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_DurationTicks</t>
+          <t>func__Charger_EnterManualTestMode</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -6335,19 +6335,19 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مود تست دستی را برمی‌دارد: مهر ددمنِ لینک و پاک‌کردن بیت خطای قطع باتری تا آلارمش حین تست بنچ نیفتد (fault.c تا وقتی مود فعال است تشخیص را فریز می‌کند). درایو کانال در همان پاس Evaluate پایین‌تر انجام می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_EnterManualTestMode</t>
+          <t>func__Charger_Evaluate</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -6357,24 +6357,24 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>مود تست دستی را برمی‌دارد: مهر ددمنِ لینک و پاک‌کردن بیت خطای قطع باتری تا آلارمش حین تست بنچ نیفتد (fault.c تا وقتی مود فعال است تشخیص را فریز می‌کند). درایو کانال در همان پاس Evaluate پایین‌تر انجام می‌شود.</t>
+          <t>الگوریتم یکسان کنترل و حفاظت را برای هر کانال نصب‌شدهٔ 12 ولت مستقل اجرا می‌کند. ولتاژ ورودی از مقدار واقعی ADC mV بررسی می‌شود، نه فقط سیگنال دیجیتال PB4. جریان کم درخواست افزایش duty است، نه fault.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Evaluate</t>
+          <t>func__Charger_EvaluateTechnicalFault</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -6389,19 +6389,19 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>الگوریتم یکسان کنترل و حفاظت را برای هر کانال نصب‌شدهٔ 12 ولت مستقل اجرا می‌کند. ولتاژ ورودی از مقدار واقعی ADC mV بررسی می‌شود، نه فقط سیگنال دیجیتال PB4. جریان کم درخواست افزایش duty است، نه fault.</t>
+          <t>خطای فنی سناریوی 7 را از snapshot تازه و JIT اجراشده ارزیابی می‌کند؛ پس از تشخیص بیت خطا و قفل خروجی را تا ریست نگه می‌دارد. /</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_EvaluateTechnicalFault</t>
+          <t>func__Charger_ExitManualTestMode</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>خطای فنی سناریوی 7 را از snapshot تازه و JIT اجراشده ارزیابی می‌کند؛ پس از تشخیص بیت خطا و قفل خروجی را تا ریست نگه می‌دارد. /</t>
+          <t>خروج از مود تست دستی (کلید خاموش پنل یا ددمن لینک): هر دو duty صفر و هر کانال شارژر خودکار را از OFF با دفترچهٔ تمیز ری‌استارت می‌کند (ثبات اتصال دوباره اعمال می‌شود). قفل FINAL_FAULT هرگز اینجا آزاد نمی‌شود؛ لچ‌های JIT کانال‌های پارک‌شده پاک می‌شوند تا کمپریتور دوباره شلیک کند. /</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ExitManualTestMode</t>
+          <t>func__Charger_FinalDisconnect</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -6443,19 +6443,19 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>خروج از مود تست دستی (کلید خاموش پنل یا ددمن لینک): هر دو duty صفر و هر کانال شارژر خودکار را از OFF با دفترچهٔ تمیز ری‌استارت می‌کند (ثبات اتصال دوباره اعمال می‌شود). قفل FINAL_FAULT هرگز اینجا آزاد نمی‌شود؛ لچ‌های JIT کانال‌های پارک‌شده پاک می‌شوند تا کمپریتور دوباره شلیک کند. /</t>
+          <t>قطع نهایی fault: بعد از سومین JIT همان کانال، هر دو PWM قبلاً متوقف شده‌اند؛ سپس رله NC باز می‌شود تا ورودی ترانس واقعاً قطع شود. /</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_FinalDisconnect</t>
+          <t>func__Charger_FinalDisconnectIdle</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -6470,19 +6470,19 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>439</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>قطع نهایی fault: بعد از سومین JIT همان کانال، هر دو PWM قبلاً متوقف شده‌اند؛ سپس رله NC باز می‌شود تا ورودی ترانس واقعاً قطع شود. /</t>
+          <t>standby خطای نهایی وقتی ورودی قطع است: قفل خطا باقی می‌ماند ولی کویل رله رها می‌شود تا باتری را خالی نکند (~50mA). با برگشت ورودی، کویل دوباره به‌صورت خودکار وصل می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_FinalDisconnectIdle</t>
+          <t>func__Charger_GetAlarmParam</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -6492,24 +6492,24 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>standby خطای نهایی وقتی ورودی قطع است: قفل خطا باقی می‌ماند ولی کویل رله رها می‌شود تا باتری را خالی نکند (~50mA). با برگشت ورودی، کویل دوباره به‌صورت خودکار وصل می‌شود. /</t>
+          <t>خواندن یک پارامتر آلارم شارژر (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetAlarmParam</t>
+          <t>func__Charger_GetAppliedDutyPermille</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -6524,19 +6524,19 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر آلارم شارژر (لینک ESP).</t>
+          <t>duty واقعی اعمال‌شده به یک کانال را بر حسب پرمیل می‌خواند؛ آشکارساز خطای فنی باید خروجیِ رسیده به سخت‌افزار را ببیند. /</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetAppliedDutyPermille</t>
+          <t>func__Charger_GetChannelEspEnable</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -6551,19 +6551,19 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>duty واقعی اعمال‌شده به یک کانال را بر حسب پرمیل می‌خواند؛ آشکارساز خطای فنی باید خروجیِ رسیده به سخت‌افزار را ببیند. /</t>
+          <t>گیت فعال‌سازی ESP یک کانال شارژر را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetChannelEspEnable</t>
+          <t>func__Charger_GetDeadParam</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -6578,19 +6578,19 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>گیت فعال‌سازی ESP یک کانال شارژر را می‌خواند.</t>
+          <t>خواندن پارامتر سناریوی 6 یا اسلات قضاوت.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDeadParam</t>
+          <t>func__Charger_GetDutyCeilingPermille</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>خواندن پارامتر سناریوی 6 یا اسلات قضاوت.</t>
+          <t>سقف زندهٔ duty ی PWM یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyCeilingPermille</t>
+          <t>func__Charger_GetDutyFixedEnable</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -6632,19 +6632,19 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>سقف زندهٔ duty ی PWM یک کانال.</t>
+          <t>کلید مود duty فیکس یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyFixedEnable</t>
+          <t>func__Charger_GetDutyFixedPermille</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -6659,19 +6659,19 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>کلید مود duty فیکس یک کانال.</t>
+          <t>مقدار ذخیره‌شدهٔ duty فیکس یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetDutyFixedPermille</t>
+          <t>func__Charger_GetLimitParam</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -6686,19 +6686,19 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>مقدار ذخیره‌شدهٔ duty فیکس یک کانال.</t>
+          <t>خواندن یک حد یا گین پشتیبان شارژر (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetLimitParam</t>
+          <t>func__Charger_GetManualTestMode</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -6713,19 +6713,19 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک حد یا گین پشتیبان شارژر (لینک ESP).</t>
+          <t>پرچم «درخواست‌شدهٔ» مود دستی (مقدار پارامتری که پنل نوشته؛ حداکثر یک دورهٔ کنترل با وضعیت فعال اختلاف دارد).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetManualTestMode</t>
+          <t>func__Charger_GetPidParam</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -6740,19 +6740,19 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>پرچم «درخواست‌شدهٔ» مود دستی (مقدار پارامتری که پنل نوشته؛ حداکثر یک دورهٔ کنترل با وضعیت فعال اختلاف دارد).</t>
+          <t>خواندن یک پارامتر PID دوحلقه‌ای (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetPidParam</t>
+          <t>func__Charger_GetProfileParam</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -6767,19 +6767,19 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر PID دوحلقه‌ای (لینک ESP).</t>
+          <t>خواندن یک پارامتر پروفایل شارژ (لینک ESP).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_GetProfileParam</t>
+          <t>func__Charger_HandleJitTrip</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -6789,24 +6789,24 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک پارامتر پروفایل شارژ (لینک ESP).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_HandleJitTrip</t>
+          <t>func__Charger_Init</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -6816,24 +6816,24 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>state سیاست را مقداردهی اولیه می‌کند، همه PWMها را متوقف و وضعیت ‎safe-idle‎ قطعی را اعمال می‌کند. با ‎CHG_MASTER_ENABLE=0‎ این تنها رفتار فعال باقی می‌ماند. /</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Init</t>
+          <t>func__Charger_IsAnyChannelActive</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -6848,19 +6848,19 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>state سیاست را مقداردهی اولیه می‌کند، همه PWMها را متوقف و وضعیت ‎safe-idle‎ قطعی را اعمال می‌کند. با ‎CHG_MASTER_ENABLE=0‎ این تنها رفتار فعال باقی می‌ماند. /</t>
+          <t>true وقتی دست‌کم یک کانال نصب‌شده واقعاً در حال شارژ است (بالک/ابزورب؛ فلوت پارک‌شده یعنی کار تمام شده و فعال حساب نمی‌شود - چهرهٔ فول با IsChargeComplete می‌آید و آشکارساز قطع باتری هم آنجا مسلح نیست).</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsAnyChannelActive</t>
+          <t>func__Charger_IsChannelActive</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -6875,19 +6875,19 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>true وقتی دست‌کم یک کانال نصب‌شده واقعاً در حال شارژ است (بالک/ابزورب؛ فلوت پارک‌شده یعنی کار تمام شده و فعال حساب نمی‌شود - چهرهٔ فول با IsChargeComplete می‌آید و آشکارساز قطع باتری هم آنجا مسلح نیست).</t>
+          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelActive</t>
+          <t>func__Charger_IsChannelInstalled</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -6897,24 +6897,24 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelInstalled</t>
+          <t>func__Charger_IsChargeComplete</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -6924,24 +6924,24 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChargeComplete</t>
+          <t>func__Charger_IsManualTestModeActive</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -6956,19 +6956,19 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
+          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsManualTestModeActive</t>
+          <t>func__Charger_IsRelayOpen</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -6983,19 +6983,19 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
+          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsRelayOpen</t>
+          <t>func__Charger_IsSuspended</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -7010,19 +7010,19 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
+          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsSuspended</t>
+          <t>func__Charger_IsTechnicalFaultLocked</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -7037,19 +7037,19 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
+          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsTechnicalFaultLocked</t>
+          <t>func__Charger_LatchFinalFault</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -7059,24 +7059,24 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_LatchFinalFault</t>
+          <t>func__Charger_Limit</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -7091,19 +7091,19 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Limit</t>
+          <t>func__Charger_ManualDriveChannel</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -7118,19 +7118,19 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
+          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ManualDriveChannel</t>
+          <t>func__Charger_MaxDutyPermille</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -7145,19 +7145,19 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_MaxDutyPermille</t>
+          <t>func__Charger_NotifyEspLinkActivity</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -7167,24 +7167,24 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_NotifyEspLinkActivity</t>
+          <t>func__Charger_PidCeilingMilli</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -7194,24 +7194,24 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>963</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidCeilingMilli</t>
+          <t>func__Charger_PidClampError</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>978</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -7238,7 +7238,7 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidClampError</t>
+          <t>func__Charger_PidInvalidate</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7265,7 +7265,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidInvalidate</t>
+          <t>func__Charger_PidStep</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -7280,19 +7280,19 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidStep</t>
+          <t>func__Charger_PwmChannel</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -7307,19 +7307,19 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PwmChannel</t>
+          <t>func__Charger_RegulateChannel</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -7346,7 +7346,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RegulateChannel</t>
+          <t>func__Charger_ResetChannelToOff</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>629</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -7373,7 +7373,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ResetChannelToOff</t>
+          <t>func__Charger_RetryDuty</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>733</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -7400,7 +7400,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RetryDuty</t>
+          <t>func__Charger_SafeIdle</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>370</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -7427,7 +7427,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SafeIdle</t>
+          <t>func__Charger_ServiceRetry</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>764</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ServiceRetry</t>
+          <t>func__Charger_SetAlarmParam</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -7464,24 +7464,24 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetAlarmParam</t>
+          <t>func__Charger_SetChannelEspEnable</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -7496,19 +7496,19 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
+          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetChannelEspEnable</t>
+          <t>func__Charger_SetDeadParam</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -7523,19 +7523,19 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDeadParam</t>
+          <t>func__Charger_SetDutyCeilingPermille</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -7550,19 +7550,19 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyCeilingPermille</t>
+          <t>func__Charger_SetDutyFixedEnable</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -7577,19 +7577,19 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedEnable</t>
+          <t>func__Charger_SetDutyFixedPermille</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -7604,19 +7604,19 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
+          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedPermille</t>
+          <t>func__Charger_SetLimitParam</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -7631,19 +7631,19 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetLimitParam</t>
+          <t>func__Charger_SetManualTestMode</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -7658,19 +7658,19 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
+          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetManualTestMode</t>
+          <t>func__Charger_SetPidParam</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -7685,19 +7685,19 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
+          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetPidParam</t>
+          <t>func__Charger_SetProfileParam</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -7712,19 +7712,19 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetProfileParam</t>
+          <t>func__Charger_SetSuspended</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -7739,19 +7739,19 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
+          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetSuspended</t>
+          <t>func__Charger_StopOneChannel</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -7761,51 +7761,51 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_StopOneChannel</t>
+          <t>func__EspLink_ApplyParam</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ApplyParam</t>
+          <t>func__EspLink_ConsumeLutResetAuthorization</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -7815,24 +7815,24 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ConsumeLutResetAuthorization</t>
+          <t>func__EspLink_Crc16</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -7847,19 +7847,19 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>639</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Crc16</t>
+          <t>func__EspLink_GetParam</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
@@ -7869,24 +7869,24 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>440</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
+          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetParam</t>
+          <t>func__EspLink_GetU32</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -7896,24 +7896,24 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
+          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetU32</t>
+          <t>func__EspLink_HandleFrame</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
@@ -7928,19 +7928,19 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleFrame</t>
+          <t>func__EspLink_HandleLutFrame</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -7955,19 +7955,19 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutFrame</t>
+          <t>func__EspLink_HandleLutRead</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
@@ -7982,19 +7982,19 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
+          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutRead</t>
+          <t>func__EspLink_HostTest_AcceptedFrames</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -8004,24 +8004,24 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_AcceptedFrames</t>
+          <t>func__EspLink_HostTest_CrcErrors</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_CrcErrors</t>
+          <t>func__EspLink_HostTest_FeedByte</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_FeedByte</t>
+          <t>func__EspLink_HostTest_HandleLutFrame</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_HandleLutFrame</t>
+          <t>func__EspLink_HostTest_RecordCommitAck</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -8129,7 +8129,7 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_RecordCommitAck</t>
+          <t>func__EspLink_HostTest_Reset</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_Reset</t>
+          <t>func__EspLink_HostTest_TryReset</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_TryReset</t>
+          <t>func__EspLink_HostTest_VersionErrors</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -8210,7 +8210,7 @@
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_VersionErrors</t>
+          <t>func__EspLink_Init</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -8225,46 +8225,46 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Init</t>
+          <t>func__EspLink_NvmCrc32</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
+          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmCrc32</t>
+          <t>func__EspLink_NvmFlushForReset</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -8279,19 +8279,19 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
+          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmFlushForReset</t>
+          <t>func__EspLink_NvmInit</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -8306,19 +8306,19 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
+          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmInit</t>
+          <t>func__EspLink_NvmMarkDirty</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -8333,19 +8333,19 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>425</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
+          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmMarkDirty</t>
+          <t>func__EspLink_NvmParamPersisted</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -8360,19 +8360,19 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
+          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmParamPersisted</t>
+          <t>func__EspLink_NvmRecordBuild</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -8387,19 +8387,19 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
+          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordBuild</t>
+          <t>func__EspLink_NvmRecordValidate</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -8414,19 +8414,19 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
+          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordValidate</t>
+          <t>func__EspLink_NvmResumeCharger</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
@@ -8436,24 +8436,24 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
+          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmResumeCharger</t>
+          <t>func__EspLink_NvmSaveNow</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -8468,19 +8468,19 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSaveNow</t>
+          <t>func__EspLink_NvmSeqCompare</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -8490,24 +8490,24 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSeqCompare</t>
+          <t>func__EspLink_NvmSuspendCharger</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -8517,24 +8517,24 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>480</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
+          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSuspendCharger</t>
+          <t>func__EspLink_NvmTick</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -8544,51 +8544,51 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
+          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmTick</t>
+          <t>func__EspLink_ParseByte</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
+          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ParseByte</t>
+          <t>func__EspLink_Power</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -8598,24 +8598,24 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
+          <t>پایه CH_PD را می‌زند.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Power</t>
+          <t>func__EspLink_PutU16</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -8625,24 +8625,24 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>پایه CH_PD را می‌زند.</t>
+          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU16</t>
+          <t>func__EspLink_PutU32</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -8657,19 +8657,19 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>145</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU32</t>
+          <t>func__EspLink_RecordLutCommitAck</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -8684,19 +8684,19 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_RecordLutCommitAck</t>
+          <t>func__EspLink_ResyncFromByte</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -8723,7 +8723,7 @@
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ResyncFromByte</t>
+          <t>func__EspLink_Run</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -8733,24 +8733,24 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Run</t>
+          <t>func__EspLink_SendFrame</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
@@ -8760,24 +8760,24 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>666</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
+          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendFrame</t>
+          <t>func__EspLink_SendLutAck</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
@@ -8792,19 +8792,19 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
+          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutAck</t>
+          <t>func__EspLink_SendLutData</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -8819,19 +8819,19 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
+          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutData</t>
+          <t>func__EspLink_SendParamReport</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -8846,19 +8846,19 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
+          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamReport</t>
+          <t>func__EspLink_SendParamsBulk</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -8873,19 +8873,19 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>830</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamsBulk</t>
+          <t>func__EspLink_SendTelemetry</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -8900,46 +8900,46 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>901</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendTelemetry</t>
+          <t>func__Fault_Any</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>468</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
+          <t>اگر هر بیتی روشن باشد true.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Any</t>
+          <t>func__Fault_ClampAlarms</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -8949,24 +8949,24 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>اگر هر بیتی روشن باشد true.</t>
+          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_ClampAlarms</t>
+          <t>func__Fault_Clear</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
@@ -8976,24 +8976,24 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
+          <t>بیت‌ها را پاک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Clear</t>
+          <t>func__Fault_DebounceDone</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -9003,24 +9003,24 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را پاک می‌کند.</t>
+          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_DebounceDone</t>
+          <t>func__Fault_Evaluate</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
@@ -9030,24 +9030,24 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>482</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
+          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Evaluate</t>
+          <t>func__Fault_Get</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
@@ -9062,19 +9062,19 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>456</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
+          <t>ماسک فعلی را برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Get</t>
+          <t>func__Fault_GetAlarmParam</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
@@ -9089,19 +9089,19 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>ماسک فعلی را برمی‌گرداند.</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_GetAlarmParam</t>
+          <t>func__Fault_Init</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -9116,19 +9116,19 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
+          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Init</t>
+          <t>func__Fault_OnSupervisionChange</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
@@ -9143,19 +9143,19 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
+          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_OnSupervisionChange</t>
+          <t>func__Fault_Set</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -9170,19 +9170,19 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>410</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
+          <t>بیت‌ها را قفل می‌کند (OR).</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Set</t>
+          <t>func__Fault_SetAlarmParam</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
@@ -9197,46 +9197,46 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را قفل می‌کند (OR).</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_SetAlarmParam</t>
+          <t>func__Imbalance_Evaluate</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Evaluate</t>
+          <t>func__Imbalance_GetOutputs</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -9263,7 +9263,7 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetOutputs</t>
+          <t>func__Imbalance_GetParam</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -9290,7 +9290,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetParam</t>
+          <t>func__Imbalance_Init</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -9317,7 +9317,7 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Init</t>
+          <t>func__Imbalance_ParamClamp</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -9344,7 +9344,7 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamClamp</t>
+          <t>func__Imbalance_ParamDefault</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamDefault</t>
+          <t>func__Imbalance_ReadParam</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ReadParam</t>
+          <t>func__Imbalance_SeedDefaultsOnce</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SeedDefaultsOnce</t>
+          <t>func__Imbalance_SetParam</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -9452,34 +9452,34 @@
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SetParam</t>
+          <t>func__Jitter_ChannelTripped</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ChannelTripped</t>
+          <t>func__Jitter_ClearChannel</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
@@ -9494,19 +9494,19 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
+          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ClearChannel</t>
+          <t>func__Jitter_Init</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
@@ -9521,19 +9521,19 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
+          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Init</t>
+          <t>func__Jitter_Run</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
@@ -9548,46 +9548,46 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
+          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Run</t>
+          <t>func__McuPowerPath_Init</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
+          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Init</t>
+          <t>func__McuPowerPath_OnInputIrq</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
@@ -9602,19 +9602,19 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
+          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_OnInputIrq</t>
+          <t>func__McuPowerPath_Run</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
@@ -9629,46 +9629,46 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
+          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Run</t>
+          <t>func__Measurement_ApplyCurrentFilters</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
+          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyCurrentFilters</t>
+          <t>func__Measurement_ApplyVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
@@ -9683,19 +9683,19 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>853</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
+          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyVoltageOffsetMv</t>
+          <t>func__Measurement_Battery24CountsToMv</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
@@ -9705,24 +9705,24 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
+          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Battery24CountsToMv</t>
+          <t>func__Measurement_BenchTableMa</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
@@ -9732,24 +9732,24 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
+          <t>جستجوی جدول بر حسب شمارش؛ فراخوان‌کننده برون‌یابی بالای جدول (تفاضل BSPfull از آخرین لنگر، با یک رُند) را می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_BenchTableMa</t>
+          <t>func__Measurement_CountsToMv</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
@@ -9759,24 +9759,24 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>568</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>جستجوی جدول بر حسب شمارش؛ فراخوان‌کننده برون‌یابی بالای جدول (تفاضل BSPfull از آخرین لنگر، با یک رُند) را می‌دهد.</t>
+          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CountsToMv</t>
+          <t>func__Measurement_Current1CountsToMa</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
@@ -9791,19 +9791,19 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMa</t>
+          <t>func__Measurement_Current1CountsToMaLocked</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
@@ -9813,24 +9813,24 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>شمارش کانال 1 به mA باتری 1. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMaLocked</t>
+          <t>func__Measurement_Current2CountsToMa</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
@@ -9840,24 +9840,24 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>799</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 1 به mA باتری 1. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
+          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMa</t>
+          <t>func__Measurement_Current2CountsToMaLocked</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
@@ -9867,24 +9867,24 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>765</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMaLocked</t>
+          <t>func__Measurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
@@ -9894,24 +9894,24 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>831</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
+          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToMa</t>
+          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -9926,19 +9926,19 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>807</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید هیچ تبدیل دوم دیگری اعمال کند.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToShuntUv</t>
+          <t>func__Measurement_CurrentMedian</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
@@ -9948,24 +9948,24 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
+          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
+          <t>func__Measurement_CurrentMovingAverage</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -9975,24 +9975,24 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید تبدیل دوم ‎Vin/Vbat‎ را اعمال کند، حتی اگر ETA کند.</t>
+          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMedian</t>
+          <t>func__Measurement_GetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
@@ -10002,24 +10002,24 @@
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMovingAverage</t>
+          <t>func__Measurement_GetFilterMedianSize</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -10029,24 +10029,24 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterAverageWindow</t>
+          <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
@@ -10061,19 +10061,19 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
+          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterMedianSize</t>
+          <t>func__Measurement_GetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -10088,19 +10088,19 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetSnapshot</t>
+          <t>func__Measurement_Init</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
@@ -10115,19 +10115,19 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>509</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
+          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetVoltageOffsetMv</t>
+          <t>func__Measurement_Median5</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
@@ -10137,47 +10137,51 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_HostTest_MulDivU32</t>
+          <t>func__Measurement_MedianFilterVoltageSample</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
-        </is>
-      </c>
-      <c r="D242" s="5" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>probeٔ دقیق arithmetic LUT، فقط برای تست هاست.</t>
+          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Init</t>
+          <t>func__Measurement_ResetCurrentFilters</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -10187,24 +10191,24 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>379</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
+          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Median5</t>
+          <t>func__Measurement_Run</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
@@ -10214,24 +10218,24 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>875</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_MedianFilterVoltageSample</t>
+          <t>func__Measurement_SetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -10241,24 +10245,24 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
+          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ResetCurrentFilters</t>
+          <t>func__Measurement_SetFilterMedianSize</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
@@ -10268,24 +10272,24 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
+          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Run</t>
+          <t>func__Measurement_SetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -10300,19 +10304,19 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterAverageWindow</t>
+          <t>func__Measurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
@@ -10327,19 +10331,19 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
+          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterMedianSize</t>
+          <t>func__Measurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -10354,294 +10358,294 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
+          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetVoltageOffsetMv</t>
+          <t>func__Protection_Init</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
+          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V12CountsToMv</t>
+          <t>func__Protection_Run</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V24CountsToMv</t>
+          <t>func__Rtos_DelayMilliseconds</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Init</t>
+          <t>func__Rtos_Fatal</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
+          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Run</t>
+          <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
+          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_DelayMilliseconds</t>
+          <t>func__Rtos_Start</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Rtos/Inc/rtos_app.h</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
+          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Fatal</t>
+          <t>func__Rtos_TicksToMilliseconds</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
+          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_MillisecondsToTicks</t>
+          <t>func__TaskComm</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Rtos/Src/task_comm.c</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
+          <t>تسک ‎UART/ESP‎.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Start</t>
+          <t>func__TaskControl</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Rtos/Src/task_control.c</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_app.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
+          <t>تسک Changeover و شارژر.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_TicksToMilliseconds</t>
+          <t>func__TaskMeasurement</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Rtos/Src/task_measurement.c</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
+          <t>تسک نمونه‌برداری ADC.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>func__TaskComm</t>
+          <t>func__TaskProtection</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_comm.c</t>
+          <t>Firmware/Rtos/Src/task_protection.c</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
@@ -10651,24 +10655,24 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>تسک ‎UART/ESP‎.</t>
+          <t>تسک حفاظت.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>func__TaskControl</t>
+          <t>func__TaskUi</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_control.c</t>
+          <t>Firmware/Rtos/Src/task_ui.c</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
@@ -10678,100 +10682,100 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>تسک Changeover و شارژر.</t>
+          <t>تسک LED و بازر. در این مرحله فعال است.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>func__TaskMeasurement</t>
+          <t>func__Ui_AlarmParamIndex</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_measurement.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>تسک نمونه‌برداری ADC.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>func__TaskProtection</t>
+          <t>func__Ui_BatteryVoltageToPercent</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_protection.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>تسک حفاظت.</t>
+          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>func__TaskUi</t>
+          <t>func__Ui_BeepDutyPercent</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_ui.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>تسک LED و بازر. در این مرحله فعال است.</t>
+          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_AlarmParamIndex</t>
+          <t>func__Ui_BoardTest_Start</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
@@ -10781,24 +10785,24 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BatteryVoltageToPercent</t>
+          <t>func__Ui_Buzzer_Gated</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
@@ -10808,51 +10812,51 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>387</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
+          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BeepDutyPercent</t>
+          <t>func__Ui_Buzzer_Tick</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
+          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BoardTest_Start</t>
+          <t>func__Ui_ChargeVoltageToPercent</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
@@ -10867,19 +10871,19 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>650</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
+          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Gated</t>
+          <t>func__Ui_ClampAlarms</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -10894,46 +10898,46 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>187</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
+          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Tick</t>
+          <t>func__Ui_ClampPeriod</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
+          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ChargeVoltageToPercent</t>
+          <t>func__Ui_ClampWindow</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -10943,24 +10947,24 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
+          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampAlarms</t>
+          <t>func__Ui_GetAlarmParam</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
@@ -10970,24 +10974,24 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>532</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
+          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampPeriod</t>
+          <t>func__Ui_Init</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -10997,24 +11001,24 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
+          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampWindow</t>
+          <t>func__Ui_ResetBatteryCriticalBeep</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
@@ -11029,19 +11033,19 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
+          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_GetAlarmParam</t>
+          <t>func__Ui_ResetBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
@@ -11051,24 +11055,24 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
+          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Init</t>
+          <t>func__Ui_ResetBatteryStablePercent</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -11078,24 +11082,24 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>896</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
+          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryCriticalBeep</t>
+          <t>func__Ui_ResetChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -11110,19 +11114,19 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
+          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryRunGreenBlink</t>
+          <t>func__Ui_ResetChargingStablePercent</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
@@ -11137,19 +11141,19 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>984</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
+          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryStablePercent</t>
+          <t>func__Ui_ResetChargingYellowBlink</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -11164,19 +11168,19 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
+          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingFullHysteresis</t>
+          <t>func__Ui_ScenarioBatLost_Tick</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -11186,24 +11190,24 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
+          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingStablePercent</t>
+          <t>func__Ui_ScenarioBatteryRun_Tick</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -11213,24 +11217,24 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
+          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingYellowBlink</t>
+          <t>func__Ui_ScenarioCharging_Tick</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -11240,24 +11244,24 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
+          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatLost_Tick</t>
+          <t>func__Ui_ScenarioDeadBattery_Tick</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -11272,19 +11276,19 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
+          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatteryRun_Tick</t>
+          <t>func__Ui_ScenarioImbalance_Tick</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -11299,19 +11303,19 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
+          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioCharging_Tick</t>
+          <t>func__Ui_ScenarioInputOk</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -11326,19 +11330,19 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
+          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioDeadBattery_Tick</t>
+          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -11348,24 +11352,24 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
+          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioImbalance_Tick</t>
+          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -11375,24 +11379,24 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
+          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOk</t>
+          <t>func__Ui_SetAlarmParam</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -11407,19 +11411,19 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
+          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
+          <t>func__Ui_Tick</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -11429,24 +11433,24 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
+          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
+          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -11461,19 +11465,19 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
+          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_SetAlarmParam</t>
+          <t>func__Ui_UpdateBatteryStablePercent</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -11483,24 +11487,24 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>909</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
+          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Tick</t>
+          <t>func__Ui_UpdateChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -11510,24 +11514,24 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
+          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
+          <t>func__Ui_UpdateChargingStablePercent</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -11542,19 +11546,19 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
+          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryStablePercent</t>
+          <t>func__Ui_UpdateChargingYellowBlink</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -11569,19 +11573,19 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
+          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingFullHysteresis</t>
+          <t>func__Ui_UpdateInputState</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -11596,19 +11600,19 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
+          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingStablePercent</t>
+          <t>func__Ui_VoltageToPercentMap</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -11623,19 +11627,19 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>578</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
+          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingYellowBlink</t>
+          <t>func__all_off</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -11650,19 +11654,19 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>699</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
+          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateInputState</t>
+          <t>func__green</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -11677,19 +11681,19 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
+          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_VoltageToPercentMap</t>
+          <t>func__red</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
@@ -11704,19 +11708,19 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>676</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>func__all_off</t>
+          <t>func__yellow</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
@@ -11731,91 +11735,10 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>688</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
-        <is>
-          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="5" t="inlineStr">
-        <is>
-          <t>func__green</t>
-        </is>
-      </c>
-      <c r="B301" s="5" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
-        </is>
-      </c>
-      <c r="C301" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D301" s="5" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="E301" s="5" t="inlineStr">
-        <is>
-          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="5" t="inlineStr">
-        <is>
-          <t>func__red</t>
-        </is>
-      </c>
-      <c r="B302" s="5" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
-        </is>
-      </c>
-      <c r="C302" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D302" s="5" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="E302" s="5" t="inlineStr">
-        <is>
-          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="5" t="inlineStr">
-        <is>
-          <t>func__yellow</t>
-        </is>
-      </c>
-      <c r="B303" s="5" t="inlineStr">
-        <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
-        </is>
-      </c>
-      <c r="C303" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D303" s="5" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>ال‌ای‌دی زرد را روشن/خاموش می‌کند.</t>
         </is>
@@ -19052,7 +18975,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>91 فایل · 301 تابع · 147 شناسه · 20 سیگنال</t>
+          <t>91 فایل · 298 تابع · 147 شناسه · 20 سیگنال</t>
         </is>
       </c>
     </row>

--- a/Documentation/Program_Map.xlsx
+++ b/Documentation/Program_Map.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>442</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>قالب فرمول مشترک هر دو کانال، یک مرحله برای هر المان شماتیک: شمارش -&gt; mV پایه ADC -&gt; خنثی‌کردن تقسیم ‎R41/R42 -&gt;‎ خنثی‌کردن گین LM358 -&gt; خنثی‌کردن mΩ شانت -&gt; mA، سپس آفست صفر پر-کانال و گین پرمیل بنچ. هر ضرب مرحلهٔ صورت/مخرج خودش را جابه‌جا می‌کند و فقط یک تقسیم در انتها اجرا می‌شود. رژیم فلش: پنج مرحله در یک ضرب+تقسیم 32بیتی با نتیجهٔ بیت‌به‌بیت یکسان جمع شد (اثبات برای هر 4096 شمارش؛ تقسیم 64بیتی ~1KB می‌خواست). اگر مقاومتی عوض شد دوباره اشتقاق بگیر (تست هاست از همین دیفاین‌ها بازمحاسبه می‌کند). رُند: تقسیم جمع‌شده همان قاعدهٔ رُند به نزدیکِ پنل و لنگرهای جدول بنچ را دارد (نصف مقسوم‌علیه پیش از تقسیم)، چون زنجیرهٔ برشی، کم‌خوانی یک‌طرفهٔ جریان اندازه‌گیری‌شده است.</t>
+          <t>قالب فرمول مشترک هر دو کانال، یک مرحله برای هر المان شماتیک: شمارش -&gt; mV پایه ADC -&gt; خنثی‌کردن تقسیم ‎R41/R42 -&gt;‎ خنثی‌کردن گین LM358 -&gt; خنثی‌کردن mΩ شانت -&gt; mA، سپس آفست صفر پر-کانال و گین پرمیل بنچ. هر ضرب مرحلهٔ صورت/مخرج خودش را جابه‌جا می‌کند و فقط یک تقسیم در انتها اجرا می‌شود. رژیم فلش: پنج مرحله در یک ضرب+تقسیم 32بیتی با نتیجهٔ بیت‌به‌بیت یکسان جمع شد (اثبات برای هر 4096 شمارش؛ تقسیم 64بیتی ~1KB می‌خواست). اگر مقاومتی عوض شد دوباره اشتقاق بگیر (تست هاست از همین دیفاین‌ها بازمحاسبه می‌کند). رُند: تقسیم جمع‌شده رو به بالا (سقف) گرد می‌شود، همان قاعدهٔ درون‌یابی جدول؛ هیچ گرد یا برشی‌ای نباید از جریان واقعی پایین‌تر بخواند.</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>544</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>693</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>483</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">

--- a/Documentation/Program_Map.xlsx
+++ b/Documentation/Program_Map.xlsx
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>298 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
+          <t>323 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
         </is>
       </c>
     </row>
@@ -673,11 +673,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>731</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>752</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>496</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1690,7 +1690,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>626</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>موتور ‎ESP-Link‎: کنترل تغذیه، پارسر فریم بایتی، اعمال پارامترها و تله‌متری دوره‌ای روی پورت منطقی UART (دستور کاربر 2026-09-22). تماماً نرم‌افزار، فقط تخصیص ایستا، بدون فراخوانی RTOS داخل پارسر. /</t>
+          <t>لاگر تشخیصی: زمان و تعداد شارژ، 10 خطای آخر، رویدادهای برق، کمینه/بیشینه. فلش پینگ‌پنگ در ‎0x0800F800 / 0x0800FC00‎ با CRC32 و ذخیره دیبانس. /</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -1732,29 +1732,29 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>195</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>قالب فریم (دو جهته)، payload اندیان کوچک: [0xAA][0x55][type:u8][len:u8][payload:len][xor:u8] که xor عبارت از XOR نوع و طول و همهٔ بایت‌های payload است. موتور بعد از هر خطا روی 0xAA 0x55 بعدی همگام می‌شود. /</t>
+          <t>لاگ تشخیصی: زمان شارژ، تعداد شارژ، 10 خطای آخر، رویدادهای قطع برق، کمینه/بیشینه. در صفحات فلش جدا ‎0x0800F800 / 0x0800FC00‎ به صورت پینگ‌پنگ ماندگار می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -1764,29 +1764,29 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>ماندگاری پارامترهای پنل در فلش رویتراشهٔ STM32 (v1.14). قرارداد در esp_link_nvm.h است. بلوک «منطق خالص رکورد» پایین خودکفاست - تست هاست همین بلوک را روی فلشِ شبیه‌سازی‌ شدهٔ RAM کامپایل می‌کند تا رفتار قطع برق بدون سخت‌افزار اثبات شود. /</t>
+          <t>موتور ‎ESP-Link‎: کنترل تغذیه، پارسر فریم بایتی، اعمال پارامترها و تله‌متری دوره‌ای روی پورت منطقی UART (دستور کاربر 2026-09-22). تماماً نرم‌افزار، فقط تخصیص ایستا، بدون فراخوانی RTOS داخل پارسر. /</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -1796,29 +1796,29 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>ماندگاری پارامترهای پنل در فلش رویتراشهٔ STM32 (v1.14). همهٔ پارامترهای قابل‌تنظیم به‌جز مودهای تست گذرا (15..18 و 19) با CRC و شمارهٔ ترتیب در دو صفحهٔ آخر 1KB فلش ذخیره می‌شوند و هر ذخیره صفحه را عوض می‌کند تا قطع برق وسط نوشتن رکورد خوب قبلی را از بین نبرد. بوت تازه‌ترین رکورد معتبر را از همان setterهای گیره‌دارِ مسیر پنل بازپخش می‌کند. ذخیره ~1٫5 ثانیه دیبانس و در تسک ارتباط است (پاک‌کردن صفحه یک‌بار ~20..40ms CPU را نگه می‌دارد). /</t>
+          <t>قالب فریم (دو جهته)، payload اندیان کوچک: [0xAA][0x55][type:u8][len:u8][payload:len][xor:u8] که xor عبارت از XOR نوع و طول و همهٔ بایت‌های payload است. موتور بعد از هر خطا روی 0xAA 0x55 بعدی همگام می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -1828,29 +1828,29 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>733</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>پیاده‌سازی انبارهٔ خطاهای قفل‌شده: یک بیت‌ماسک ایستا با دسترسی ست/پاک/پرسش، آشکارسازِ قطع باتری که کانال در حال پمپِ شارژر را می‌پاید تا ببیند ولتاژ پک جواب می‌دهد یا نه، آستانه‌های آلارم زمان اجرا (شناسه‌های 27 تا 34) با گیره‌های سختِ هر فیلد، و قلاب نظارتی که پس از تغییر همان گیره‌ها را دوباره اعمال می‌کند. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
+          <t>ماندگاری پارامترهای پنل در فلش رویتراشهٔ STM32 (v1.14). قرارداد در esp_link_nvm.h است. بلوک «منطق خالص رکورد» پایین خودکفاست - تست هاست همین بلوک را روی فلشِ شبیه‌سازی‌ شدهٔ RAM کامپایل می‌کند تا رفتار قطع برق بدون سخت‌افزار اثبات شود. /</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1875,14 +1875,14 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>رابط عمومی بیت‌ماسک خطاهای قفل‌شده: خودِ تعریف بیت‌ها، ای‌پی‌آیِ ست/پاک/پرسش، ثابت‌های تشخیص قطع باتری، قرارداد آستانه‌های زمان اجرا (شناسه‌های 27 تا 34) و قلابِ نظارتی که شارژر هنگام جابه‌جایی آستانهٔ خودش صدا می‌زند. هر بیت قفل‌شده برنامه را به حالت FAULT می‌برد و تا پاک‌شدن صریح همان‌جا نگه می‌دارد. ممیزی 2026-10-05: سرخط قبلی این فایل را «اسکلت» می‌نامید. مدت‌هاست که اسکلت نیست (آشکارسازِ قطع باتری، مجموعهٔ آلارم و آبشار نظارتی اینجاست)، پس آن برچسب کهنه برداشته شد. /</t>
+          <t>ماندگاری پارامترهای پنل در فلش رویتراشهٔ STM32 (v1.14). همهٔ پارامترهای قابل‌تنظیم به‌جز مودهای تست گذرا (15..18 و 19) با CRC و شمارهٔ ترتیب در دو صفحهٔ آخر 1KB فلش ذخیره می‌شوند و هر ذخیره صفحه را عوض می‌کند تا قطع برق وسط نوشتن رکورد خوب قبلی را از بین نبرد. بوت تازه‌ترین رکورد معتبر را از همان setterهای گیره‌دارِ مسیر پنل بازپخش می‌کند. ذخیره ~1٫5 ثانیه دیبانس و در تسک ارتباط است (پاک‌کردن صفحه یک‌بار ~20..40ms CPU را نگه می‌دارد). /</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>سناریوی 5 - پایش عدم‌توازن باتری؛ قرارداد رفتار در imbalance.h. ماندگاری: اسلات‌های 200..202 فقط هنگام تغییر واقعی میزبان ذخیرهٔ فلش می‌شوند (بارها در روز با باتریِ خیلی خراب)؛ با تحمل ~10٬000 بار پاک‌سازی، حاشیهٔ فرسودگی دهه‌هاست - پس حتی ذخیرهٔ فوری هم هزینه‌ای ندارد، چه رسد به دبونس. /</t>
+          <t>پیاده‌سازی انبارهٔ خطاهای قفل‌شده: یک بیت‌ماسک ایستا با دسترسی ست/پاک/پرسش، آشکارسازِ قطع باتری که کانال در حال پمپِ شارژر را می‌پاید تا ببیند ولتاژ پک جواب می‌دهد یا نه، آستانه‌های آلارم زمان اجرا (شناسه‌های 27 تا 34) با گیره‌های سختِ هر فیلد، و قلاب نظارتی که پس از تغییر همان گیره‌ها را دوباره اعمال می‌کند. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -1924,29 +1924,29 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>سناریوی 5 - پایش عدم‌توازن (آنبالانس) دو نیم‌باتری. قدرمطلق اختلاف دو نیم به شارژ 12 ولتی پک 24 ولتی (|‎v_high - v_low|)‎ با حد استراحت و حد دشارژ سنجیده می‌شود، شرط فراتر از حد با زمان پایداری و هیسترزیس به نامزد تبدیل می‌شود و پس از FLOAT واقعی ثبت می‌گردد (هر سیکل حداکثر یک‌بار). پس از پر شدن سقف رویدادها قفل صادر می‌شود: LED قرمز چشمک‌زن + بوق کوتاه ساعتی + (با تیک کاربر) ممنوعیت سوئیچ شدن باتری روی خروجی. شارژ در حالت قفل آزاد می‌ماند تا بوق ساعتی کار کند، ولی پس از تعداد قابل‌تنظیم سیکل شارژ در حالت قفل، شارژ هم بسته می‌شود. سه سیکل کامل بدون رویداد جدید، فقط شمارندهٔ عدم‌توازن را صفر می‌کند؛ قفل و بودجهٔ آن حفظ می‌شوند. نبود باتری (تعویض واقعی) مسیر ریست فوری همهٔ این مقادیر است. گیت زمانی ارزیابی: آستانه‌ها فقط (الف) در استراحت و پس از زمان پارامتر 110 از پایان سیکل کامل و (ب) در حین شارژ پس از زمان پارامتر 111 اعمال می‌شوند؛ هر دو زمان تا 5 ساعت قابل تنظیم‌اند. حین شارژ همان آستانهٔ استراحت استفاده می‌شود. در دشارژ حد پارامتر 109 بلافاصله دیده می‌شود، اما ثبت رویداد همچنان به کامل‌شدن سیکل و رسیدن به FLOAT وابسته است. منطق خالص: Evaluate همهٔ ورودی‌ها و زمان فعلی را می‌گیرد؛ بی‌وابستگی به ‎BSP/RTOS‎. خروجی‌ها را پس از هر فراخوانی بخوان. /</t>
+          <t>رابط عمومی بیت‌ماسک خطاهای قفل‌شده: خودِ تعریف بیت‌ها، ای‌پی‌آیِ ست/پاک/پرسش، ثابت‌های تشخیص قطع باتری، قرارداد آستانه‌های زمان اجرا (شناسه‌های 27 تا 34) و قلابِ نظارتی که شارژر هنگام جابه‌جایی آستانهٔ خودش صدا می‌زند. هر بیت قفل‌شده برنامه را به حالت FAULT می‌برد و تا پاک‌شدن صریح همان‌جا نگه می‌دارد. ممیزی 2026-10-05: سرخط قبلی این فایل را «اسکلت» می‌نامید. مدت‌هاست که اسکلت نیست (آشکارسازِ قطع باتری، مجموعهٔ آلارم و آبشار نظارتی اینجاست)، پس آن برچسب کهنه برداشته شد. /</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>753</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -1971,14 +1971,14 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>پیاده‌سازی قفلِ پرچم تریپ LM393: پرچم‌های نرم‌افزاری EXTI لایهٔ برد را می‌خواند، برای هر کانال یک بولینِ چسبنده قفل می‌کند و پاک‌کردن تکی می‌دهد. هیچ HAL و شمارهٔ پایه‌ای اینجا نیست؛ اینکه کدام خط EXTI به کدام مقایسه‌گر می‌رود کار پورت برد است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
+          <t>سناریوی 5 - پایش عدم‌توازن باتری؛ قرارداد رفتار در imbalance.h. ماندگاری: اسلات‌های 200..202 فقط هنگام تغییر واقعی میزبان ذخیرهٔ فلش می‌شوند (بارها در روز با باتریِ خیلی خراب)؛ با تحمل ~10٬000 بار پاک‌سازی، حاشیهٔ فرسودگی دهه‌هاست - پس حتی ذخیرهٔ فوری هم هزینه‌ای ندارد، چه رسد به دبونس. /</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -1988,29 +1988,29 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>رابط عمومی پرچم‌های تریپِ مقایسه‌گرِ اضافه‌جریان LM393. دو مقایسه‌گر کلکتور-باز با مقاومت بالاکش‌اند، پس تریپ یک لبهٔ پایین‌رونده است که EXTI سخت‌افزاری می‌گیرد؛ این ماژول فقط پرچم نرم‌افزاری هر کانال را قفل می‌کند و به شارژر می‌دهد که صاحب واکنش است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
+          <t>سناریوی 5 - پایش عدم‌توازن (آنبالانس) دو نیم‌باتری. قدرمطلق اختلاف دو نیم به شارژ 12 ولتی پک 24 ولتی (|‎v_high - v_low|)‎ با حد استراحت و حد دشارژ سنجیده می‌شود، شرط فراتر از حد با زمان پایداری و هیسترزیس به نامزد تبدیل می‌شود و پس از FLOAT واقعی ثبت می‌گردد (هر سیکل حداکثر یک‌بار). پس از پر شدن سقف رویدادها قفل صادر می‌شود: LED قرمز چشمک‌زن + بوق کوتاه ساعتی + (با تیک کاربر) ممنوعیت سوئیچ شدن باتری روی خروجی. شارژ در حالت قفل آزاد می‌ماند تا بوق ساعتی کار کند، ولی پس از تعداد قابل‌تنظیم سیکل شارژ در حالت قفل، شارژ هم بسته می‌شود. سه سیکل کامل بدون رویداد جدید، فقط شمارندهٔ عدم‌توازن را صفر می‌کند؛ قفل و بودجهٔ آن حفظ می‌شوند. نبود باتری (تعویض واقعی) مسیر ریست فوری همهٔ این مقادیر است. گیت زمانی ارزیابی: آستانه‌ها فقط (الف) در استراحت و پس از زمان پارامتر 110 از پایان سیکل کامل و (ب) در حین شارژ پس از زمان پارامتر 111 اعمال می‌شوند؛ هر دو زمان تا 5 ساعت قابل تنظیم‌اند. حین شارژ همان آستانهٔ استراحت استفاده می‌شود. در دشارژ حد پارامتر 109 بلافاصله دیده می‌شود، اما ثبت رویداد همچنان به کامل‌شدن سیکل و رسیدن به FLOAT وابسته است. منطق خالص: Evaluate همهٔ ورودی‌ها و زمان فعلی را می‌گیرد؛ بی‌وابستگی به ‎BSP/RTOS‎. خروجی‌ها را پس از هر فراخوانی بخوان. /</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2035,14 +2035,14 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>مسیر تغذیه MCU با Q1 (PB5) - مستقل از Changeover. هیسترزیس ‎22000/21500‎. /</t>
+          <t>پیاده‌سازی قفلِ پرچم تریپ LM393: پرچم‌های نرم‌افزاری EXTI لایهٔ برد را می‌خواند، برای هر کانال یک بولینِ چسبنده قفل می‌کند و پاک‌کردن تکی می‌دهد. هیچ HAL و شمارهٔ پایه‌ای اینجا نیست؛ اینکه کدام خط EXTI به کدام مقایسه‌گر می‌رود کار پورت برد است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -2052,93 +2052,93 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>مسیر تغذیهٔ خود MCU با Q1 (PB5، ‎active-low)‎ مستقل از ‎Changeover (PB11): v_in &gt;= 22000mV‎ به‌مدت 5000ms ← قطع؛ ‎v_in &lt; 21500mV‎ ← وصل؛ 21500..21999 نوار مرده؛ لبهٔ نزولی PB4 بلافاصله در ISR وصل می‌کند. فقط مالک PB5 است؛ آستانه‌ها فقط برای v_in هستند و آستانه‌های Changeover اینجا استفاده نمی‌شوند. /</t>
+          <t>رابط عمومی پرچم‌های تریپِ مقایسه‌گرِ اضافه‌جریان LM393. دو مقایسه‌گر کلکتور-باز با مقاومت بالاکش‌اند، پس تریپ یک لبهٔ پایین‌رونده است که EXTI سخت‌افزاری می‌گیرد؛ این ماژول فقط پرچم نرم‌افزاری هر کانال را قفل می‌کند و به شارژر می‌دهد که صاحب واکنش است. ممیزی 2026-10-05: برچسب کهنهٔ «اسکلت» از سرخط قبلی برداشته شد. /</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/calibration.h</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>261</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>ثابت‌های کالیبراسیون زمان بیلد ChangeOver (مرجع ADC). ---------------------------------------------------------------------------- [EN] (2026-10-10) The battery CURRENT tables are NO LONGER compiled in. They are made on the panel from the bench data and stored in flash (CalLut). Until the first calibration the board reads through the gain and offset in the BSP, which start at the MAXIMUM gain and zero offset (safe direction: a high reading only slows the charge). [FA] جدول‌های جریان باتری دیگر در کد کامپایل نمی‌شوند. روی پنل از داده‌های بنچ ساخته و در فلش (CalLut) ذخیره می‌شوند. تا اولین کالیبراسیون، برد با گین و آفست BSP کار می‌کند که از بیشترین گین و آفست صفر شروع می‌کنند (جهت امن: خوانش بالا فقط شارژ را کند می‌کند). ============================================================================</t>
+          <t>مسیر تغذیه MCU با Q1 (PB5) - مستقل از Changeover. هیسترزیس ‎22000/21500‎. /</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>.c</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>شمارش ADC به واحد مهندسی (‎mV/mA)‎ گام‌به‌گام؛ آخرین snapshot مشترک با تسک‌های دیگر. فقط چند تبدیل + یک خواندن GPIO و بعد yield - بدون HAL_Delay. جریان شارژ = نمونهٔ سنکرون وسط ON که اول روی شمارش خام فیلتر می‌شود (مدین + میانگین متحرک) و بعد تبدیل؛ ولتاژ باتری محافظ مدین-5 روی شمارش خام دارد. ثابت‌های تقسیم/گین خصوصی bsp_measurement.c است؛ مقادیر تبدیل‌شده در گلوبال‌های Meas* فقط با نوشتن همین تسک در دسترس همه‌اند (از جمله دیباگ با Live Expressions). /</t>
+          <t>مسیر تغذیهٔ خود MCU با Q1 (PB5، ‎active-low)‎ مستقل از ‎Changeover (PB11): v_in &gt;= 22000mV‎ به‌مدت 5000ms ← قطع؛ ‎v_in &lt; 21500mV‎ ← وصل؛ 21500..21999 نوار مرده؛ لبهٔ نزولی PB4 بلافاصله در ISR وصل می‌کند. فقط مالک PB5 است؛ آستانه‌ها فقط برای v_in هستند و آستانه‌های Changeover اینجا استفاده نمی‌شوند. /</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Measurement/calibration.h</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -2148,29 +2148,29 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>شمارش ADC را به واحد مهندسی (‎mV / mA)‎ تبدیل می‌کند و آخرین نمونه را برای تسک‌های دیگر نگه می‌دارد. منطق این ماژول مستقل از برد است؛ ADC خام از BSP می‌آید و کالیبراسیون برد در `bsp_measurement` انجام می‌شود. /</t>
+          <t>ثابت‌های کالیبراسیون زمان بیلد ChangeOver (مرجع ADC). ---------------------------------------------------------------------------- [EN] (2026-10-10) The battery CURRENT tables are NO LONGER compiled in. They are made on the panel from the bench data and stored in flash (CalLut). Until the first calibration the board reads through the gain and offset in the BSP, which start at the MAXIMUM gain and zero offset (safe direction: a high reading only slows the charge). [FA] جدول‌های جریان باتری دیگر در کد کامپایل نمی‌شوند. روی پنل از داده‌های بنچ ساخته و در فلش (CalLut) ذخیره می‌شوند. تا اولین کالیبراسیون، برد با گین و آفست BSP کار می‌کند که از بیشترین گین و آفست صفر شروع می‌کنند (جهت امن: خوانش بالا فقط شارژ را کند می‌کند). ============================================================================</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2195,14 +2195,14 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>پیادهسازی ناظر سبک: ‎FAULT_ADC‎ یک وضعیت زنده (بدون قفل) است که تا نامعتبربودن نمونهٔ اندازهگیری نگه داشته می‌شود. نظارت اضافهجریان و باتری ضعیف در مسیر آلارم شارژر و آشکارسازهای فالت است؛ ماژول بهطور پیشفرض بیرون کامپایل می‌ماند ‎(MODULE_PROTECTION = 0)‎. نام تایپ کامل. @‎note    [EN] Full-program audit‎ 2026-10-07: the stale "placeholder" label was removed and the "latch faults" wording corrected - see the design note inside func__Protection_Run for why FAULT_ADC must stay live instead of latching. ممیزی کل برنامه 2026-10-07: برچسب کهنهٔ «اسکلت» برداشته شد و عبارت «خطا را قفل می‌کند» اصلاح شد - دلیل زندهبودن ‎FAULT_ADC‎ در یادداشت طراحی داخل ‎func__Protection_Run‎ آمده است. /</t>
+          <t>شمارش ADC به واحد مهندسی (‎mV/mA)‎ گام‌به‌گام؛ آخرین snapshot مشترک با تسک‌های دیگر. فقط چند تبدیل + یک خواندن GPIO و بعد yield - بدون HAL_Delay. جریان شارژ = نمونهٔ سنکرون وسط ON که اول روی شمارش خام فیلتر می‌شود (مدین + میانگین متحرک) و بعد تبدیل؛ ولتاژ باتری محافظ مدین-5 روی شمارش خام دارد. ثابت‌های تقسیم/گین خصوصی bsp_measurement.c است؛ مقادیر تبدیل‌شده در گلوبال‌های Meas* فقط با نوشتن همین تسک در دسترس همه‌اند (از جمله دیباگ با Live Expressions). /</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -2212,29 +2212,29 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>ناظر سبک: تا وقتی نمونهٔ اندازهگیری نامعتبر است ‎FAULT_ADC‎ را بهصورت وضعیت زنده (بدون قفل) نگه می‌دارد؛ نظارت اضافهجریان و باتری ضعیف در مسیر آلارم شارژر و آشکارسازهای فالت است. ماژول بهطور پیشفرض بیرون کامپایل می‌ماند ‎(MODULE_PROTECTION = 0)‎. نام تایپ کامل. @‎note    [EN] Full-program audit‎ 2026-10-07: the stale "placeholder" label was removed and the "latch faults" wording corrected - the implementation deliberately keeps FAULT_ADC live instead of latching it (see the note inside protection.c). ممیزی کل برنامه 2026-10-07: برچسب کهنهٔ «اسکلت» برداشته شد و عبارت «خطا را قفل می‌کند» اصلاح شد - پیادهسازی عمداً ‎FAULT_ADC‎ را زنده نگه می‌دارد نه قفلشده (یادداشت داخل ‎protection.c‎). /</t>
+          <t>شمارش ADC را به واحد مهندسی (‎mV / mA)‎ تبدیل می‌کند و آخرین نمونه را برای تسک‌های دیگر نگه می‌دارد. منطق این ماژول مستقل از برد است؛ ADC خام از BSP می‌آید و کالیبراسیون برد در `bsp_measurement` انجام می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>یک سرویس غیرمسدودکننده بوق دوره‌ای؛ زمان پالس را از دوره، دیوتی، تعداد و گپ محاسبه می‌کند. فقط سناریوهای صریح این سرویس را صدا می‌زنند؛ کنترل GPIO بوق همچنان در این فایل است و فراخواننده چهار ورودی را می‌دهد. /</t>
+          <t>پیادهسازی ناظر سبک: ‎FAULT_ADC‎ یک وضعیت زنده (بدون قفل) است که تا نامعتبربودن نمونهٔ اندازهگیری نگه داشته می‌شود. نظارت اضافهجریان و باتری ضعیف در مسیر آلارم شارژر و آشکارسازهای فالت است؛ ماژول بهطور پیشفرض بیرون کامپایل می‌ماند ‎(MODULE_PROTECTION = 0)‎. نام تایپ کامل. @‎note    [EN] Full-program audit‎ 2026-10-07: the stale "placeholder" label was removed and the "latch faults" wording corrected - see the design note inside func__Protection_Run for why FAULT_ADC must stay live instead of latching. ممیزی کل برنامه 2026-10-07: برچسب کهنهٔ «اسکلت» برداشته شد و عبارت «خطا را قفل می‌کند» اصلاح شد - دلیل زندهبودن ‎FAULT_ADC‎ در یادداشت طراحی داخل ‎func__Protection_Run‎ آمده است. /</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -2276,29 +2276,29 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>یک سرویس عمومی بوق UI: الگوی دوره‌ای بر اساس دوره، دیوتی، تعداد و گپ. مقدار بازگشتی، زمان پیشنهادی مراجعه بعدی بر حسب میلی‌ثانیه است. /</t>
+          <t>ناظر سبک: تا وقتی نمونهٔ اندازهگیری نامعتبر است ‎FAULT_ADC‎ را بهصورت وضعیت زنده (بدون قفل) نگه می‌دارد؛ نظارت اضافهجریان و باتری ضعیف در مسیر آلارم شارژر و آشکارسازهای فالت است. ماژول بهطور پیشفرض بیرون کامپایل می‌ماند ‎(MODULE_PROTECTION = 0)‎. نام تایپ کامل. @‎note    [EN] Full-program audit‎ 2026-10-07: the stale "placeholder" label was removed and the "latch faults" wording corrected - the implementation deliberately keeps FAULT_ADC live instead of latching it (see the note inside protection.c). ممیزی کل برنامه 2026-10-07: برچسب کهنهٔ «اسکلت» برداشته شد و عبارت «خطا را قفل می‌کند» اصلاح شد - پیادهسازی عمداً ‎FAULT_ADC‎ را زنده نگه می‌دارد نه قفلشده (یادداشت داخل ‎protection.c‎). /</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -2308,29 +2308,29 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>277</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>سناریوهای LED ماژول UI - ثابت‌های LED در هدر خودش، هر تابع و متغیر با جدا کننده و کامنت. ui_led.h پیش‌فرض‌ها را می‌دهد؛ از v1.16 مقدارهای زنده از struct ماندگار UI می‌آیند (38..82) نه از APP_CONFIG (که فقط زمان‌بندی تست برد را می‌دهد). نام‌گذاری با __، پیشوند func__، فرمول غیرخطی. /</t>
+          <t>یک سرویس غیرمسدودکننده بوق دوره‌ای؛ زمان پالس را از دوره، دیوتی، تعداد و گپ محاسبه می‌کند. فقط سناریوهای صریح این سرویس را صدا می‌زنند؛ کنترل GPIO بوق همچنان در این فایل است و فراخواننده چهار ورودی را می‌دهد. /</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -2340,61 +2340,61 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>سناریوهای LED ماژول UI - ثابت‌های LED در هدر خودش، فرمول غیرخطی، RTOS ساده. پیش‌فرض‌های LED در این هدر هستند؛ از v1.16 منطق زمان اجرا از ui_alarm_t ماندگار (38..82) می‌خواند و APP_CONFIG فقط زمان‌بندی تست برد را نگه می‌دارد. /</t>
+          <t>یک سرویس عمومی بوق UI: الگوی دوره‌ای بر اساس دوره، دیوتی، تعداد و گپ. مقدار بازگشتی، زمان پیشنهادی مراجعه بعدی بر حسب میلی‌ثانیه است. /</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_app.h</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های برنامه و کرنل ‎CMSIS-RTOS2‎ را راه‌اندازی می‌کند. /</t>
+          <t>سناریوهای LED ماژول UI - ثابت‌های LED در هدر خودش، هر تابع و متغیر با جدا کننده و کامنت. ui_led.h پیش‌فرض‌ها را می‌دهد؛ از v1.16 مقدارهای زنده از struct ماندگار UI می‌آیند (38..82) نه از APP_CONFIG (که فقط زمان‌بندی تست برد را می‌دهد). نام‌گذاری با __، پیشوند func__، فرمول غیرخطی. /</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_backend_memory.h</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -2404,29 +2404,29 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>852</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>نوع حافظهٔ ثابت موردنیاز Backend انتخاب‌شدهٔ ‎CMSIS-RTOS2‎. فقط این مرز می‌داند که Backend فعلی ‎CMSIS-RTOS2‎، FreeRTOS است. /</t>
+          <t>سناریوهای LED ماژول UI - ثابت‌های LED در هدر خودش، فرمول غیرخطی، RTOS ساده. پیش‌فرض‌های LED در این هدر هستند؛ از v1.16 منطق زمان اجرا از ui_alarm_t ماندگار (38..82) می‌خواند و APP_CONFIG فقط زمان‌بندی تست برد را نگه می‌دارد. /</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Rtos/Inc/rtos_app.h</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -2451,14 +2451,14 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>اعلان توابع ورود تسک‌های ‎CMSIS-RTOS2‎ لایهٔ کاربرد. /</t>
+          <t>تسک‌های برنامه و کرنل ‎CMSIS-RTOS2‎ را راه‌اندازی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Rtos/Inc/rtos_backend_memory.h</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2483,78 +2483,78 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>تبدیل قابل‌حمل تیک و میلی‌ثانیه در ‎CMSIS-RTOS2‎. /</t>
+          <t>نوع حافظهٔ ثابت موردنیاز Backend انتخاب‌شدهٔ ‎CMSIS-RTOS2‎. فقط این مرز می‌داند که Backend فعلی ‎CMSIS-RTOS2‎، FreeRTOS است. /</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/freertos_hooks.c</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>.c</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>هوک تخصیص استاتیک ‎Idle/Timer‎ و تله سرریز استک. اگر CubeMX همین توابع را ساخت، این فایل را از Build خارج کن. /</t>
+          <t>اعلان توابع ورود تسک‌های ‎CMSIS-RTOS2‎ لایهٔ کاربرد. /</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>.c</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های ‎CMSIS-RTOS2‎ را با تخصیص استاتیک می‌سازد و کرنل را شروع می‌کند. FreeRTOS در این مرحله Backend داخلی ‎CMSIS-RTOS2‎ است، اما کد برنامه از رابط ‎CMSIS-RTOS2‎ استفاده می‌کند و حافظهٔ همهٔ تسک‌ها را خودش می‌دهد. /</t>
+          <t>تبدیل قابل‌حمل تیک و میلی‌ثانیه در ‎CMSIS-RTOS2‎. /</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Rtos/Src/freertos_hooks.c</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2579,14 +2579,14 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>تبدیل قابل‌حمل تیک و میلی‌ثانیه در ‎CMSIS-RTOS2‎. /</t>
+          <t>هوک تخصیص استاتیک ‎Idle/Timer‎ و تله سرریز استک. اگر CubeMX همین توابع را ساخت، این فایل را از Build خارج کن. /</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_comm.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2611,14 +2611,14 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>تسک ارتباط ساده RTOS. /</t>
+          <t>تسک‌های ‎CMSIS-RTOS2‎ را با تخصیص استاتیک می‌سازد و کرنل را شروع می‌کند. FreeRTOS در این مرحله Backend داخلی ‎CMSIS-RTOS2‎ است، اما کد برنامه از رابط ‎CMSIS-RTOS2‎ استفاده می‌کند و حافظهٔ همهٔ تسک‌ها را خودش می‌دهد. /</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_control.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2643,14 +2643,14 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>تسک کنترل ساده RTOS. از v1.74 تصمیم باتری کم داخل خود Changeover است و این تسک چیز اضافه‌ای نمی‌فرستد. /</t>
+          <t>تبدیل قابل‌حمل تیک و میلی‌ثانیه در ‎CMSIS-RTOS2‎. /</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_measurement.c</t>
+          <t>Firmware/Rtos/Src/task_comm.c</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2675,14 +2675,14 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>تسک اندازه‌گیری ‎CMSIS-RTOS2. backend ADC‎ برد فریم‌های کامل استانداردشده را می‌دهد؛ این تسک فقط جدیدترین فریم را در snapshot مشترک تبدیل می‌کند. الگوی RTOS ساده: osDelayUntil، بدون HAL_Delay. دوره از MEASUREMENT_PERIOD_MS (بالای measurement.h) — برای تغییر نرخ فقط یک خط. استک: TASK_STACK_MEASUREMENT word در rtos_config.h (فقط محلی‌های تبدیل، بدون آرایه‌ی بزرگ). /</t>
+          <t>تسک ارتباط ساده RTOS. /</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_protection.c</t>
+          <t>Firmware/Rtos/Src/task_control.c</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>تسک حفاظت ساده RTOS. /</t>
+          <t>تسک کنترل ساده RTOS. از v1.74 تصمیم باتری کم داخل خود Changeover است و این تسک چیز اضافه‌ای نمی‌فرستد. /</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_ui.c</t>
+          <t>Firmware/Rtos/Src/task_measurement.c</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -2739,78 +2739,78 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>تسک ‎CMSIS-RTOS2‎ رابط کاربر - سناریوهای LED را از snapshot واقعی Measurement انتخاب می‌کند. ولتاژ باتری تولید فقط از snapshot.v_bat24_mv می‌آید و قبل از هر تصمیم UI مقدار snapshot.valid بررسی می‌شود. /</t>
+          <t>تسک اندازه‌گیری ‎CMSIS-RTOS2. backend ADC‎ برد فریم‌های کامل استانداردشده را می‌دهد؛ این تسک فقط جدیدترین فریم را در snapshot مشترک تبدیل می‌کند. الگوی RTOS ساده: osDelayUntil، بدون HAL_Delay. دوره از MEASUREMENT_PERIOD_MS (بالای measurement.h) — برای تغییر نرخ فقط یک خط. استک: TASK_STACK_MEASUREMENT word در rtos_config.h (فقط محلی‌های تبدیل، بدون آرایه‌ی بزرگ). /</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Inc/FreeRTOSConfig.h</t>
+          <t>Firmware/Rtos/Src/task_protection.c</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>USER CODE BEGIN Header</t>
+          <t>تسک حفاظت ساده RTOS. /</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Inc/main.h</t>
+          <t>Firmware/Rtos/Src/task_ui.c</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>USER CODE BEGIN Header</t>
+          <t>تسک ‎CMSIS-RTOS2‎ رابط کاربر - سناریوهای LED را از snapshot واقعی Measurement انتخاب می‌کند. ولتاژ باتری تولید فقط از snapshot.v_bat24_mv می‌آید و قبل از هر تصمیم UI مقدار snapshot.valid بررسی می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Inc/stm32f1xx_hal_conf.h</t>
+          <t>CubeIDE/Core/Inc/FreeRTOSConfig.h</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>214</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -2842,7 +2842,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Inc/stm32f1xx_it.h</t>
+          <t>CubeIDE/Core/Inc/main.h</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>108</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -2874,17 +2874,17 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/freertos.c</t>
+          <t>CubeIDE/Core/Inc/stm32f1xx_hal_conf.h</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>.c</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>392</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -2906,17 +2906,17 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/main.c</t>
+          <t>CubeIDE/Core/Inc/stm32f1xx_it.h</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>.c</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -2938,7 +2938,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/stm32f1xx_hal_msp.c</t>
+          <t>CubeIDE/Core/Src/freertos.c</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -2970,7 +2970,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/stm32f1xx_hal_timebase_tim.c</t>
+          <t>CubeIDE/Core/Src/main.c</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>503</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/stm32f1xx_it.c</t>
+          <t>CubeIDE/Core/Src/stm32f1xx_hal_msp.c</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>272</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>CubeIDE/Core/Src/system_stm32f1xx.c</t>
+          <t>CubeIDE/Core/Src/stm32f1xx_hal_timebase_tim.c</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3054,29 +3054,29 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>CMSIS Cortex-M3 Device Peripheral Access Layer System Source File. 1.  This file provides two functions and one global variable to be called from user application: - SystemInit(): Setups the system clock (System clock source, PLL Multiplier factors, AHB/APBx prescalers and Flash settings). This function is called at startup just after reset and before branch to main program. This call is made inside the "startup_stm32f1xx_xx.s" file. - SystemCoreClock variable: Contains the core clock (HCLK), it can be used by the user application to setup the SysTick timer or configure other parameters. - SystemCoreClockUpdate(): Updates the variable SystemCoreClock and must be called whenever the core clock is changed during program execution. 2. After each device reset the HSI (8 MHz) is used as system clock source. Then SystemInit() function is called, in "startup_stm32f1xx_xx.s" file, to configure the system clock before to branch to main program. 4. The default value of HSE crystal is set to 8 MHz (or 25 MHz, depending on the product used), refer to "HSE_VALUE". When HSE is used as system clock source, directly or through PLL, and you are using different crystal you have to adapt the HSE value to your own configuration. @attention Copyright (c) 2017-2021 STMicroelectronics. All rights reserved. This software is licensed under terms that can be found in the LICENSE file in the root directory of this software component. If no LICENSE file comes with this software, it is provided AS-IS. /</t>
+          <t>USER CODE BEGIN Header</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/esp_link_panel.ino</t>
+          <t>CubeIDE/Core/Src/stm32f1xx_it.c</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>.ino</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>210</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3091,24 +3091,24 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>پل ‎ESP-Link‎ سمت ESP: تبادل فریم باینری با STM32 روی UART (921600 8N1، مطابق ESP_AGENT_SPEC.md نسخهٔ 1.4) و یک پنل وب دارک راست‌به‌چپ با فونت وزیرمتن و «دو» تب (کارت duty دستی از 1.10 در تب پنل؛ سقف duty، نمونه‌های نمودار، حذف صبر و مقسم پک هم در 1.10): 1) پنل: ولتاژهای مشترک (با کالیبراسیون آفست از مولتی‌متر)، فیلتر جریان (median 1..15، میانگین 1..300) و یک ستون برای هر شارژر: وضعیت زنده، زنجیرهٔ اندازه‌گیری با فرمول زنده، نمودار فیلتر و دکمهٔ قطع شارژر. 2) داده‌برداری بنچ (بخش ‎5.6): SOLO1/SOLO2/BOTH‎ با فهرست duty دلخواه و جلو رفتن فقط با دکمهٔ کاربر. اصلاح 1.7 (دستور کاربر 2026-09-25): پنجرهٔ آمار با باز شدن فرم مولتی‌متر صفر می‌شود و «همان لحظهٔ زدن ثبت» خوانده می‌شود تا ردیف CSV با عددهای واردشده هم‌لحظه باشد، نه یک پنجرهٔ کهنه؛ ستون sample_ms مدت واقعی همان پنجره است. یک ردیف 89ستونی برای هر مرحله در LittleFS به نام /benchlog.csv، دانلود با ‎GET /benchlog‎. اضافات نسخهٔ 1.6 (کارت CAL، تست‌های دستی ‎B/C/D‎، تب اصلاح/تحلیل، حالت مهندس) حذف شدند؛ هیچ کالیبراسیونی خودکار اعمال نمی‌شود و پروتکل سیمی (‎SET/GET/TLM)‎ دست‌نخورده و دوطرفه است.  @note    [EN] Wiring: STM32 PA9 (TX) -&gt; ESP RX, STM32 PA10 (RX) &lt;- ESP TX, common GND. STM32 PA8 drives ESP CH_PD/EN; this sketch never touches that line. Wi-Fi AP "ChangeOver-ESP", password "123456789", panel at http://192.168.4.1 No cloud: only MCU &lt;-&gt; ESP data exchange (flash is used only for the bench log file). Manual test mode (ID 19): a GET_PARAMS keepalive is sent every 1 s while manual mode is active (TLM flag b5 or param 19), also with a background tab (spec 5.2). Safety: if no browser has polled /t for 10 s (or none since the ESP booted), the ESP sends ID 19 = 0 every 1 s until the STM32 reports manual off, so a closed panel never leaves a channel on an unregulated duty; the STM32 3 s dead-man still covers an ESP hang or a broken link. [FA] سیم‌بندی: PA9 به RX ماژول، PA10 به TX ماژول، زمین مشترک. پایه ‎CH_PD/EN‎ را STM32 (PA8) کنترل می‌کند؛ این برنامه به آن دست نمی‌زند. وای‌فای "‎ChangeOver-ESP‎" با رمز "123456789"، پنل در http://192.168.4.1 بدون اینترنت: فقط تبادل داده بین MCU و ESP (فلش فقط برای فایل ثبت بنچ استفاده می‌شود). مود تست دستی (شناسه 19): تا وقتی مود دستی فعال است (پرچم b5 یا پارامتر 19) هر 1 ثانیه یک GET_PARAMS فرستاده می‌شود، حتی با تب پس‌زمینه (بخش 19 سند). ایمنی: اگر 10 ثانیه هیچ مرورگری /t را نخواند (یا از بوت ESP هنوز نخوانده باشد)، ESP هر 1 ثانیه شناسهٔ 19 = 0 را می‌فرستد تا STM32 خاموشی مود دستی را گزارش کند؛ پس پنل بسته هرگز کانال را روی duty بدون تنظیم رها نمی‌کند. هنگ ESP یا قطع لینک را ‎dead-man‎ سه‌ثانیه‌ای STM32 پوشش می‌دهد.</t>
+          <t>USER CODE BEGIN Header</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/panel_preview.html</t>
+          <t>CubeIDE/Core/Src/system_stm32f1xx.c</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>.html</t>
+          <t>.c</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>407</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3118,29 +3118,29 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>ویرایش با کلیک (دستور کاربر): خودِ عدد همان کنترل است. تنها نشانه، زیرخط نقطه‌چین است - عددی که شبیه دکمه باشد دیگر مثل عدد خوانده نمی‌شود و کار اصلی این جدول خوانده‌شدن است.</t>
+          <t>CMSIS Cortex-M3 Device Peripheral Access Layer System Source File. 1.  This file provides two functions and one global variable to be called from user application: - SystemInit(): Setups the system clock (System clock source, PLL Multiplier factors, AHB/APBx prescalers and Flash settings). This function is called at startup just after reset and before branch to main program. This call is made inside the "startup_stm32f1xx_xx.s" file. - SystemCoreClock variable: Contains the core clock (HCLK), it can be used by the user application to setup the SysTick timer or configure other parameters. - SystemCoreClockUpdate(): Updates the variable SystemCoreClock and must be called whenever the core clock is changed during program execution. 2. After each device reset the HSI (8 MHz) is used as system clock source. Then SystemInit() function is called, in "startup_stm32f1xx_xx.s" file, to configure the system clock before to branch to main program. 4. The default value of HSE crystal is set to 8 MHz (or 25 MHz, depending on the product used), refer to "HSE_VALUE". When HSE is used as system clock source, directly or through PLL, and you are using different crystal you have to adapt the HSE value to your own configuration. @attention Copyright (c) 2017-2021 STMicroelectronics. All rights reserved. This software is licensed under terms that can be found in the LICENSE file in the root directory of this software component. If no LICENSE file comes with this software, it is provided AS-IS. /</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_config.h</t>
+          <t>esp_link_panel/esp_link_panel.ino</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.ino</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>181</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3150,29 +3150,29 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>plink_config.h - link/message/param constants, bench CSV header, Wi-Fi/HTTP constants, parser states.</t>
+          <t>پل ‎ESP-Link‎ سمت ESP: تبادل فریم باینری با STM32 روی UART (921600 8N1، مطابق ESP_AGENT_SPEC.md نسخهٔ 1.4) و یک پنل وب دارک راست‌به‌چپ با فونت وزیرمتن و «دو» تب (کارت duty دستی از 1.10 در تب پنل؛ سقف duty، نمونه‌های نمودار، حذف صبر و مقسم پک هم در 1.10): 1) پنل: ولتاژهای مشترک (با کالیبراسیون آفست از مولتی‌متر)، فیلتر جریان (median 1..15، میانگین 1..300) و یک ستون برای هر شارژر: وضعیت زنده، زنجیرهٔ اندازه‌گیری با فرمول زنده، نمودار فیلتر و دکمهٔ قطع شارژر. 2) داده‌برداری بنچ (بخش ‎5.6): SOLO1/SOLO2/BOTH‎ با فهرست duty دلخواه و جلو رفتن فقط با دکمهٔ کاربر. اصلاح 1.7 (دستور کاربر 2026-09-25): پنجرهٔ آمار با باز شدن فرم مولتی‌متر صفر می‌شود و «همان لحظهٔ زدن ثبت» خوانده می‌شود تا ردیف CSV با عددهای واردشده هم‌لحظه باشد، نه یک پنجرهٔ کهنه؛ ستون sample_ms مدت واقعی همان پنجره است. یک ردیف 89ستونی برای هر مرحله در LittleFS به نام /benchlog.csv، دانلود با ‎GET /benchlog‎. اضافات نسخهٔ 1.6 (کارت CAL، تست‌های دستی ‎B/C/D‎، تب اصلاح/تحلیل، حالت مهندس) حذف شدند؛ هیچ کالیبراسیونی خودکار اعمال نمی‌شود و پروتکل سیمی (‎SET/GET/TLM)‎ دست‌نخورده و دوطرفه است.  @note    [EN] Wiring: STM32 PA9 (TX) -&gt; ESP RX, STM32 PA10 (RX) &lt;- ESP TX, common GND. STM32 PA8 drives ESP CH_PD/EN; this sketch never touches that line. Wi-Fi AP "ChangeOver-ESP", password "123456789", panel at http://192.168.4.1 No cloud: only MCU &lt;-&gt; ESP data exchange (flash is used only for the bench log file). Manual test mode (ID 19): a GET_PARAMS keepalive is sent every 1 s while manual mode is active (TLM flag b5 or param 19), also with a background tab (spec 19). Safety: if no browser has polled /t for 10 s (or none since the ESP booted), the ESP sends ID 19 = 0 every 1 s until the STM32 reports manual off, so a closed panel never leaves a channel on an unregulated duty; the STM32 3 s dead-man still covers an ESP hang or a broken link. [FA] سیم‌بندی: PA9 به RX ماژول، PA10 به TX ماژول، زمین مشترک. پایه ‎CH_PD/EN‎ را STM32 (PA8) کنترل می‌کند؛ این برنامه به آن دست نمی‌زند. وای‌فای "‎ChangeOver-ESP‎" با رمز "123456789"، پنل در http://192.168.4.1 بدون اینترنت: فقط تبادل داده بین MCU و ESP (فلش فقط برای فایل ثبت بنچ استفاده می‌شود). مود تست دستی (شناسه 19): تا وقتی مود دستی فعال است (پرچم b5 یا پارامتر 19) هر 1 ثانیه یک GET_PARAMS فرستاده می‌شود، حتی با تب پس‌زمینه (بخش 19 سند). ایمنی: اگر 10 ثانیه هیچ مرورگری /t را نخواند (یا از بوت ESP هنوز نخوانده باشد)، ESP هر 1 ثانیه شناسهٔ 19 = 0 را می‌فرستد تا STM32 خاموشی مود دستی را گزارش کند؛ پس پنل بسته هرگز کانال را روی duty بدون تنظیم رها نمی‌کند. هنگ ESP یا قطع لینک را ‎dead-man‎ سه‌ثانیه‌ای STM32 پوشش می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_font.h</t>
+          <t>esp_link_panel/panel_preview.html</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>.h</t>
+          <t>.html</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3187,14 +3187,14 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>plink_font.h - Vazirmatn subset font in PROGMEM.</t>
+          <t>ویرایش با کلیک (دستور کاربر): خودِ عدد همان کنترل است. تنها نشانه، زیرخط نقطه‌چین است - عددی که شبیه دکمه باشد دیگر مثل عدد خوانده نمی‌شود و کار اصلی این جدول خوانده‌شدن است.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_http.h</t>
+          <t>esp_link_panel/plink_config.h</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -3204,29 +3204,29 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>plink_http.h - HTTP handlers: / /t /s /m /benchlog (+info).</t>
+          <t>plink_config.h - link/message/param constants, bench CSV header, Wi-Fi/HTTP constants, parser states.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_link.h</t>
+          <t>esp_link_panel/plink_font.h</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -3236,29 +3236,29 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>plink_link.h - UART frame transmit/receive, TLM store, bench statistics window.</t>
+          <t>plink_font.h - Vazirmatn subset font in PROGMEM.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_panel.h</t>
+          <t>esp_link_panel/plink_http.h</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -3268,29 +3268,29 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>860</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>plink_panel.h - the web panel HTML in PROGMEM (single R"HTML" raw string).</t>
+          <t>plink_http.h - HTTP handlers: / /t /s /m /benchlog (+info).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_params.h</t>
+          <t>esp_link_panel/plink_link.h</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -3300,29 +3300,29 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>plink_params.h - ESP-side parameter envelopes (clamp mirror) + transmit priority order.</t>
+          <t>plink_link.h - UART frame transmit/receive, TLM store, bench statistics window.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>esp_link_panel/plink_state.h</t>
+          <t>esp_link_panel/plink_panel.h</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3347,24 +3347,24 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>plink_state.h - RX buffers, live TLM data, TX queue, bench window, HTTP server object.</t>
+          <t>plink_panel.h - the web panel HTML in PROGMEM (single R"HTML" raw string).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>tools/audit_consistency.py</t>
+          <t>esp_link_panel/plink_params.h</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3379,24 +3379,24 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>چرا این فایل هست تقریباً هر ایرادی که در این پروژه پیدا شده یک شکل داشته: یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. فقط جدول پارامترها در هشت فایل تکرار شده و هیچ‌چیز به هم وصلشان نمی‌کرد، پس تغییر در یک جا بی‌صدا بقیه را می‌پوساند. خواندن خط‌به‌خط این‌ها را نمی‌گیرد، چون هر فایل به‌تنهایی درست است و ایراد فقط «بین» فایل‌ها وجود دارد. پس این اسکریپت آن‌ها را با هم مقایسه می‌کند و قرار است به‌عنوان دروازه اجرا شود.  Run: python3 tools/audit_consistency.py """  import os import re import sys from pathlib import Path  ROOT = Path(__file__).resolve().parents[1]  FINDINGS = [] CHECKS = [0]   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def ok(cond, what, detail=""): """[EN] Record one invariant. / [FA] ثبت یک نامتغیر.""" CHECKS[0] += 1 if not cond: FINDINGS.append((what, detail)) return bool(cond)   def c_array(text, name): """[EN] Values of a C initialiser, comments stripped (they contain commas - that detail produced a false alarm in an earlier hand-written audit). [FA] مقادیر یک آرایهٔ C با حذف کامنت‌ها (کامنت‌ها کاما دارند و همین یک بار هشدار کاذب ساخت).""" m = re.search(re.escape(name) + r"\s*\[[^\]]*\]\s*=\s*\{(.*?)\}", text, re.S) if not m: return None body = re.sub(r"/\*.*?\</t>
+          <t>plink_params.h - ESP-side parameter envelopes (clamp mirror) + transmit priority order.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>tools/fix_rtl_comments.py</t>
+          <t>esp_link_panel/plink_state.h</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>.py</t>
+          <t>.h</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3411,14 +3411,14 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>بهداشت کامنت‌های راست‌به‌چپ.  کامنت فارسی یک پاراگراف راست‌به‌چپ است. اگر فرمول یا بازهٔ عددی بدون علامت جهت وسط آن بیفتد، الگوریتم bidi پرانتزها و علامت‌ها را جابه‌جا نشان می‌دهد و فرمول به‌هم می‌ریزد. راه‌حل یک کاراکتر است: هر رشتهٔ لاتین/ریاضی که عملگر دارد بین دو LRM بسته می‌شود تا مثل یک جزیرهٔ چپ‌به‌راست دیده شود.  فقط خط‌های کامنتی که حرف فارسی دارند دست می‌خورند. """  import re import sys import glob  LRM = "\u200e"  # [EN] Persian/Arabic letters. [FA] حروف فارسی. FA = re.compile(r"[\u0600-\u06FF]")  # [EN] A latin/arithmetic run: letters, digits, brackets, operators, dots. # [FA] رشتهٔ لاتین/ریاضی. RUN = re.compile(r"[A-Za-z0-9_][A-Za-z0-9_ \t()\[\]{}&lt;&gt;=+\-</t>
+          <t>plink_state.h - RX buffers, live TLM data, TX queue, bench window, HTTP server object.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>tools/make_module_state_machines.py</t>
+          <t>tools/audit_consistency.py</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3443,14 +3443,14 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>چرا این فایل هست تقریباً هر ایرادی که در این پروژه پیدا شده یک شکل داشته: یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. فقط جدول پارامترها در هشت فایل تکرار شده و هیچ‌چیز به هم وصلشان نمی‌کرد، پس تغییر در یک جا بی‌صدا بقیه را می‌پوساند. خواندن خط‌به‌خط این‌ها را نمی‌گیرد، چون هر فایل به‌تنهایی درست است و ایراد فقط «بین» فایل‌ها وجود دارد. پس این اسکریپت آن‌ها را با هم مقایسه می‌کند و قرار است به‌عنوان دروازه اجرا شود.  Run: python3 tools/audit_consistency.py """  import os import re import sys from pathlib import Path  ROOT = Path(__file__).resolve().parents[1]  FINDINGS = [] CHECKS = [0]   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def ok(cond, what, detail=""): """[EN] Record one invariant. / [FA] ثبت یک نامتغیر.""" CHECKS[0] += 1 if not cond: FINDINGS.append((what, detail)) return bool(cond)   def c_array(text, name): """[EN] Values of a C initialiser, comments stripped (they contain commas - that detail produced a false alarm in an earlier hand-written audit). [FA] مقادیر یک آرایهٔ C با حذف کامنت‌ها (کامنت‌ها کاما دارند و همین یک بار هشدار کاذب ساخت).""" m = re.search(re.escape(name) + r"\s*\[[^\]]*\]\s*=\s*\{(.*?)\}", text, re.S) if not m: return None body = re.sub(r"/\*.*?\</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>tools/make_panel_preview.py</t>
+          <t>tools/check_diag_fault_bits.py</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3475,14 +3475,14 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>چرا پنل داخل فرم‌ور به‌صورت رشتهٔ PROGMEM است، پس تنها راه دیدنش فلش‌کردن ESP یا اجرای سرور Node بود. این اسکریپت یک فایل html خودکفا می‌سازد که مستقیم از روی دیسک باز می‌شود - بدون سرور، بدون برد، بدون شبکه. فایل «تولید» می‌شود و هرگز دستی ویرایش نمی‌شود: مارک‌آپ عیناً از plink_panel.h بیرون کشیده می‌شود، پس پیش‌نمایش نمی‌تواند از فرم‌ور جدا بیفتد. هر جدولی که در این پروژه دستی تکرار شده، بالاخره کهنه شده است. تنها چیزی که اضافه می‌شود یک shim برای fetch است که پیش از اسکریپت خود پنل تزریق می‌شود و /t و /m را از یک شبیه‌سازی کوچک چرخهٔ شارژ جواب می‌دهد.  Run: python3 tools/make_panel_preview.py Out: esp_link_panel/panel_preview.html """  import json import re import sys from pathlib import Path  ROOT = Path(__file__).resolve().parents[1] SRC = ROOT / "esp_link_panel" / "plink_panel.h" FONT = ROOT / "esp_link_panel" / "plink_font.h" PREV = ROOT / "tools" / "panel_preview_server.js" CFG = ROOT / "esp_link_panel" / "plink_config.h" BSP = ROOT / "Firmware" / "Bsp" / "Src" / "bsp_measurement.c" OUT = ROOT / "esp_link_panel" / "panel_preview.html"   def c_define(path, name): """[EN] One unsigned #define, read from the firmware. Dies loudly if the name moved, because a silently-missing constant is how the shim drifted away from the frame in the first place. [FA] یک #define بدون علامت از فرم‌ور. اگر نام جابه‌جا شود با صدای بلند می‌میرد، چون ثابتی که بی‌صدا غایب شود همان راهی است که شیم از ابتدا از قاب فاصله گرفت.""" m = re.search(r"#define\s+" + name + r"\s+(\d+)u?(?![0-9A-Za-z_])", path.read_text(encoding="utf-8")) if not m: sys.exit("could not read %s from %s" % (name, path.name)) return int(m.group(1))   def tlm_fields(): """[EN] Telemetry width, from the firmware header. / [FA] عرض تله‌متری.""" return c_define(CFG, "ESP_LINK_TLM_FIELD_COUNT")   def divider_scales(): """[EN] mV per ADC count for the 24 V and 12 V nets, derived from the BSP resistors exactly as bsp_measurement.c derives them, so the simulated raw counts reconstruct the simulated volts. [FA] میلی‌ولت بر هر شمارش ADC برای نت‌های 24 و 12 ولت، از مقاومت‌های BSP دقیقاً به همان روش bsp_measurement.c مشتق می‌شود تا شمارش خام شبیه‌سازی همان ولتاژ شبیه‌سازی را بازبسازد.""" vref = c_define(BSP, "BSP_MEASUREMENT_VREF_MV") full = c_define(BSP, "BSP_MEASUREMENT_ADC_FULL_SCALE") shunt = c_define(BSP, "BSP_MEASUREMENT_SENSE_SHUNT_OHMS") top24 = c_define(BSP, "BSP_MEASUREMENT_SENSE_TOP_24V_OHMS") top12 = c_define(BSP, "BSP_MEASUREMENT_DIV12_TOP_OHMS") lsb = vref / full return (lsb * (top24 + shunt) / shunt, lsb * (top12 + shunt) / shunt, round(1200 / vref * full), vref)   def panel_html(): """[EN] The raw string, verbatim. / [FA] رشتهٔ خام، عیناً.""" s = SRC.read_text(encoding="utf-8") a = s.index('R"HTML(') + len('R"HTML(') b = s.rindex(')HTML"') return s[a:b]   def font_css(): """[EN] Extract the same embedded Vazirmatn CSS served by the ESP. [FA] همان CSS فونت وزیرمتن جاسازی‌شده در ESP را بیرون می‌کشد.""" s = FONT.read_text(encoding="utf-8") start = s.index("static const char ESP_PANEL_FONT_CSS") eq = s.index("=", start) + 1 end = s.index(";\n", eq) block = s[eq:end] literals = re.findall(r'"(?:\\.|[^"\\])*"', block) return "".join(json.loads(x) for x in literals)   def factory_params(): """[EN] Boot defaults, taken from the preview server so there is ONE list, not a third hand-written copy. tools/audit_consistency.py already pins that list against the firmware. [FA] پیش‌فرض‌ها از سرور پیش‌نمایش خوانده می‌شوند تا نسخهٔ دستی سومی ساخته نشود؛ ممیز خودکار همان فهرست را در برابر فرم‌ور قفل کرده است.""" js = PREV.read_text(encoding="utf-8") m = re.search(r"const P = \[(.*?)\];", js, re.S) if not m: sys.exit("could not read the default parameter list from the preview server") body = re.sub(r"/\*.*?\</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>tools/make_program_map.py</t>
+          <t>tools/fix_rtl_comments.py</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3507,14 +3507,14 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>ساخت فایل Documentation/Program_Map.xlsx - کل برنامه روی جدول: هر فایل سورس و نقش آن، هر تابع با @brief خودش، همهٔ 143 شناسهٔ سیم ESP با نوع/واحد/پیش‌فرض/بازه/ماندگاری، نگاشت پایه‌های MCU با قطبیت و سطح امن، نقشهٔ فلش داخلی، و دروازه‌هایی که همهٔ این‌ها را چک می‌کنند.  چرا: در این پروژه یک شکل ایراد بارها تکرار شده - یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. جدولی که «با ابزار» ساخته شود نمی‌تواند کهنه شود: همه‌چیز پایین در زمان ساخت از هدرهای فرم‌ور خوانده می‌شود، پس کتاب یک «نما» از کد است، نه کپی دوم آن. """  import pathlib import re import sys  from openpyxl import Workbook from openpyxl.styles import Alignment, Border, Font, PatternFill, Side from openpyxl.utils import get_column_letter  ROOT = pathlib.Path(__file__).resolve().parents[1] OUT = ROOT / "Documentation" / "Program_Map.xlsx"  FONT = "Vazirmatn" C_TITLE = "1F3864" C_HEAD = "2F5597" C_BAND = "D9E2F3" PALETTE = { "ok": "C6EFCE",      # تأییدشده / جاری "warn": "FFE699",    # کهنه / نیازمند توجه "bad": "FFC7CE",     # ایراد "info": "DDEBF7",    # اطلاعاتی "idle": "EDEDED",    # خاموش / غیرفعال "act": "FCE4D6",     # فعال } thin = Side(style="thin", color="9DB7E8") BORDER = Border(left=thin, right=thin, top=thin, bottom=thin)   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def sheet(wb, name, title, headers, rows, widths): """[EN] One RTL sheet in the house style. / [FA] یک برگهٔ راست‌به‌چپ با سبک پروژه.""" ws = wb.create_sheet(name) ws.sheet_view.rightToLeft = True ws.freeze_panes = "A3"  ncol = len(headers) ws.merge_cells(start_row=1, start_column=1, end_row=1, end_column=ncol) tc = ws.cell(row=1, column=1, value=title) tc.font = Font(name=FONT, size=14, bold=True, color="FFFFFF") tc.fill = PatternFill("solid", fgColor=C_TITLE) tc.alignment = Alignment(horizontal="center", vertical="center") ws.row_dimensions[1].height = 30  for c, h in enumerate(headers, start=1): cell = ws.cell(row=2, column=c, value=h) cell.font = Font(name=FONT, size=11, bold=True, color="FFFFFF") cell.fill = PatternFill("solid", fgColor=C_HEAD) cell.alignment = Alignment(horizontal="center", vertical="center", wrap_text=True) cell.border = BORDER ws.row_dimensions[2].height = 28  for r, row in enumerate(rows, start=3): tone = row[-1] values = row[:-1] fill = PatternFill("solid", fgColor=PALETTE.get(tone, "FFFFFF")) if tone else None for c, v in enumerate(values, start=1): cell = ws.cell(row=r, column=c, value=v) cell.font = Font(name=FONT, size=10) cell.alignment = Alignment(horizontal="right", vertical="top", wrap_text=True) cell.border = BORDER if fill is not None: cell.fill = fill elif r % 2 == 1: cell.fill = PatternFill("solid", fgColor=C_BAND)  for c, w in enumerate(widths, start=1): ws.column_dimensions[get_column_letter(c)].width = w ws.sheet_properties.tabColor = C_HEAD return ws   # --------------------------------------------------------------- parsing  def doc_block_brief(text, at): """[EN] Brief of the doc block that sits directly above line `at` (0-based). Returns (en, fa) or ('', ''). [FA] خلاصهٔ بلوک مستندِ بالای خط داده‌شده.""" lines = text.split("\n") end = None block = None for i in range(at - 1, max(-1, at - 60), -1): t = lines[i].strip() if t.startswith("</t>
+          <t>بهداشت کامنت‌های راست‌به‌چپ.  کامنت فارسی یک پاراگراف راست‌به‌چپ است. اگر فرمول یا بازهٔ عددی بدون علامت جهت وسط آن بیفتد، الگوریتم bidi پرانتزها و علامت‌ها را جابه‌جا نشان می‌دهد و فرمول به‌هم می‌ریزد. راه‌حل یک کاراکتر است: هر رشتهٔ لاتین/ریاضی که عملگر دارد بین دو LRM بسته می‌شود تا مثل یک جزیرهٔ چپ‌به‌راست دیده شود.  فقط خط‌های کامنتی که حرف فارسی دارند دست می‌خورند. """  import re import sys import glob  LRM = "\u200e"  # [EN] Persian/Arabic letters. [FA] حروف فارسی. FA = re.compile(r"[\u0600-\u06FF]")  # [EN] A latin/arithmetic run: letters, digits, brackets, operators, dots. # [FA] رشتهٔ لاتین/ریاضی. RUN = re.compile(r"[A-Za-z0-9_][A-Za-z0-9_ \t()\[\]{}&lt;&gt;=+\-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>tools/make_state_machine_xlsx.py</t>
+          <t>tools/make_module_state_machines.py</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>654</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3546,7 +3546,7 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>tools/measure_flash.py</t>
+          <t>tools/make_panel_preview.py</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>258</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>اندازه‌گیری حجم ایمیج STM32 روی هاست، تا «هنوز در ناحیهٔ فلش برنامهٔ لینکر جا می‌شود یا نه» سؤالی نباشد که فقط IDE ویندوز جوابش را بداند. ناحیه امروز 56K است (پیش از رزرو بلوک‌های NVM برابر 62K و پیش از جابه‌جایی بانک پارامترها در v1.80 برابر 60K)؛ بودجه اینجا دوباره تایپ نمی‌شود - اسکریپت لینکر خود پروژه خوانده می‌شود، پس این ابزار با تغییر اندازهٔ ناحیه خودش را هم‌گام می‌کند.  در این سندباکس arm-none-eabi-gcc نیست، پس سورس‌ها با توولچین LLVM داخل بستهٔ ziglang برای Thumb/Cortex-M3 ساخته می‌شوند. عدد مطلق با گزارش CubeIDE یکی نخواهد بود - کامپایلر فرق دارد، libc فرق دارد، و startup و جدول بردار اینجا نیست. کار این ابزار «اختلاف» است: درخت را دو بار بساز، یک‌بار پیش از تغییر و یک‌بار پس از آن؛ اختلاف حجم کد Thumb قابل‌اعتماد است. تصمیم «780 بایت سرریز» دقیقاً به همین نیاز دارد، و حدس‌زدن از روی سورس همان کاری است که باعث می‌شود آدم چیز اشتباه را حذف کند. """ import json import re import subprocess import sys from pathlib import Path  ROOT = Path(__file__).resolve().parent.parent TARGET = ["-target", "thumb-linux-musleabi", "-mcpu=cortex_m3"]  INCLUDES = [ "CubeIDE/Core/Inc", "CubeIDE/Drivers/CMSIS/Include", "CubeIDE/Drivers/CMSIS/Device/ST/STM32F1xx/Include", "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Inc", "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Inc/Legacy", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/include", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/CMSIS_RTOS_V2", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/portable/GCC/ARM_CM3", "Firmware/App/Inc", "Firmware/Bsp/Inc", "Firmware/Config/Inc", "Firmware/Rtos/Inc", "Firmware/Modules/Ui", "Firmware/Modules/Measurement", "Firmware/Modules/Protection", "Firmware/Modules/Changeover", "Firmware/Modules/Charger", "Firmware/Modules/Jitter", "Firmware/Modules/Fault", "Firmware/Modules/EspLink", "Firmware/Modules/McuPowerPath", # [EN] v1.53: the Imbalance module was missing, so five translation units #      failed and the "total" silently excluded them. # [FA] ماژول Imbalance جا افتاده بود و پنج فایل بی‌صدا از مجموع می‌افتادند. "Firmware/Modules/Imbalance", # [EN] v1.66: the CalLut module (its own flash block for the pushed bench #      table) joins the build; without this include path its translation #      unit would fail and drop out of the total silently. # [FA] v1.66: ماژول CalLut به بیلد اضافه شد؛ بدون این مسیر، فایل آن #      بی‌صدا از مجموع می‌افتاد. "Firmware/Modules/CalLut", ]   def sources(): """[EN] The same set CubeIDE compiles. / [FA] همان مجموعه‌ای که CubeIDE می‌سازد.""" out = [] out += sorted((ROOT / "CubeIDE/Core/Src").glob("*.c")) out += sorted((ROOT / "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Src").glob("*.c")) frt = ROOT / "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source" out += sorted(frt.glob("*.c")) out += sorted((frt / "CMSIS_RTOS_V2").glob("*.c")) out += [frt / "portable/GCC/ARM_CM3/port.c"]  # static allocation only: no heap_4 out += sorted(f for f in (ROOT / "Firmware").rglob("*.c") if "Tester" not in f.parts)   # [EN] host tests are not flashed # [FA] تست‌های هاست روی برد نمی‌روند return [p for p in out if p.is_file()]   def section_sizes(obj): """[EN] Flash-resident sections only. / [FA] فقط بخش‌هایی که روی فلش می‌نشینند.""" from elftools.elf.elffile import ELFFile text = rodata = data = 0 with open(obj, "rb") as fh: for sec in ELFFile(fh).iter_sections(): name, size = sec.name, sec["sh_size"] if not (sec["sh_flags"] &amp; 0x2):          # SHF_ALLOC continue if name.startswith(".text"): text += size elif name.startswith(".rodata") or name.startswith(".srodata"): rodata += size elif name.startswith(".data") and ".rel" not in name: data += size return text, rodata, data   def build(outdir): outdir = Path(outdir) outdir.mkdir(parents=True, exist_ok=True) rows, failures = [], [] for src in sources(): rel = src.relative_to(ROOT) obj = outdir / (str(rel).replace("/", "_") + ".o") cmd = (["python3", "-m", "ziglang", "cc"] + TARGET + ["-c", "-Os", "-ffunction-sections", "-fdata-sections", "-fno-common", "-w", "-DSTM32F103xB", "-DUSE_HAL_DRIVER"] + [f"-I{ROOT / i}" for i in INCLUDES] + [str(src), "-o", str(obj)]) res = subprocess.run(cmd, capture_output=True, text=True) if res.returncode != 0: failures.append((str(rel), res.stderr.strip().splitlines()[:1])) continue t, r, d = section_sizes(obj) rows.append({"file": str(rel), "text": t, "rodata": r, "data": d, "total": t + r + d}) return rows, failures    def lld_linker_script(outdir): """[EN] The project's own script, with two things lld will not take: a MEMORY block referenced before it is defined, and the GCC-11 READONLY attribute. Hoisted and stripped here, never in the project file. [FA] اسکریپت خود پروژه، با دو چیزی که lld نمی‌پذیرد: بلوک MEMORY که پیش از تعریف ارجاع داده شده و صفت READONLY مخصوص GCC 11. اینجا جابه‌جا و حذف می‌شوند، نه در فایل پروژه.""" import re as _re src = (ROOT / "CubeIDE/STM32CubeIDE/STM32F103C8TX_FLASH.ld").read_text() mem = _re.search(r"MEMORY\s*\{.*?\n\}", src, _re.S).group(0) out = src.replace(mem, "/* hoisted for lld</t>
+          <t>چرا پنل داخل فرم‌ور به‌صورت رشتهٔ PROGMEM است، پس تنها راه دیدنش فلش‌کردن ESP یا اجرای سرور Node بود. این اسکریپت یک فایل html خودکفا می‌سازد که مستقیم از روی دیسک باز می‌شود - بدون سرور، بدون برد، بدون شبکه. فایل «تولید» می‌شود و هرگز دستی ویرایش نمی‌شود: مارک‌آپ عیناً از plink_panel.h بیرون کشیده می‌شود، پس پیش‌نمایش نمی‌تواند از فرم‌ور جدا بیفتد. هر جدولی که در این پروژه دستی تکرار شده، بالاخره کهنه شده است. تنها چیزی که اضافه می‌شود یک shim برای fetch است که پیش از اسکریپت خود پنل تزریق می‌شود و /t و /m را از یک شبیه‌سازی کوچک چرخهٔ شارژ جواب می‌دهد.  Run: python3 tools/make_panel_preview.py Out: esp_link_panel/panel_preview.html """  import json import re import sys from pathlib import Path  ROOT = Path(__file__).resolve().parents[1] SRC = ROOT / "esp_link_panel" / "plink_panel.h" FONT = ROOT / "esp_link_panel" / "plink_font.h" PREV = ROOT / "tools" / "panel_preview_server.js" CFG = ROOT / "esp_link_panel" / "plink_config.h" BSP = ROOT / "Firmware" / "Bsp" / "Src" / "bsp_measurement.c" OUT = ROOT / "esp_link_panel" / "panel_preview.html"   def c_define(path, name): """[EN] One unsigned #define, read from the firmware. Dies loudly if the name moved, because a silently-missing constant is how the shim drifted away from the frame in the first place. [FA] یک #define بدون علامت از فرم‌ور. اگر نام جابه‌جا شود با صدای بلند می‌میرد، چون ثابتی که بی‌صدا غایب شود همان راهی است که شیم از ابتدا از قاب فاصله گرفت.""" m = re.search(r"#define\s+" + name + r"\s+(\d+)u?(?![0-9A-Za-z_])", path.read_text(encoding="utf-8")) if not m: sys.exit("could not read %s from %s" % (name, path.name)) return int(m.group(1))   def tlm_fields(): """[EN] Telemetry width, from the firmware header. / [FA] عرض تله‌متری.""" return c_define(CFG, "ESP_LINK_TLM_FIELD_COUNT")   def divider_scales(): """[EN] mV per ADC count for the 24 V and 12 V nets, derived from the BSP resistors exactly as bsp_measurement.c derives them, so the simulated raw counts reconstruct the simulated volts. [FA] میلی‌ولت بر هر شمارش ADC برای نت‌های 24 و 12 ولت، از مقاومت‌های BSP دقیقاً به همان روش bsp_measurement.c مشتق می‌شود تا شمارش خام شبیه‌سازی همان ولتاژ شبیه‌سازی را بازبسازد.""" vref = c_define(BSP, "BSP_MEASUREMENT_VREF_MV") full = c_define(BSP, "BSP_MEASUREMENT_ADC_FULL_SCALE") shunt = c_define(BSP, "BSP_MEASUREMENT_SENSE_SHUNT_OHMS") top24 = c_define(BSP, "BSP_MEASUREMENT_SENSE_TOP_24V_OHMS") top12 = c_define(BSP, "BSP_MEASUREMENT_DIV12_TOP_OHMS") lsb = vref / full return (lsb * (top24 + shunt) / shunt, lsb * (top12 + shunt) / shunt, round(1200 / vref * full), vref)   def panel_html(): """[EN] The raw string, verbatim. / [FA] رشتهٔ خام، عیناً.""" s = SRC.read_text(encoding="utf-8") a = s.index('R"HTML(') + len('R"HTML(') b = s.rindex(')HTML"') return s[a:b]   def font_css(): """[EN] Extract the same embedded Vazirmatn CSS served by the ESP. [FA] همان CSS فونت وزیرمتن جاسازی‌شده در ESP را بیرون می‌کشد.""" s = FONT.read_text(encoding="utf-8") start = s.index("static const char ESP_PANEL_FONT_CSS") eq = s.index("=", start) + 1 end = s.index(";\n", eq) block = s[eq:end] literals = re.findall(r'"(?:\\.|[^"\\])*"', block) return "".join(json.loads(x) for x in literals)   def factory_params(): """[EN] Boot defaults, taken from the preview server so there is ONE list, not a third hand-written copy. tools/audit_consistency.py already pins that list against the firmware. [FA] پیش‌فرض‌ها از سرور پیش‌نمایش خوانده می‌شوند تا نسخهٔ دستی سومی ساخته نشود؛ ممیز خودکار همان فهرست را در برابر فرم‌ور قفل کرده است.""" js = PREV.read_text(encoding="utf-8") m = re.search(r"const P = \[(.*?)\];", js, re.S) if not m: sys.exit("could not read the default parameter list from the preview server") body = re.sub(r"/\*.*?\</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>tools/measure_ram.py</t>
+          <t>tools/make_program_map.py</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>475</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -3603,37 +3603,133 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ساخت فایل Documentation/Program_Map.xlsx - کل برنامه روی جدول: هر فایل سورس و نقش آن، هر تابع با @brief خودش، همهٔ 143 شناسهٔ سیم ESP با نوع/واحد/پیش‌فرض/بازه/ماندگاری، نگاشت پایه‌های MCU با قطبیت و سطح امن، نقشهٔ فلش داخلی، و دروازه‌هایی که همهٔ این‌ها را چک می‌کنند.  چرا: در این پروژه یک شکل ایراد بارها تکرار شده - یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. جدولی که «با ابزار» ساخته شود نمی‌تواند کهنه شود: همه‌چیز پایین در زمان ساخت از هدرهای فرم‌ور خوانده می‌شود، پس کتاب یک «نما» از کد است، نه کپی دوم آن. """  import pathlib import re import sys  from openpyxl import Workbook from openpyxl.styles import Alignment, Border, Font, PatternFill, Side from openpyxl.utils import get_column_letter  ROOT = pathlib.Path(__file__).resolve().parents[1] OUT = ROOT / "Documentation" / "Program_Map.xlsx"  FONT = "Vazirmatn" C_TITLE = "1F3864" C_HEAD = "1F4E79" C_BAND = "D9E2F3" PALETTE = { "ok": "C6EFCE",      # تأییدشده / جاری "warn": "FFE699",    # کهنه / نیازمند توجه "bad": "FFC7CE",     # ایراد "info": "DDEBF7",    # اطلاعاتی "idle": "EDEDED",    # خاموش / غیرفعال "act": "FCE4D6",     # فعال } thin = Side(style="thin", color="9DB7E8") BORDER = Border(left=thin, right=thin, top=thin, bottom=thin)   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def sheet(wb, name, title, headers, rows, widths): """[EN] One RTL sheet in the house style. / [FA] یک برگهٔ راست‌به‌چپ با سبک پروژه.""" ws = wb.create_sheet(name) ws.sheet_view.rightToLeft = True ws.freeze_panes = "A3"  ncol = len(headers) ws.merge_cells(start_row=1, start_column=1, end_row=1, end_column=ncol) tc = ws.cell(row=1, column=1, value=title) tc.font = Font(name=FONT, size=14, bold=True, color="FFFFFF") tc.fill = PatternFill("solid", fgColor=C_TITLE) tc.alignment = Alignment(horizontal="center", vertical="center") ws.row_dimensions[1].height = 30  for c, h in enumerate(headers, start=1): cell = ws.cell(row=2, column=c, value=h) cell.font = Font(name=FONT, size=11, bold=True, color="FFFFFF") cell.fill = PatternFill("solid", fgColor=C_HEAD) cell.alignment = Alignment(horizontal="center", vertical="center", wrap_text=True) cell.border = BORDER ws.row_dimensions[2].height = 28  for r, row in enumerate(rows, start=3): tone = row[-1] values = row[:-1] fill = PatternFill("solid", fgColor=PALETTE.get(tone, "FFFFFF")) if tone else None for c, v in enumerate(values, start=1): cell = ws.cell(row=r, column=c, value=v) cell.font = Font(name=FONT, size=10) cell.alignment = Alignment(horizontal="right", vertical="top", wrap_text=True) cell.border = BORDER if fill is not None: cell.fill = fill elif r % 2 == 1: cell.fill = PatternFill("solid", fgColor=C_BAND)  for c, w in enumerate(widths, start=1): ws.column_dimensions[get_column_letter(c)].width = w ws.sheet_properties.tabColor = C_HEAD return ws   # --------------------------------------------------------------- parsing  def doc_block_brief(text, at): """[EN] Brief of the doc block that sits directly above line `at` (0-based). Returns (en, fa) or ('', ''). [FA] خلاصهٔ بلوک مستندِ بالای خط داده‌شده.""" lines = text.split("\n") end = None block = None for i in range(at - 1, max(-1, at - 60), -1): t = lines[i].strip() if t.startswith("</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
+          <t>tools/make_state_machine_xlsx.py</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>.py</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>tools/measure_flash.py</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>.py</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>اندازه‌گیری حجم ایمیج STM32 روی هاست، تا «هنوز در ناحیهٔ فلش برنامهٔ لینکر جا می‌شود یا نه» سؤالی نباشد که فقط IDE ویندوز جوابش را بداند. ناحیه امروز 56K است (پیش از رزرو بلوک‌های NVM برابر 62K و پیش از جابه‌جایی بانک پارامترها در v1.80 برابر 60K)؛ بودجه اینجا دوباره تایپ نمی‌شود - اسکریپت لینکر خود پروژه خوانده می‌شود، پس این ابزار با تغییر اندازهٔ ناحیه خودش را هم‌گام می‌کند.  در این سندباکس arm-none-eabi-gcc نیست، پس سورس‌ها با توولچین LLVM داخل بستهٔ ziglang برای Thumb/Cortex-M3 ساخته می‌شوند. عدد مطلق با گزارش CubeIDE یکی نخواهد بود - کامپایلر فرق دارد، libc فرق دارد، و startup و جدول بردار اینجا نیست. کار این ابزار «اختلاف» است: درخت را دو بار بساز، یک‌بار پیش از تغییر و یک‌بار پس از آن؛ اختلاف حجم کد Thumb قابل‌اعتماد است. تصمیم «780 بایت سرریز» دقیقاً به همین نیاز دارد، و حدس‌زدن از روی سورس همان کاری است که باعث می‌شود آدم چیز اشتباه را حذف کند. """ import json import re import subprocess import sys from pathlib import Path  ROOT = Path(__file__).resolve().parent.parent TARGET = ["-target", "thumb-linux-musleabi", "-mcpu=cortex_m3"]  INCLUDES = [ "CubeIDE/Core/Inc", "CubeIDE/Drivers/CMSIS/Include", "CubeIDE/Drivers/CMSIS/Device/ST/STM32F1xx/Include", "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Inc", "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Inc/Legacy", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/include", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/CMSIS_RTOS_V2", "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source/portable/GCC/ARM_CM3", "Firmware/App/Inc", "Firmware/Bsp/Inc", "Firmware/Config/Inc", "Firmware/Rtos/Inc", "Firmware/Modules/Ui", "Firmware/Modules/Measurement", "Firmware/Modules/Protection", "Firmware/Modules/Changeover", "Firmware/Modules/Charger", "Firmware/Modules/Jitter", "Firmware/Modules/Fault", "Firmware/Modules/EspLink", "Firmware/Modules/McuPowerPath", # [EN] v1.53: the Imbalance module was missing, so five translation units #      failed and the "total" silently excluded them. # [FA] ماژول Imbalance جا افتاده بود و پنج فایل بی‌صدا از مجموع می‌افتادند. "Firmware/Modules/Imbalance", # [EN] v1.66: the CalLut module (its own flash block for the pushed bench #      table) joins the build; without this include path its translation #      unit would fail and drop out of the total silently. # [FA] v1.66: ماژول CalLut به بیلد اضافه شد؛ بدون این مسیر، فایل آن #      بی‌صدا از مجموع می‌افتاد. "Firmware/Modules/CalLut", # [EN] 2026-10-15: the Diag module was missing, so four translation units #      that include diag.h (app.c, charger.c, esp_link.c, task_control.c) #      failed and the link died on undefined symbols - measure_ram.py #      could not measure RAM at all. Same fix as v1.53/v1.66 above. # [FA] ماژول Diag جا افتاده بود و چهار فایل بی‌صدا #      می‌افتادند و لینک می‌مرد؛ اصلاح هم‌جنسِ موارد بالا. "Firmware/Modules/Diag", ]   def sources(): """[EN] The same set CubeIDE compiles. / [FA] همان مجموعه‌ای که CubeIDE می‌سازد.""" out = [] out += sorted((ROOT / "CubeIDE/Core/Src").glob("*.c")) out += sorted((ROOT / "CubeIDE/Drivers/STM32F1xx_HAL_Driver/Src").glob("*.c")) frt = ROOT / "CubeIDE/Middlewares/Third_Party/FreeRTOS/Source" out += sorted(frt.glob("*.c")) out += sorted((frt / "CMSIS_RTOS_V2").glob("*.c")) out += [frt / "portable/GCC/ARM_CM3/port.c"]  # static allocation only: no heap_4 out += sorted(f for f in (ROOT / "Firmware").rglob("*.c") if "Tester" not in f.parts)   # [EN] host tests are not flashed # [FA] تست‌های هاست روی برد نمی‌روند return [p for p in out if p.is_file()]   def section_sizes(obj): """[EN] Flash-resident sections only. / [FA] فقط بخش‌هایی که روی فلش می‌نشینند.""" from elftools.elf.elffile import ELFFile text = rodata = data = 0 with open(obj, "rb") as fh: for sec in ELFFile(fh).iter_sections(): name, size = sec.name, sec["sh_size"] if not (sec["sh_flags"] &amp; 0x2):          # SHF_ALLOC continue if name.startswith(".text"): text += size elif name.startswith(".rodata") or name.startswith(".srodata"): rodata += size elif name.startswith(".data") and ".rel" not in name: data += size return text, rodata, data   def build(outdir): outdir = Path(outdir) outdir.mkdir(parents=True, exist_ok=True) rows, failures = [], [] for src in sources(): rel = src.relative_to(ROOT) obj = outdir / (str(rel).replace("/", "_") + ".o") cmd = (["python3", "-m", "ziglang", "cc"] + TARGET + ["-c", "-Os", "-ffunction-sections", "-fdata-sections", "-fno-common", "-w", "-DSTM32F103xB", "-DUSE_HAL_DRIVER"] + [f"-I{ROOT / i}" for i in INCLUDES] + [str(src), "-o", str(obj)]) res = subprocess.run(cmd, capture_output=True, text=True) if res.returncode != 0: failures.append((str(rel), res.stderr.strip().splitlines()[:1])) continue t, r, d = section_sizes(obj) rows.append({"file": str(rel), "text": t, "rodata": r, "data": d, "total": t + r + d}) return rows, failures    def lld_linker_script(outdir): """[EN] The project's own script, with two things lld will not take: a MEMORY block referenced before it is defined, and the GCC-11 READONLY attribute. Hoisted and stripped here, never in the project file. [FA] اسکریپت خود پروژه، با دو چیزی که lld نمی‌پذیرد: بلوک MEMORY که پیش از تعریف ارجاع داده شده و صفت READONLY مخصوص GCC 11. اینجا جابه‌جا و حذف می‌شوند، نه در فایل پروژه.""" import re as _re src = (ROOT / "CubeIDE/STM32CubeIDE/STM32F103C8TX_FLASH.ld").read_text() mem = _re.search(r"MEMORY\s*\{.*?\n\}", src, _re.S).group(0) out = src.replace(mem, "/* hoisted for lld</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>tools/measure_ram.py</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>.py</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
           <t>tools/stamp_panel.py</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>.py</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3650,11 +3746,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3716,7 +3812,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -3743,7 +3839,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -4418,7 +4514,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>367</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -4430,7 +4526,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_ChainDeltaMa</t>
+          <t>func__BspMeasurement_ChainDeltaTenthMa</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4445,12 +4541,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>515</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>round(BSPfull(high) - BSPfull(low)) in mA, one rounding. The difference is taken on the exact numerators, so it is exact. [‎FA] round(BSPfull(high) - BSPfull(low))‎ بر حسب mA با یک رُند. تفاضل روی صورت‌های دقیق گرفته می‌شود، پس دقیق است.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4568,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>443</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4499,7 +4595,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4526,7 +4622,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4553,7 +4649,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>570</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -4565,7 +4661,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_Current1DeltaMa</t>
+          <t>func__BspMeasurement_Current1DeltaTenthMa</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -4580,12 +4676,12 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>542</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>تفاضل زنجیرهٔ کانال 1 (برای برون‌یابی بالای آخرین لنگر جدول): ‎round(BSPfull(high) - BSPfull(low))‎ بر حسب mA. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4703,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4619,7 +4715,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>func__BspMeasurement_Current2DeltaMa</t>
+          <t>func__BspMeasurement_Current2DeltaTenthMa</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -4634,7 +4730,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>551</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -4661,7 +4757,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -4688,7 +4784,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -4715,7 +4811,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>674</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -4742,7 +4838,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>484</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -4769,7 +4865,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>640</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4796,7 +4892,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -4823,7 +4919,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -4850,7 +4946,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -4877,7 +4973,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -5228,7 +5324,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>380</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -5255,7 +5351,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>429</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -5309,7 +5405,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>572</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5390,7 +5486,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>367</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -5417,7 +5513,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5444,7 +5540,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>393</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -5471,7 +5567,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -5498,7 +5594,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -5525,7 +5621,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -5552,7 +5648,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -5579,7 +5675,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>438</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -5606,7 +5702,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>478</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -5633,7 +5729,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>530</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5660,7 +5756,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -5687,7 +5783,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -5714,7 +5810,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -5741,7 +5837,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>524</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -5768,7 +5864,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>542</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -5795,7 +5891,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>536</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -5822,7 +5918,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>854</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -5849,7 +5945,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>935</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -5876,7 +5972,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -5903,7 +5999,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -5930,7 +6026,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -5957,7 +6053,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -5984,7 +6080,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -6011,7 +6107,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6038,7 +6134,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -6065,7 +6161,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -6092,7 +6188,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -6119,7 +6215,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -6146,7 +6242,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -6173,7 +6269,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -6200,7 +6296,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -6227,7 +6323,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -6254,7 +6350,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>632</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -6281,7 +6377,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>371</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -6308,7 +6404,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -6335,7 +6431,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -6362,7 +6458,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -6389,7 +6485,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -6416,7 +6512,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -6443,7 +6539,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>422</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -6470,7 +6566,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -6497,7 +6593,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -6524,7 +6620,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -6551,7 +6647,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -6578,7 +6674,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -6605,7 +6701,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -6632,7 +6728,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -6659,7 +6755,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -6686,7 +6782,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -6713,7 +6809,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -6740,7 +6836,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -6767,7 +6863,7 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -6794,7 +6890,7 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>679</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -6821,7 +6917,7 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -6848,7 +6944,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -6860,7 +6956,7 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelActive</t>
+          <t>func__Charger_IsAnyChannelInThermalRest</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -6875,19 +6971,19 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
+          <t>آیا کانالی در استراحت حرارتی است (1 ساعت ماکس -&gt; 10 دقیقه). برای نمایش چشمک زرد در UI استفاده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChannelInstalled</t>
+          <t>func__Charger_IsChannelActive</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -6897,24 +6993,24 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>کانالِ داده‌شده (0 = شارژر 1 / باتری بالا، 1 = شارژر 2 / باتری پایین) واقعاً پمپ می‌کند؟ نصب‌شده و در BULK یا ABSORB - همان محمولِ IsAnyChannelActive، تجزیه‌شده به‌ازای کانال (v1.21، دستور کاربر 2026-09-28) تا قانون پمپِ فالت هر نیم را با شارژر خودش مسلح کند: کانال پارک‌شده پمپی ندارد پس نیمش نمی‌تواند تا آستانهٔ قطع بالا پرود.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsChargeComplete</t>
+          <t>func__Charger_IsChannelInstalled</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -6924,24 +7020,24 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>469</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsManualTestModeActive</t>
+          <t>func__Charger_IsChargeComplete</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
@@ -6956,19 +7052,19 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
+          <t>شارژ همهٔ کانال‌های مربوط (نصب+فعال) کامل شده؟ دست‌کم یکی هست و همه در FLOATاند. کانال غیرفعال/نصب‌نشده کنار گذاشته می‌شود و مانع نیست.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsRelayOpen</t>
+          <t>func__Charger_IsManualTestModeActive</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -6983,19 +7079,19 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
+          <t>پرچم «فعالِ» مود دستی (مالکش تسک شارژر؛ تله‌متری b5 و ماژول Fault برای فریز کردن تشخیص قطع باتری استفاده‌اش می‌کنند).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsSuspended</t>
+          <t>func__Charger_IsRelayOpen</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -7010,19 +7106,19 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
+          <t>آیا کنتاکت رلهٔ مشترک شارژر باز است؟ /</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_IsTechnicalFaultLocked</t>
+          <t>func__Charger_IsSuspended</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -7037,19 +7133,19 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
+          <t>خواندن پرچم تعلیق ذخیرهٔ NVM.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_LatchFinalFault</t>
+          <t>func__Charger_IsTechnicalFaultLocked</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -7059,24 +7155,24 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آیا قفل خروجی سناریوی 7 برقرار است؟ /</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_Limit</t>
+          <t>func__Charger_IsThermalRestActive</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
@@ -7086,24 +7182,24 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
+          <t>کانال داده‌شده در استراحت حرارتی است؟</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ManualDriveChannel</t>
+          <t>func__Charger_LatchFinalFault</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -7118,19 +7214,19 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_MaxDutyPermille</t>
+          <t>func__Charger_Limit</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -7145,19 +7241,19 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>مقدار زندهٔ یک حد شارژر، با نمایهٔ جدول.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_NotifyEspLinkActivity</t>
+          <t>func__Charger_ManualDriveChannel</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -7167,24 +7263,24 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
+          <t>درایو یک کانال در مود تست دستی: duty فرمان‌شده (مقدار فیکس ذخیره‌شده، پارامتر 16/18) مستقیم اعمال می‌شود - بدون رمپ، بدون حلقهٔ تنظیم، بدون گیت باتری. کف سخت‌افزاری می‌ماند: قطع ESP کانال → صفر، قطع سخت 15٫0V (CHG_MAX_VALID_BATTERY_MV) → صفر تا افت ولتاژ، و ApplyDuty به کمینهٔ سقف کامپایل و سقف زمان اجرا گیره می‌زند. وضعیت MANUAL نشان داده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidCeilingMilli</t>
+          <t>func__Charger_MaxDutyPermille</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -7199,7 +7295,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>514</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -7211,7 +7307,7 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidClampError</t>
+          <t>func__Charger_NotifyEspLinkActivity</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -7221,24 +7317,24 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>غذای ددمنِ لینک مود دستی: هر فریم معتبر از ESP مهر را تازه می‌کند؛ 3 ثانیه سکوت = خروج از مود دستی و صفرشدن هر دو duty. /</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidInvalidate</t>
+          <t>func__Charger_PidCeilingMilli</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -7253,7 +7349,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>974</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7265,7 +7361,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PidStep</t>
+          <t>func__Charger_PidClampError</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -7280,19 +7376,19 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>989</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_PwmChannel</t>
+          <t>func__Charger_PidInvalidate</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
@@ -7307,7 +7403,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -7319,7 +7415,7 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RegulateChannel</t>
+          <t>func__Charger_PidStep</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -7334,19 +7430,19 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک قدم PID دوحلقه‌ای برای یک کانال و بازگرداندن دیوتی خواسته‌شده بر حسب پرمیل. هر پاس کنترل صدا زده می‌شود ولی ریاضی فقط هر CHG_PID_PERIOD_MS جلو می‌رود؛ بین آن‌ها همان دیوتی قبلی تکرار می‌شود تا کارهای جانبی ApplyDuty بماند.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ResetChannelToOff</t>
+          <t>func__Charger_PwmChannel</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -7361,7 +7457,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -7373,7 +7469,7 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_RetryDuty</t>
+          <t>func__Charger_RegulateChannel</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -7388,7 +7484,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -7400,7 +7496,7 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SafeIdle</t>
+          <t>func__Charger_ResetChannelToOff</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
@@ -7415,7 +7511,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>640</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -7427,7 +7523,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_ServiceRetry</t>
+          <t>func__Charger_RetryDuty</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -7442,7 +7538,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>744</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -7454,7 +7550,7 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetAlarmParam</t>
+          <t>func__Charger_SafeIdle</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
@@ -7464,24 +7560,24 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>379</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetChannelEspEnable</t>
+          <t>func__Charger_ServiceRetry</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -7491,24 +7587,24 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Charger/charger.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>775</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDeadParam</t>
+          <t>func__Charger_SetAlarmParam</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -7523,19 +7619,19 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>نوشتن یک پارامتر آلارم شارژر (لینک ESP، شناسه‌های 35..37). جهت ایمنی فقط پایین است: خطای سخت جریان هرگز بالای 950mA و قطع OV هرگز بالای 15000mV نمی‌رود؛ هر دو بالای باند زندهٔ پروفایل فاصله نگه می‌دارند تا تنظیم سالم تریپ نکند.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyCeilingPermille</t>
+          <t>func__Charger_SetChannelEspEnable</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -7550,19 +7646,19 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>گیت فعال‌سازی ESP یک کانال شارژر. false = قطع: PWM قطع و وضعیت روی OFF نگه داشته می‌شود (قفل FINAL_FAULT هرگز با این گیت آزاد نمی‌شود)؛ true = وصل با ری‌استارت نرم BULK از duty 1٪. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت گیت‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedEnable</t>
+          <t>func__Charger_SetDeadParam</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -7577,19 +7673,19 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
+          <t>نوشتن پارامتر سناریوی 6 (125..131 یا 134..135) یا پخش اسلات 203 هنگام بوت؛ مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetDutyFixedPermille</t>
+          <t>func__Charger_SetDutyCeilingPermille</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -7604,19 +7700,19 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
+          <t>سقف duty ی PWM یک کانال در زمان اجرا، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. هر duty اعمالی (رمپ، تنظیم، مود فیکس) داخل ApplyDuty به کمینهٔ سقف کامپایل و این سقف گیره می‌خورد. روی فلش می‌ماند از نسخهٔ 1.14 - ری‌استارت سقف‌ها را نگه می‌دارد (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetLimitParam</t>
+          <t>func__Charger_SetDutyFixedEnable</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -7631,19 +7727,19 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
+          <t>مود duty فیکس یک کانال: تا وقتی فعال است کانال duty فیکس را به‌جای حلقهٔ تنظیم نگه می‌دارد با همان پوشش امنیتی بنچ (توقف سوئیچینگ بالای CHG_ABSORB_MV؛ برش‌های JIT/ورودی/ باتری/ESP فعال). عدد duty با SetDutyFixedPermille تنظیم و موقع اعمال گیره می‌خورد. فقط RAM (دستور 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetManualTestMode</t>
+          <t>func__Charger_SetDutyFixedPermille</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -7658,19 +7754,19 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
+          <t>مقدار duty فیکس یک کانال، گیرهٔ 0..CHG_DUTY_MAX_PERMILLE. فقط وقتی مود فیکس همان کانال روشن است اثر دارد؛ ApplyDuty به‌علاوه سقف زمان اجرا را رعایت می‌کند. روی فلش می‌ماند از نسخهٔ 1.14 (پنل ESP، دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetPidParam</t>
+          <t>func__Charger_SetLimitParam</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -7685,19 +7781,19 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
+          <t>نوشتن یک حد یا گین پشتیبان شارژر (لینک ESP، 93..107). مقدار به پنجرهٔ کامپایل همان ردیف گیره می‌خورد و مقدار اعمال‌شده برگردانده می‌شود، دقیقاً مثل بلوک پروفایل و PID.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetProfileParam</t>
+          <t>func__Charger_SetManualTestMode</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -7712,19 +7808,19 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
+          <t>درخواست روشن/خاموش مود تست دستی (از تسک ESP صدا زده می‌شود؛ تسک شارژر در پاس بعدی درخواست را برمی‌دارد و عملیات ورود/خروج را در زمینهٔ خودش انجام می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_SetSuspended</t>
+          <t>func__Charger_SetPidParam</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -7739,19 +7835,19 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
+          <t>نوشتن یک پارامتر PID دوحلقه‌ای (لینک ESP، 83..92). مقادیر به پنجره‌های کامپایل گیره می‌خورند: فعال‌ساز 0/1، ضرایب تا CHG_PID_GAIN_MAX و شیب‌ها بین CHG_PID_RATE_MIN و CHG_PID_RATE_MAX میلی‌پرمیل بر ثانیه. تغییر ضریب هیچ پرشی در دیوتی نمی‌سازد: انتگرال‌گیر نقطهٔ کار فعلی را نگه می‌دارد و فقط نرخ تغییرش زمان‌بندی دوباره می‌شود. مقدار اعمال‌شده برگردانده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>func__Charger_StopOneChannel</t>
+          <t>func__Charger_SetProfileParam</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -7761,56 +7857,56 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نوشتن یک پارامتر پروفایل شارژ (لینک ESP، شناسه‌های 20..26: 20=ولتاژ ابزورب، 21=آستانهٔ ورود، 22=سقف تجاوز، 23=ولتاژ شناور، 24=ولتاژ بازگشت، 25=جریان حداکثر بالک، 26=جریان تیپر/شناوری). مقدار گیره می‌خورد و همهٔ وابسته‌ها دوباره گیره می‌شوند تا مجموعه سازنده بماند. مقدار «اعمال‌شده» را برمی‌گرداند (SET_PARAM همان را پاس می‌دهد).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ApplyParam</t>
+          <t>func__Charger_SetSuspended</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Charger/charger.h</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
+          <t>ست‌کردن پرچم تعلیق ذخیرهٔ NVM (قرارداد هدر).</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ConsumeLutResetAuthorization</t>
+          <t>func__Charger_StopOneChannel</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Charger/charger.c</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
@@ -7820,7 +7916,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>606</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -7832,66 +7928,66 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Crc16</t>
+          <t>func__Diag_AddChargeSec</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
+          <t>افزودن ثانیه شارژ برای یک کانال.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetParam</t>
+          <t>func__Diag_BuildRecord</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
+          <t>ساخت رکورد با CRC.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_GetU32</t>
+          <t>func__Diag_Crc32</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
@@ -7901,78 +7997,78 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
+          <t>محاسبه CRC32 روی داده.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleFrame</t>
+          <t>func__Diag_GetBoardTime</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>گرفتن ساعت فعلی برد = پایه + آپتایم.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutFrame</t>
+          <t>func__Diag_Init</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>175</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
+          <t>تازه‌ترین رکورد سالم از دو صفحهٔ فلش بار می‌شود: نسخهٔ صفحهٔ ‎A‎ اگر سالم باشد در رکورد فعال پارک می‌شود و صفحهٔ ‎B‎ در بافر ‎Stage‎ داوری می‌شود؛ بین دو خواندن فقط شماره‌های ترتیب به‌صورت اسکالر می‌مانند و هیچ نسخهٔ رکوردی روی استک صدازننده نمی‌نشیند.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HandleLutRead</t>
+          <t>func__Diag_ReadFlash</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
@@ -7982,456 +8078,456 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
+          <t>خواندن رکورد از آدرس فلش.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_AcceptedFrames</t>
+          <t>func__Diag_RecordChargeComplete</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ثبت یک سیکل شارژ کامل.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_CrcErrors</t>
+          <t>func__Diag_RecordFault</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ثبت خطا با نمونه فعلی.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_FeedByte</t>
+          <t>func__Diag_RecordPowerOff</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ثبت شروع قطع برق شهر. /</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_HandleLutFrame</t>
+          <t>func__Diag_RecordPowerOn</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ثبت پایان قطع و وصل برق. /</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_RecordCommitAck</t>
+          <t>func__Diag_RecordValidate</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>اعتبارسنجی رکورد فلش.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_Reset</t>
+          <t>func__Diag_SaveNow</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>520</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نوشتن فلش با شارژرِ معلق و هر دو گیت PWM متوقف انجام می‌شود (اصلاح ممیزی 2026-10-15): پاک‌کردن صفحه روی این قطعهٔ تک‌بانک کل ‎CPU‎ را حدود 20 تا 40 میلی‌ثانیه نگه می‌دارد و ذخیره‌های ‎NVM/CalLut‎ همین حالا هم سوییچینگ داخل آن پنجرهٔ کور را ممنوع کرده‌اند - این ذخیره هم از همان قانون پیروی می‌کند. ‎SaveNow‎ در تسک کنترل اجرا می‌شود، یعنی همان زمینه‌ای که مالک ارزیابی شارژر است، پس ‎StopAll‎ بی‌درنگ اثر می‌کند (بدون نظرسنجی) و آینه‌های duty دست‌نخورده می‌مانند؛ پاس بعدی کنترل، تنظیم را یکپارچه ادامه می‌دهد. رکورد فعال در صفحهٔ قدیمی‌تر فلش ذخیره می‌شود (پینگ‌پنگ). هر دو صفحه یکی‌یکی در بافر ‎Stage‎ داوری می‌شوند و فقط شماره‌های ترتیب به‌صورت اسکالر می‌مانند؛ قبلاً سه رکورد محلی حدود 2KB از استک صدازننده می‌خواستند — بیشتر از کل استک تسک کنترل. فقط از زمینهٔ تیک Diag صدا زده می‌شود، پس بافر کمکی تک‌مالک است.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_TryReset</t>
+          <t>func__Diag_SetBoardTime</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تنظیم ساعت برد از گوشی (یونیکس).</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_HostTest_VersionErrors</t>
+          <t>func__Diag_Tick</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تیک دوره‌ای، افزایش آپتایم و ذخیره دیبانس فلش. هر 1000ms صدا بزن. /</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Init</t>
+          <t>func__Diag_UpdateMinMax</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/Diag/diag.h</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>441</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
+          <t>به‌روزرسانی کمینه بیشینه از نمونه.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmCrc32</t>
+          <t>func__Diag_WriteFlash</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/Diag/diag.c</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
+          <t>نوشتن رکورد در صفحه فلش.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmFlushForReset</t>
+          <t>func__EspLink_ApplyParam</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>201</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
+          <t>یک مقدار پارامتر را از طریق setter ماژول مالکش اعمال می‌کند (همهٔ setter ها گیره می‌زنند) و مقدار اعمال‌شده را برمی‌گرداند. برای id ناشناخته false می‌دهد و فریمی ارسال نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmInit</t>
+          <t>func__EspLink_ConsumeLutResetAuthorization</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmMarkDirty</t>
+          <t>func__EspLink_Crc16</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
+          <t>CRC-16/CCITT-FALSE (poly 0x1021, init 0xFFFF, no reflection, no final xor). Bitwise on purpose: a 256-entry table would cost 512 bytes of flash on a part that does not have it to spare, and these frames are at most ~470 bytes at 10 Hz, so the loop is far cheaper than the table. [‎FA] CRC-16/CCITT-FALSE‎. عمداً بیتی: جدول 256تایی 512 بایت فلش می‌خواهد روی قطعه‌ای که این فضا را ندارد، و این فریم‌ها حداکثر ~470 بایت با نرخ 10 هرتز‌اند، پس حلقه از جدول خیلی ارزان‌تر است.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmParamPersisted</t>
+          <t>func__EspLink_GetParam</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>447</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
+          <t>مقدار زندهٔ یک پارامتر برای فریم‌های گزارش می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordBuild</t>
+          <t>func__EspLink_GetU32</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
+          <t>یک u32 اندیان‌کوچک از بافر payload می‌خواند. ممیزی 2026-10-05: آفست ‎uint8_t‎ بود ولی حلقهٔ ‎LUT_CHUNK‎ با سقف 512 بایتی ‎3 + 8*i‎ را می‌سازد؛ فریمی با بیش از 31 نقطه آفست را می‌پیچاند و بایت اشتباه می‌خواند. امروز دست‌نیافتنی است (پنل سقف 24 نقطه دارد) ولی سخت‌تر شد: پارسر نباید به ادب فرستنده تکیه کند.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmRecordValidate</t>
+          <t>func__EspLink_HandleFrame</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmResumeCharger</t>
+          <t>func__EspLink_HandleLutFrame</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
@@ -8441,24 +8537,24 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
+          <t>پیام‌های ارسال و بازخوانی جدول را رسیدگی می‌کند و از HandleFrame جداست تا مسیر داغ پارامترها کوتاه بماند.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSaveNow</t>
+          <t>func__EspLink_HandleLutRead</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -8468,100 +8564,100 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>به LUT_READ بدون payload با هر دو کانال فعال پاسخ می‌دهد. @‎param  uint16_t__payloadLength [EN] Must be zero / [FA]‎ باید صفر باشد @‎return bool [EN] true when this was a LUT read request / [FA]‎ درست اگر درخواست خواندن جدول بود /</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSeqCompare</t>
+          <t>func__EspLink_HostTest_AcceptedFrames</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmSuspendCharger</t>
+          <t>func__EspLink_HostTest_CrcErrors</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_NvmTick</t>
+          <t>func__EspLink_HostTest_FeedByte</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ParseByte</t>
+          <t>func__EspLink_HostTest_HandleLutFrame</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -8571,24 +8667,24 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Power</t>
+          <t>func__EspLink_HostTest_RecordCommitAck</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -8603,19 +8699,19 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>پایه CH_PD را می‌زند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU16</t>
+          <t>func__EspLink_HostTest_Reset</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -8625,24 +8721,24 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_PutU32</t>
+          <t>func__EspLink_HostTest_TryReset</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -8652,24 +8748,24 @@
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_RecordLutCommitAck</t>
+          <t>func__EspLink_HostTest_VersionErrors</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -8679,12 +8775,12 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -8696,7 +8792,7 @@
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_ResyncFromByte</t>
+          <t>func__EspLink_Init</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -8706,245 +8802,245 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>لینک را بالا می‌آورد: انتخاب backend ی UART (فعال‌کردن وقفهٔ USART1 و مسلح‌کردن دریافت وقفه‌ای)، ریست پارسر و روشن‌کردن ESP (CH_PD high). فقط با فعال‌بودن MODULE_ESP فعال است. /</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_Run</t>
+          <t>func__EspLink_NvmCrc32</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
+          <t>CRC32 بازتابیده (چندجمله‌ای 0xEDB88320، مقدار اولی/پایانی 0xFFFFFFFF) - همان CRC استاندارد، بیتی-به-بیتی بدون جدول. /</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendFrame</t>
+          <t>func__EspLink_NvmFlushForReset</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
+          <t>نگهداری تسک ارتباط (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutAck</t>
+          <t>func__EspLink_NvmInit</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>361</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
+          <t>بارگذاری هنگام بوت (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendLutData</t>
+          <t>func__EspLink_NvmMarkDirty</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>433</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
+          <t>کثیف‌علامت‌کردن پیکربندی ذخیره‌شونده (قرارداد هدر). /</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamReport</t>
+          <t>func__EspLink_NvmParamPersisted</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
+          <t>این شناسه جزو پیکربندی ذخیره‌شونده است؟ /</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendParamsBulk</t>
+          <t>func__EspLink_NvmRecordBuild</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پرکردن یک رکورد از ورودی‌های داده‌شده (لایه‌گذاری قطعی - ابتدا صفر می‌شود تا ورودی یکسان، CRC یکسان بدهد) و زدن شمارهٔ ترتیب. /</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>func__EspLink_SendTelemetry</t>
+          <t>func__EspLink_NvmRecordValidate</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/EspLink/esp_link.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
+          <t>بررسی کامل رکورد: جادو، نسخه، فیلد reserved صفر، تعداد ورودی، persisted بودن و یکتایی شناسهٔ هر ورودی و CRC روی همهٔ بایت‌های قبل از فیلد CRC. رکوردی با هر شناسهٔ گذرا (مودهای تست 15..19 و میوت جلسه‌ای 76) عمداً رد می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Any</t>
+          <t>func__EspLink_NvmResumeCharger</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>اگر هر بیتی روشن باشد true.</t>
+          <t>ادامهٔ شارژر بعد از ذخیرهٔ فلش (بی‌اثر اگر پرچم ست نشده).</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_ClampAlarms</t>
+          <t>func__EspLink_NvmSaveNow</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -8954,51 +9050,51 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>540</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Clear</t>
+          <t>func__EspLink_NvmSeqCompare</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را پاک می‌کند.</t>
+          <t>مقایسهٔ علامت‌دارِ ترتیب نیم‌کلمه: ‎+1 اگر a تازه‌تر، ‎−1 اگر b تازه‌تر، 0 در برابری. تفاضل int16 چرخش u16 در 65535→0 را یکنوا می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_DebounceDone</t>
+          <t>func__EspLink_NvmSuspendCharger</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
@@ -9008,277 +9104,277 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
+          <t>آرام‌کردن شارژر برای ذخیرهٔ فلش (دستور کاربر): پرچم تعلیق ست و بعد حقیقت سخت‌افزار (هر دو compare صفر) نظرسنجی می‌شود. با timeout هم ذخیره انجام می‌شود (پارامترها باید بمانند). بدون شارژر یا پیش از کرنل بلافاصله false (چیزی برای ادامه نیست).</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Evaluate</t>
+          <t>func__EspLink_NvmTick</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.c</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>Firmware/Modules/EspLink/esp_link_nvm.h</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
+          <t>نگهداری تسک ارتباط: شمارش دیبانس بعد از آخرین تغییر و سپس عکس‌فوری همهٔ پارامترهای ذخیره‌شونده و نوشتن رکورد پینگ‌پنگ. تلاش مجدد محدود برای صحت‌سنجی شکست‌خورده هم همینجاست. /</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Get</t>
+          <t>func__EspLink_ParseByte</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>ماسک فعلی را برمی‌گرداند.</t>
+          <t>یک بایت دریافتی را به ماشین حالت پارسر می‌دهد.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_GetAlarmParam</t>
+          <t>func__EspLink_Power</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
+          <t>پایه CH_PD را می‌زند.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Init</t>
+          <t>func__EspLink_PutU16</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
+          <t>یک u16 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_OnSupervisionChange</t>
+          <t>func__EspLink_PutU32</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
+          <t>یک u32 اندیان‌کوچک در مکان cursor می‌نویسد و جلو می‌برد.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Set</t>
+          <t>func__EspLink_RecordLutCommitAck</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را قفل می‌کند (OR).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_SetAlarmParam</t>
+          <t>func__EspLink_ResyncFromByte</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Fault/fault.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Evaluate</t>
+          <t>func__EspLink_Run</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/EspLink/esp_link.h</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>همهٔ بایت‌های دریافتی را مصرف می‌کند (هر فریم فرمان کامل بلافاصله اعمال می‌شود) و بعد یک فریم تله‌متری TLM_LIVE می‌فرستد. یک‌بار در هر دورهٔ تسک ارتباط صدا زده می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetOutputs</t>
+          <t>func__EspLink_SendDiagChunk0</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ارسال یک چانک DIAG_DATA - سازگار با پارسر پنل ساده. /</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetParam</t>
+          <t>func__EspLink_SendDiagData</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -9290,22 +9386,22 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Init</t>
+          <t>func__EspLink_SendDiagErrors</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -9317,12 +9413,12 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamClamp</t>
+          <t>func__EspLink_SendDiagPower</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
@@ -9332,7 +9428,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -9344,12 +9440,12 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamDefault</t>
+          <t>func__EspLink_SendFrame</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
@@ -9359,24 +9455,24 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>payload را در فریم استاندارد می‌پیچد و ارسال می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ReadParam</t>
+          <t>func__EspLink_SendLutAck</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
@@ -9386,24 +9482,24 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پاسخ به یک مرحلهٔ ارسال جدول: هر فریم ACK می‌گیرد تا پنل بتواند بگوید «کجا» شکست، نه فقط «شکست». /</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SeedDefaultsOnce</t>
+          <t>func__EspLink_SendLutData</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
@@ -9413,537 +9509,537 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نقاط فعال یک کانال را به شکل جفت‌مقدار می‌فرستد. فریم با تعداد صفر عمدی است تا پنل بداند برای این کانال override فلش فعال نیست و مقدارهای قدیمی را نگه ندارد. @‎param  uint8_t__channel [EN] Channel 1 or 2 / [FA]‎ کانال 1 یا 2 @‎return [EN] None / [FA]‎ ندارد /</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SetParam</t>
+          <t>func__EspLink_SendParamNak</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>754</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>یک فریم PARAM_NAK: SET_PARAM ای که اعمال نشد. @‎param  uint8_t__paramId [EN] Parameter id (0xFF when unknown) / [FA]‎ شناسه (0xFF اگر نامشخص)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ChannelTripped</t>
+          <t>func__EspLink_SendParamReport</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>772</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
+          <t>یک فریم PARAM_REPORT می‌فرستد (شناسه + مقدار اعمال‌شده).</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ClearChannel</t>
+          <t>func__EspLink_SendParamsBulk</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>855</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Init</t>
+          <t>func__EspLink_SendTelemetry</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/EspLink/esp_link.c</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
+          <t>یک فریم TLM_LIVE از گلوبال‌های زنده می‌سازد و می‌فرستد.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Run</t>
+          <t>func__Fault_Any</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>468</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
+          <t>اگر هر بیتی روشن باشد true.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Init</t>
+          <t>func__Fault_ClampAlarms</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
+          <t>گیره‌های سختِ تک‌پارامتری را دوباره روی مجموعهٔ آلارم زمان‌اجرا اعمال می‌کند. قرارداد ESP/فرم‌ور بازهٔ خام هر فیلد را مالک است؛ آستانهٔ قطع باتری مستقل و در بازهٔ 14000..15000 میلی‌ولت قابل نوشتن است. این مقدار عمداً از absorbOver یا قطع OV مشتق نمی‌شود: آن‌ها کنترل‌های جدا هستند و ممکن است اپراتور سطح قطعی انتخاب کند که مسیر OV زودتر به آن برسد. بنابراین مقدار اعمال‌شده/بازخوانی همان گیرهٔ 14000..15000 فرم‌ور است. بقیهٔ فیلدهای فالت همچنان هیسترزیس واقعی 500 میلی‌ولتِ غیبت/برگشت و پنجرهٔ ورودی 1000 میلی‌ولت را نگه می‌دارند. اجرای تکراری بی‌خطر است. /</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_OnInputIrq</t>
+          <t>func__Fault_Clear</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
+          <t>بیت‌ها را پاک می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Run</t>
+          <t>func__Fault_DebounceDone</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
+          <t>دبانس مشترک: وقتی شرط به‌طور پیوسته به مدت خواسته‌شده برقرار بود true می‌دهد؛ با false‌شدن شرط، تیک شروع را صفر کنید.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyCurrentFilters</t>
+          <t>func__Fault_Evaluate</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>482</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
+          <t>ارزیابی متمرکز قطع باتری؛ فقط همین بیت را ‎Set/Clear‎ می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyVoltageOffsetMv</t>
+          <t>func__Fault_Get</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>456</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
+          <t>ماسک فعلی را برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Battery24CountsToMv</t>
+          <t>func__Fault_GetAlarmParam</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌خواند. آینهٔ دقیق تابع نوشتن است و همان قرارداد شناسه به کلمهٔ ساختار را دارد، پس بازخوانی پنل همیشه همان مقداری را گزارش می‌کند که فرم‌ور واقعاً دارد استفاده می‌کند، از جمله هر چیزی که گیره‌های وابستگی عوض کرده‌اند.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_BenchTableMa</t>
+          <t>func__Fault_Init</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>جستجوی جدول بر حسب شمارش؛ فراخوان‌کننده برون‌یابی بالای جدول (تفاضل BSPfull از آخرین لنگر، با یک رُند) را می‌دهد.</t>
+          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CountsToMv</t>
+          <t>func__Fault_OnSupervisionChange</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMa</t>
+          <t>func__Fault_Set</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>410</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>بیت‌ها را قفل می‌کند (OR).</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMaLocked</t>
+          <t>func__Fault_SetAlarmParam</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>240</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 1 به mA باتری 1. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMa</t>
+          <t>func__Imbalance_Evaluate</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMaLocked</t>
+          <t>func__Imbalance_GetOutputs</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToShuntUv</t>
+          <t>func__Imbalance_GetParam</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
+          <t>func__Imbalance_Init</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید هیچ تبدیل دوم دیگری اعمال کند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMedian</t>
+          <t>func__Imbalance_ParamClamp</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
@@ -9953,24 +10049,24 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMovingAverage</t>
+          <t>func__Imbalance_ParamDefault</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
@@ -9980,289 +10076,289 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterAverageWindow</t>
+          <t>func__Imbalance_ReadParam</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterMedianSize</t>
+          <t>func__Imbalance_SeedDefaultsOnce</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetSnapshot</t>
+          <t>func__Imbalance_SetParam</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetVoltageOffsetMv</t>
+          <t>func__Jitter_ChannelTripped</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
+          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Init</t>
+          <t>func__Jitter_ClearChannel</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
+          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Median5</t>
+          <t>func__Jitter_Init</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_MedianFilterVoltageSample</t>
+          <t>func__Jitter_Run</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
+          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ResetCurrentFilters</t>
+          <t>func__McuPowerPath_Init</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
+          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Run</t>
+          <t>func__McuPowerPath_OnInputIrq</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
+          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterAverageWindow</t>
+          <t>func__McuPowerPath_Run</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
+          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterMedianSize</t>
+          <t>func__Measurement_ApplyCurrentFilters</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
@@ -10272,24 +10368,24 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
+          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetVoltageOffsetMv</t>
+          <t>func__Measurement_ApplyVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -10299,24 +10395,24 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
+          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V12CountsToMv</t>
+          <t>func__Measurement_Battery24CountsToMv</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
@@ -10331,19 +10427,19 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V24CountsToMv</t>
+          <t>func__Measurement_BenchTableMa</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -10353,110 +10449,110 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>674</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>جستجوی جدول بنچ. جدول و افزایش بالای آخرین نقطه بر حسب دهم mA هستند. درون‌یابی دقیق است (بدون گرد میانی) و خروجی فقط یک بار به بالا به mA صحیح گرد می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Init</t>
+          <t>func__Measurement_CeilDivU32</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
+          <t>سقف ‎n / d (d &gt; 0)‎. جدول در CalLut به CAL_LUT_BATTERY_TENTHS_MAX محدود است، پس همهٔ صورت‌ها در 32 بیت جا می‌شوند. /</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Run</t>
+          <t>func__Measurement_CountsToMv</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>568</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
+          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_DelayMilliseconds</t>
+          <t>func__Measurement_Current1CountsToMa</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>759</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
+          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Fatal</t>
+          <t>func__Measurement_Current1CountsToMaLocked</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
@@ -10466,348 +10562,348 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_MillisecondsToTicks</t>
+          <t>func__Measurement_Current2CountsToMa</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>809</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
+          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Start</t>
+          <t>func__Measurement_Current2CountsToMaLocked</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_app.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>775</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
+          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_TicksToMilliseconds</t>
+          <t>func__Measurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>841</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
+          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>func__TaskComm</t>
+          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_comm.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>817</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>تسک ‎UART/ESP‎.</t>
+          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید هیچ تبدیل دوم دیگری اعمال کند.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>func__TaskControl</t>
+          <t>func__Measurement_CurrentMedian</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_control.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>تسک Changeover و شارژر.</t>
+          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>func__TaskMeasurement</t>
+          <t>func__Measurement_CurrentMovingAverage</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_measurement.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>تسک نمونه‌برداری ADC.</t>
+          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>func__TaskProtection</t>
+          <t>func__Measurement_GetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>تسک حفاظت.</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>func__TaskUi</t>
+          <t>func__Measurement_GetFilterMedianSize</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_ui.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>تسک LED و بازر. در این مرحله فعال است.</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_AlarmParamIndex</t>
+          <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BatteryVoltageToPercent</t>
+          <t>func__Measurement_GetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BeepDutyPercent</t>
+          <t>func__Measurement_Init</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>509</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
+          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BoardTest_Start</t>
+          <t>func__Measurement_Median5</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Gated</t>
+          <t>func__Measurement_MedianFilterVoltageSample</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
@@ -10817,294 +10913,294 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
+          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Tick</t>
+          <t>func__Measurement_ResetCurrentFilters</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>379</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
+          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ChargeVoltageToPercent</t>
+          <t>func__Measurement_Run</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
+          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampAlarms</t>
+          <t>func__Measurement_SetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
+          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampPeriod</t>
+          <t>func__Measurement_SetFilterMedianSize</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
+          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampWindow</t>
+          <t>func__Measurement_SetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_GetAlarmParam</t>
+          <t>func__Measurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
+          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Init</t>
+          <t>func__Measurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
+          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryCriticalBeep</t>
+          <t>func__Protection_Init</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
+          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryRunGreenBlink</t>
+          <t>func__Protection_Run</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
+          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryStablePercent</t>
+          <t>func__Rtos_DelayMilliseconds</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
+          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingFullHysteresis</t>
+          <t>func__Rtos_Fatal</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
@@ -11114,235 +11210,235 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
+          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingStablePercent</t>
+          <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
+          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingYellowBlink</t>
+          <t>func__Rtos_Start</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_app.h</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
+          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatLost_Tick</t>
+          <t>func__Rtos_TicksToMilliseconds</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
+          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatteryRun_Tick</t>
+          <t>func__TaskComm</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_comm.c</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
+          <t>تسک ‎UART/ESP‎.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioCharging_Tick</t>
+          <t>func__TaskControl</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_control.c</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
+          <t>تسک Changeover و شارژر.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioDeadBattery_Tick</t>
+          <t>func__TaskMeasurement</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_measurement.c</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
+          <t>تسک نمونه‌برداری ADC.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioImbalance_Tick</t>
+          <t>func__TaskProtection</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_protection.c</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
+          <t>تسک حفاظت.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOk</t>
+          <t>func__TaskUi</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_ui.c</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
+          <t>تسک LED و بازر. در این مرحله فعال است.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
+          <t>func__Ui_AlarmParamIndex</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
@@ -11357,19 +11453,19 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>435</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
+          <t>func__Ui_BatteryVoltageToPercent</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -11379,24 +11475,24 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
+          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_SetAlarmParam</t>
+          <t>func__Ui_BeepDutyPercent</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
@@ -11406,24 +11502,24 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
+          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Tick</t>
+          <t>func__Ui_BoardTest_Start</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -11438,19 +11534,19 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
+          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
+          <t>func__Ui_Buzzer_Gated</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
@@ -11465,46 +11561,46 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>387</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
+          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryStablePercent</t>
+          <t>func__Ui_Buzzer_Tick</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
+          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingFullHysteresis</t>
+          <t>func__Ui_ChargeVoltageToPercent</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -11514,24 +11610,24 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>650</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
+          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingStablePercent</t>
+          <t>func__Ui_ClampAlarms</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -11546,19 +11642,19 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>187</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
+          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingYellowBlink</t>
+          <t>func__Ui_ClampPeriod</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -11573,19 +11669,19 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
+          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateInputState</t>
+          <t>func__Ui_ClampWindow</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -11600,19 +11696,19 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
+          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_VoltageToPercentMap</t>
+          <t>func__Ui_GetAlarmParam</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -11622,24 +11718,24 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>532</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>func__all_off</t>
+          <t>func__Ui_Init</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -11649,24 +11745,24 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
+          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>func__green</t>
+          <t>func__Ui_ResetBatteryCriticalBeep</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -11681,19 +11777,19 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
+          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>func__red</t>
+          <t>func__Ui_ResetBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
@@ -11708,37 +11804,712 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>881</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
+          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
+          <t>func__Ui_ResetBatteryStablePercent</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ResetChargingFullHysteresis</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ResetChargingStablePercent</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ResetChargingYellowBlink</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>1087</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioBatLost_Tick</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioBatteryRun_Tick</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioCharging_Tick</t>
+        </is>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioDeadBattery_Tick</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioImbalance_Tick</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioInputOk</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_ScenarioThermalRest_Tick</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>چهره استراحت حرارتی: زرد چشمک 1 ثانیه 50٪ حین استراحت 10 دقیقه بعد از 1 ساعت جریان ماکس. سبز ثابت، قرمز خاموش، بوق خاموش.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_SetAlarmParam</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_Tick</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateBatteryStablePercent</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateChargingFullHysteresis</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateChargingStablePercent</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateChargingYellowBlink</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_UpdateInputState</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_VoltageToPercentMap</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>func__all_off</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>func__green</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>func__red</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
           <t>func__yellow</t>
         </is>
       </c>
-      <c r="B300" s="5" t="inlineStr">
+      <c r="B325" s="5" t="inlineStr">
         <is>
           <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
-      <c r="C300" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D300" s="5" t="inlineStr">
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="E300" s="5" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>ال‌ای‌دی زرد را روشن/خاموش می‌کند.</t>
         </is>
@@ -11755,7 +12526,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17052,7 +17823,7 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>600000 (10 min)</t>
+          <t>60000 (1 min)</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -17922,11 +18693,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17979,113 +18750,113 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>PA5</t>
+          <t>PB5</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>ADC_12_BAT</t>
+          <t>BAT_SWITCH</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>PA5</t>
+          <t>PB5</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-low</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>PA5 ADC1_IN5 MCU_ADC_12_BAT</t>
+          <t>PB5 MCU_BAT_SWITCH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>PA3</t>
+          <t>PA4</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ADC_24_BAT</t>
+          <t>BUZZER</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>PA3</t>
+          <t>PA4</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-high</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>PA3 ADC1_IN3 MCU_ADC_24_BAT</t>
+          <t>PA4 MCU_BUZZER, active high</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PA2</t>
+          <t>PA8</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ADC_24_IN</t>
+          <t>ESP_CHPD</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>PA2</t>
+          <t>PA8</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-high</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>PA2 ADC1_IN2 MCU_ADC_24_IN</t>
+          <t>PA8 MCU_ESP_CHPD, active high</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PA1</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ADC_CURRENT1</t>
+          <t>INT_24_IN</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>PA1</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -18100,24 +18871,24 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>PA1 ADC1_IN1 ADC_CURRENT1</t>
+          <t>PB4 MCU_INT_24_IN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>PA7</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ADC_CURRENT2</t>
+          <t>JITTER1</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>PA7</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -18132,56 +18903,56 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>PA7 ADC1_IN7 ADC_CURRENT2</t>
+          <t>PB2 MCU_JITTER1 / JITT1, falling trip</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PB5</t>
+          <t>PB6</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>BAT_SWITCH</t>
+          <t>JITTER2</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>PB5</t>
+          <t>PB6</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>active-low</t>
+          <t>ورودی/—</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>پایین</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PB5 MCU_BAT_SWITCH</t>
+          <t>PB6 MCU_JITTER2 / JITT2, falling trip</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PA4</t>
+          <t>PB10</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>BUZZER</t>
+          <t>LED_G</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>PA4</t>
+          <t>PB10</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -18196,24 +18967,24 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>PA4 MCU_BUZZER, active high</t>
+          <t>PB10 MCU_G_LED, active high</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PA8</t>
+          <t>PB0</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ESP_CHPD</t>
+          <t>LED_R</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>PA8</t>
+          <t>PB0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -18228,391 +18999,103 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>PA8 MCU_ESP_CHPD, active high</t>
+          <t>PB0 MCU_R_LED, active high</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>INT_24_IN</t>
+          <t>LED_Y</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-high</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>PB4 MCU_INT_24_IN</t>
+          <t>PB1 MCU_Y_LED, active high</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>PB11</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>JITTER1</t>
+          <t>PROTECT_BATT</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>PB11</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-low</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>بالا</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>PB2 MCU_JITTER1 / JITT1, falling trip</t>
+          <t>PB11 MCU_LOW_BAT / MCU_PROTECT_BATT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PB6</t>
+          <t>PB7</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>JITTER2</t>
+          <t>RELAY</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>PB6</t>
+          <t>PB7</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ورودی/—</t>
+          <t>active-high</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پایین</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>PB6 MCU_JITTER2 / JITT2, falling trip</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>PB10</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>LED_G</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>PB10</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>active-high</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>PB10 MCU_G_LED, active high</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>PB0</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>LED_R</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>PB0</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>active-high</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>PB0 MCU_R_LED, active high</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>PB1</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>LED_Y</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>PB1</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>active-high</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>PB1 MCU_Y_LED, active high</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>PB11</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>PROTECT_BATT</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>PB11</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>active-low</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>PB11 MCU_LOW_BAT / MCU_PROTECT_BATT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>PA0</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>PWM1</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>PA0</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>ورودی/—</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>PA0 TIM2_CH1 MCU_PWM1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>PA6</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>PWM2</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>PA6</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>ورودی/—</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>PA6 TIM3_CH1 MCU_PWM2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>PB7</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>RELAY</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>PB7</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>active-high</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
           <t>PB7 MCU_PROTECT_CHARGER / Relay_MICRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>PA10</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>PA10</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>ورودی/—</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PA10 MCU_RX &lt;- ESP_TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>PA9</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>PA9</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>ورودی/—</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>PA9 MCU_TX -&gt; ESP_RX</t>
         </is>
       </c>
     </row>
@@ -18627,7 +19110,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -18875,7 +19358,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -18975,7 +19458,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>91 فایل · 298 تابع · 147 شناسه · 20 سیگنال</t>
+          <t>94 فایل · 323 تابع · 147 شناسه · 11 سیگنال</t>
         </is>
       </c>
     </row>

--- a/Documentation/Program_Map.xlsx
+++ b/Documentation/Program_Map.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>390 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
+          <t>395 تابع با نام، فایل، شمارهٔ خط و خلاصهٔ @brief خود تابع</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>173 شناسهٔ سیم با نوع/واحد/پیش‌فرض/بازه و ماندگاری NVM</t>
+          <t>175 شناسهٔ سیم با نوع/واحد/پیش‌فرض/بازه و ماندگاری NVM</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>890</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>777</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>308</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>316</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>مسیر تغذیه MCU با Q1 (PB5) - مستقل از Changeover. هیسترزیس ‎22000/21500‎. /</t>
+          <t>مسیر تغذیه MCU با Q1 (PB5) - مستقل از Changeover. پنجرهٔ ورودی سالم همان جفت مشترک پنل ‎q33/q34 (Fault)‎ است. حاشیه‌های داخلی: داخل [‎q33+QM, q34-QM]‎ برای 5000ms ← قطع؛ بیرون [‎q33+RM, q34-RM]‎ ← وصل؛ بین این دو نوار مرده؛ لبهٔ نزولی PB4 فوراً در ISR وصل می‌کند. /</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>مسیر تغذیهٔ خود MCU با Q1 (PB5، ‎active-low)‎ مستقل از ‎Changeover (PB11): v_in &gt;= 22000mV‎ به‌مدت 5000ms ← قطع؛ ‎v_in &lt; 21500mV‎ ← وصل؛ 21500..21999 نوار مرده؛ لبهٔ نزولی PB4 بلافاصله در ISR وصل می‌کند. فقط مالک PB5 است؛ آستانه‌ها فقط برای v_in هستند و آستانه‌های Changeover اینجا استفاده نمی‌شوند. /</t>
+          <t>مسیر تغذیهٔ خود MCU با Q1 (PB5، ‎active-low)‎ مستقل از Changeover. تصمیم ولتاژی همان مجوز مشترک اشمیت ورودی فالت است (پنجرهٔ ‎q33/q34‎ + حاشیه‌های برگشت ‎q169/q170)‎. تا آن مجوز 5000 میلی‌ثانیه درست بماند Q1 قطع می‌شود؛ با افتادن مجوز Q1 وصل می‌شود. لبهٔ نزولی PB4 بلافاصله در ISR وصل می‌کند. فقط مالک PB5 است؛ آستانه‌ها فقط برای v_in هستند و آستانه‌های Changeover اینجا استفاده نمی‌شوند. /</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>954</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>542</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -3460,17 +3460,17 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>712</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>ساخت فایل Documentation/Program_Map.xlsx - کل برنامه روی جدول: هر فایل سورس و نقش آن، هر تابع با @brief خودش، همهٔ 143 شناسهٔ سیم ESP با نوع/واحد/پیش‌فرض/بازه/ماندگاری، نگاشت پایه‌های MCU با قطبیت و سطح امن، نقشهٔ فلش داخلی، و دروازه‌هایی که همهٔ این‌ها را چک می‌کنند.  چرا: در این پروژه یک شکل ایراد بارها تکرار شده - یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. جدولی که «با ابزار» ساخته شود نمی‌تواند کهنه شود: همه‌چیز پایین در زمان ساخت از هدرهای فرم‌ور خوانده می‌شود، پس کتاب یک «نما» از کد است، نه کپی دوم آن. """  import pathlib import re import sys  from openpyxl import Workbook from openpyxl.styles import Alignment, Border, Font, PatternFill, Side from openpyxl.utils import get_column_letter  ROOT = pathlib.Path(__file__).resolve().parents[1] OUT = ROOT / "Documentation" / "Program_Map.xlsx"  FONT = "Vazirmatn" C_TITLE = "1F3864" C_HEAD = "1F4E79" C_BAND = "D9E2F3" PALETTE = { "ok": "C6EFCE",      # تأییدشده / جاری "warn": "FFE699",    # کهنه / نیازمند توجه "bad": "FFC7CE",     # ایراد "info": "DDEBF7",    # اطلاعاتی "idle": "EDEDED",    # خاموش / غیرفعال "act": "FCE4D6",     # فعال } thin = Side(style="thin", color="9DB7E8") BORDER = Border(left=thin, right=thin, top=thin, bottom=thin)   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def sheet(wb, name, title, headers, rows, widths): """[EN] One RTL sheet in the house style. / [FA] یک برگهٔ راست‌به‌چپ با سبک پروژه.""" ws = wb.create_sheet(name) ws.sheet_view.rightToLeft = True ws.freeze_panes = "A3"  ncol = len(headers) ws.merge_cells(start_row=1, start_column=1, end_row=1, end_column=ncol) tc = ws.cell(row=1, column=1, value=title) tc.font = Font(name=FONT, size=14, bold=True, color="FFFFFF") tc.fill = PatternFill("solid", fgColor=C_TITLE) tc.alignment = Alignment(horizontal="center", vertical="center") ws.row_dimensions[1].height = 30  for c, h in enumerate(headers, start=1): cell = ws.cell(row=2, column=c, value=h) cell.font = Font(name=FONT, size=11, bold=True, color="FFFFFF") cell.fill = PatternFill("solid", fgColor=C_HEAD) cell.alignment = Alignment(horizontal="center", vertical="center", wrap_text=True) cell.border = BORDER ws.row_dimensions[2].height = 28  for r, row in enumerate(rows, start=3): tone = row[-1] values = row[:-1] fill = PatternFill("solid", fgColor=PALETTE.get(tone, "FFFFFF")) if tone else None for c, v in enumerate(values, start=1): cell = ws.cell(row=r, column=c, value=v) cell.font = Font(name=FONT, size=10) cell.alignment = Alignment(horizontal="right", vertical="top", wrap_text=True) cell.border = BORDER if fill is not None: cell.fill = fill elif r % 2 == 1: cell.fill = PatternFill("solid", fgColor=C_BAND)  for c, w in enumerate(widths, start=1): ws.column_dimensions[get_column_letter(c)].width = w ws.sheet_properties.tabColor = C_HEAD return ws   # --------------------------------------------------------------- parsing  def doc_block_brief(text, at): """[EN] Brief of the doc block that sits directly above line `at` (0-based). Returns (en, fa) or ('', ''). [FA] خلاصهٔ بلوک مستندِ بالای خط داده‌شده.""" lines = text.split("\n") end = None block = None for i in range(at - 1, max(-1, at - 60), -1): t = lines[i].strip() if t.startswith("</t>
+          <t>ساخت فایل Documentation/Program_Map.xlsx - کل برنامه روی جدول: هر فایل سورس و نقش آن، هر تابع با @brief خودش، همهٔ 171 شناسهٔ سیم ESP با نوع/واحد/پیش‌فرض/بازه/ماندگاری، نگاشت پایه‌های MCU با قطبیت و سطح امن، نقشهٔ فلش داخلی، و دروازه‌هایی که همهٔ این‌ها را چک می‌کنند.  چرا: در این پروژه یک شکل ایراد بارها تکرار شده - یک عدد که دستی در چند فایل نوشته شده و کپی‌ها از هم جدا افتاده‌اند. جدولی که «با ابزار» ساخته شود نمی‌تواند کهنه شود: همه‌چیز پایین در زمان ساخت از هدرهای فرم‌ور خوانده می‌شود، پس کتاب یک «نما» از کد است، نه کپی دوم آن. """  import pathlib import re import sys  from openpyxl import Workbook from openpyxl.styles import Alignment, Border, Font, PatternFill, Side from openpyxl.utils import get_column_letter  ROOT = pathlib.Path(__file__).resolve().parents[1] OUT = ROOT / "Documentation" / "Program_Map.xlsx"  FONT = "Vazirmatn" C_TITLE = "1F3864" C_HEAD = "1F4E79" C_BAND = "D9E2F3" PALETTE = { "ok": "C6EFCE",      # تأییدشده / جاری "warn": "FFE699",    # کهنه / نیازمند توجه "bad": "FFC7CE",     # ایراد "info": "DDEBF7",    # اطلاعاتی "idle": "EDEDED",    # خاموش / غیرفعال "act": "FCE4D6",     # فعال } thin = Side(style="thin", color="9DB7E8") BORDER = Border(left=thin, right=thin, top=thin, bottom=thin)   def read(rel): return (ROOT / rel).read_text(encoding="utf-8", errors="ignore")   def sheet(wb, name, title, headers, rows, widths): """[EN] One RTL sheet in the house style. / [FA] یک برگهٔ راست‌به‌چپ با سبک پروژه.""" ws = wb.create_sheet(name) ws.sheet_view.rightToLeft = True ws.freeze_panes = "A3"  ncol = len(headers) ws.merge_cells(start_row=1, start_column=1, end_row=1, end_column=ncol) tc = ws.cell(row=1, column=1, value=title) tc.font = Font(name=FONT, size=14, bold=True, color="FFFFFF") tc.fill = PatternFill("solid", fgColor=C_TITLE) tc.alignment = Alignment(horizontal="center", vertical="center") ws.row_dimensions[1].height = 30  for c, h in enumerate(headers, start=1): cell = ws.cell(row=2, column=c, value=h) cell.font = Font(name=FONT, size=11, bold=True, color="FFFFFF") cell.fill = PatternFill("solid", fgColor=C_HEAD) cell.alignment = Alignment(horizontal="center", vertical="center", wrap_text=True) cell.border = BORDER ws.row_dimensions[2].height = 28  for r, row in enumerate(rows, start=3): tone = row[-1] values = row[:-1] fill = PatternFill("solid", fgColor=PALETTE.get(tone, "FFFFFF")) if tone else None for c, v in enumerate(values, start=1): cell = ws.cell(row=r, column=c, value=v) cell.font = Font(name=FONT, size=10) cell.alignment = Alignment(horizontal="right", vertical="top", wrap_text=True) cell.border = BORDER if fill is not None: cell.fill = fill elif r % 2 == 1: cell.fill = PatternFill("solid", fgColor=C_BAND)  for c, w in enumerate(widths, start=1): ws.column_dimensions[get_column_letter(c)].width = w ws.sheet_properties.tabColor = C_HEAD return ws   # --------------------------------------------------------------- parsing  def doc_block_brief(text, at): """[EN] Brief of the doc block that sits directly above line `at` (0-based). Returns (en, fa) or ('', ''). [FA] خلاصهٔ بلوک مستندِ بالای خط داده‌شده.""" lines = text.split("\n") end = None block = None for i in range(at - 1, max(-1, at - 60), -1): t = lines[i].strip() if t.startswith("</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>345</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E392"/>
+  <dimension ref="A1:E397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>632</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>626</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>959</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>576</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>714</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>779</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>551</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>764</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>735</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>847</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>880</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>949</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>685</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>678</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>375</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>449</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>548</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>562</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>510</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>721</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>976</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>733</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>721</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -11505,7 +11505,7 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Init</t>
+          <t>func__Fault_GetInputHystParam</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -11520,19 +11520,19 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>467</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
+          <t>خواندن یک حاشیهٔ زندهٔ مشترک اشمیت ورودی (169/170). /</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_IsBatteryAbsent</t>
+          <t>func__Fault_GetInputPermission</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
@@ -11547,19 +11547,19 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>499</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>نشانهٔ زندهٔ جدایی باتری را که آخرین Evaluate معتبر ساخته برمی‌گرداند؛ عمداً از بیت قفل‌شدهٔ خطای مشترک جداست.</t>
+          <t>آخرین تصمیم مشترک ورودی منتشرشده را زیر یک قفل کپی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_IsChannelBatteryAbsent</t>
+          <t>func__Fault_GetInputWindow</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -11574,19 +11574,19 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>392</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>نشانهٔ زندهٔ جدایی باتری را به‌تفکیک کانال (0 = نیم بالا، 1 = نیم پایین) از آخرین Evaluate معتبر برمی‌گرداند.</t>
+          <t>پنجرهٔ مشترک ورودی سالم (33/34) را زیر یک قفل زمان‌بند کپی می‌کند تا مصرف‌کننده هنگام نوشتن پنل، کف جدید را با سقف قدیمی نبیند.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_OnSupervisionChange</t>
+          <t>func__Fault_Init</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
@@ -11601,19 +11601,19 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
+          <t>همه بیت‌های خطا را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_Set</t>
+          <t>func__Fault_IsBatteryAbsent</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -11628,19 +11628,19 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>974</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>بیت‌ها را قفل می‌کند (OR).</t>
+          <t>نشانهٔ زندهٔ جدایی باتری را که آخرین Evaluate معتبر ساخته برمی‌گرداند؛ عمداً از بیت قفل‌شدهٔ خطای مشترک جداست.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>func__Fault_SetAlarmParam</t>
+          <t>func__Fault_IsChannelBatteryAbsent</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
@@ -11655,208 +11655,208 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>990</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
+          <t>نشانهٔ زندهٔ جدایی باتری را به‌تفکیک کانال (0 = نیم بالا، 1 = نیم پایین) از آخرین Evaluate معتبر برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>func__FlashLock_ApplyOnce</t>
+          <t>func__Fault_OnSupervisionChange</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/FlashLock/flash_lock.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/FlashLock/flash_lock.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>605</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>اعمال قفل یک‌بارمصرف اگر قطعه هنوز باز است. یک‌بار از App_Init و پیش از شروع زمان‌بند صدا زده می‌شود تا پاک‌کردن option byte به تسک در حال اجرا آسیب نزند. در موفقیت، میکرو داخل فراخوانی BSP ریست می‌شود و تابع برنمی‌گردد؛ مقدار برگشتی برای تست هاست و مسیر شکست است. ALREADY_PROTECTED وقتی کاری لازم نبود، JUST_LOCKED وقتی ریست درخواست شد، FAILED وقتی نوشتن شکست خورد (برد باز و بدون قفل بالا می‌آید) /</t>
+          <t>قلاب نظارتی که شارژر پس از جابه‌جاکردن یکی از آستانه‌های خودش صدا می‌زند. فیلدهای فالت پنجرهٔ سختِ خودشان را دارند؛ این قلاب پس از بازپخش پروفایل یا آلارم همان پنجره‌ها را دوباره اعمال می‌کند، بدون وابسته‌کردن q27 به absorbOver یا قطع OV. نام‌دار بودن قلاب به‌جای صادرکردن گیره باعث می‌شود شارژر هرگز به درونیات این ماژول دست نزند. /</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>func__FlashLock_IsProtected</t>
+          <t>func__Fault_Set</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/FlashLock/flash_lock.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/FlashLock/flash_lock.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>پرسش فقط‌خواندنی وضعیت فعلی قفل. @‎return bool [EN] true when RDP level 1 is active / [FA] true‎ وقتی RDP سطح 1 فعال است /</t>
+          <t>بیت‌ها را قفل می‌کند (OR).</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ClearBatteryState</t>
+          <t>func__Fault_SetAlarmParam</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>شمارنده‌ها و قفلِ متعلق به باتری را پس از تأیید تعویض پاک می‌کند. @‎return bool [EN] true iff an NVM-backed value changed‎ / اگر مقدار ماندگار عوض شد true /</t>
+          <t>یک آستانهٔ آلارم زمان‌اجرا را با شناسهٔ فشردهٔ پارامتر می‌نویسد و مقداری را که واقعاً اثر کرده برمی‌گرداند. شناسه‌ها یک‌به‌یک روی کلمه‌های ‎fault_alarm_t‎ می‌افتند (همان چیدمانی که اثبات‌های ایستای بالا میخکوبش می‌کنند)، پس نوشتن یک ذخیرهٔ نمایه‌ای ساده است نه سوییچی که می‌تواند ناهمگام شود. کل به‌روزرسانی زیر قفل زمان‌بند اجرا می‌شود: تسک ارتباط می‌نویسد و تسک کنترل خطاها را می‌سنجد، و بدون قفل، سنجنده می‌توانست وسط گیره‌زدن پیشی بگیرد و یک پاس مجموعهٔ آستانهٔ پاره بخواند. بعد از ذخیره، گیره‌های وابستگی اجرا می‌شوند؛ به همین دلیل مقدار اعمال‌شده می‌تواند به حق با مقدار درخواستی فرق کند و همان مقدار گیره‌خورده به فراخوان گفته می‌شود، نه یک دروغ.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Evaluate</t>
+          <t>func__Fault_SetInputHystParam</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/Fault/fault.h</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>424</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نوشتن یکی از حاشیه‌های مشترک اشمیت ورودی (169/170). درخواست خام به 0..FAULT_INPUT_HYST_MAX_MV گیره می‌شود، سپس کل مجموعه دوباره گیره می‌خورد تا فاصلهٔ زندهٔ ‎q33/q34‎ نیز هر حاشیه را به ‎span/4‎ محدود کند. مقدار اعمال‌شده بازخوانی می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetOutputs</t>
+          <t>func__Fault_UpdateInputPermission</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/Fault/fault.c</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تنها مجوز مشترک اشمیت را از تازه‌ترین snapshot اندازه‌گیری تازه می‌کند. بیرون ‎[q33,q34]‎ مجوز فوراً می‌افتد؛ از حالت رهاشده فقط داخل ‎[q33+H_low, q34-H_high]‎ دوباره مسلح می‌شود. snapshot نامعتبر ‎valid=false / permitted=false‎ منتشر می‌کند تا همهٔ مصرف‌کننده‌ها بسته بمانند. /</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_GetParam</t>
+          <t>func__FlashLock_ApplyOnce</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/FlashLock/flash_lock.c</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/FlashLock/flash_lock.h</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>اعمال قفل یک‌بارمصرف اگر قطعه هنوز باز است. یک‌بار از App_Init و پیش از شروع زمان‌بند صدا زده می‌شود تا پاک‌کردن option byte به تسک در حال اجرا آسیب نزند. در موفقیت، میکرو داخل فراخوانی BSP ریست می‌شود و تابع برنمی‌گردد؛ مقدار برگشتی برای تست هاست و مسیر شکست است. ALREADY_PROTECTED وقتی کاری لازم نبود، JUST_LOCKED وقتی ریست درخواست شد، FAILED وقتی نوشتن شکست خورد (برد باز و بدون قفل بالا می‌آید) /</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_Init</t>
+          <t>func__FlashLock_IsProtected</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.c</t>
+          <t>Firmware/Modules/FlashLock/flash_lock.c</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>Firmware/Modules/FlashLock/flash_lock.h</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>پرسش فقط‌خواندنی وضعیت فعلی قفل. @‎return bool [EN] true when RDP level 1 is active / [FA] true‎ وقتی RDP سطح 1 فعال است /</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamClamp</t>
+          <t>func__Imbalance_ClearBatteryState</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -11871,19 +11871,19 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>شمارنده‌ها و قفلِ متعلق به باتری را پس از تأیید تعویض پاک می‌کند. @‎return bool [EN] true iff an NVM-backed value changed‎ / اگر مقدار ماندگار عوض شد true /</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ParamDefault</t>
+          <t>func__Imbalance_Evaluate</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>375</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
@@ -11910,7 +11910,7 @@
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_PublishOutputs</t>
+          <t>func__Imbalance_GetOutputs</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -11920,24 +11920,24 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>خروجی زنده و ماندگارِ عدم‌توازن را برای مصرف‌کننده منتشر می‌کند. @‎param  uint32_t__imbalanceMv [EN] Absolute half-voltage difference in mV‎ / اختلاف دو نیم، میلی‌ولت @‎param  bool__sameState [EN] true when both charger channels match / true‎ اگر دو کانال هم‌حالت‌اند @‎param  bool__beepDue [EN] One-pass beep pulse‎ / پالس بوق همین پاس</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ReadParam</t>
+          <t>func__Imbalance_GetParam</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>978</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
@@ -11964,7 +11964,7 @@
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_ResetCycleState</t>
+          <t>func__Imbalance_Init</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
@@ -11974,24 +11974,24 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>229</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>همهٔ وضعیت‌های موقت چرخه/رویداد را پس از نبود باتری پاک می‌کند؛ پیش از پذیرش FLOAT، شروع یک شارژ تازه لازم است.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SeedDefaultsOnce</t>
+          <t>func__Imbalance_ParamClamp</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
@@ -12018,7 +12018,7 @@
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>func__Imbalance_SetParam</t>
+          <t>func__Imbalance_ParamDefault</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Imbalance/imbalance.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
@@ -12045,331 +12045,331 @@
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ChannelTripped</t>
+          <t>func__Imbalance_PublishOutputs</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
+          <t>خروجی زنده و ماندگارِ عدم‌توازن را برای مصرف‌کننده منتشر می‌کند. @‎param  uint32_t__imbalanceMv [EN] Absolute half-voltage difference in mV‎ / اختلاف دو نیم، میلی‌ولت @‎param  bool__sameState [EN] true when both charger channels match / true‎ اگر دو کانال هم‌حالت‌اند @‎param  bool__beepDue [EN] One-pass beep pulse‎ / پالس بوق همین پاس</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_ClearChannel</t>
+          <t>func__Imbalance_ReadParam</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Init</t>
+          <t>func__Imbalance_ResetCycleState</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
+          <t>همهٔ وضعیت‌های موقت چرخه/رویداد را پس از نبود باتری پاک می‌کند؛ پیش از پذیرش FLOAT، شروع یک شارژ تازه لازم است.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>func__Jitter_Run</t>
+          <t>func__Imbalance_SeedDefaultsOnce</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Jitter/jitter.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Init</t>
+          <t>func__Imbalance_SetParam</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Imbalance/imbalance.c</t>
         </is>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Imbalance/imbalance.h</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>867</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_OnInputIrq</t>
+          <t>func__Jitter_ChannelTripped</t>
         </is>
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
+          <t>اگر کانال 1 یا 2 تریپ قفل کرده باشد true.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>func__McuPowerPath_Run</t>
+          <t>func__Jitter_ClearChannel</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>سنجش دوره‌ای (~10ms) با هیسترزیس: ‎v_in &gt;= 22000‎ برای 5s ← قطع؛ 21500..21999 ← لغو تایمر و حفظ Q1؛ &lt; 21500 ← وصل. ولتاژ باتری بی‌اثر است و لبهٔ PB4 همچنان در ISR مدیریت می‌شود. /</t>
+          <t>تریپ قفل‌شدهٔ یک کانال را پاک می‌کند تا retry بعدی لبهٔ جدید comparator را ببیند، نه رویداد قبلی را.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyCurrentFilters</t>
+          <t>func__Jitter_Init</t>
         </is>
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
+          <t>پرچم تریپ و EXTI را پاک می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ApplyVoltageOffsetMv</t>
+          <t>func__Jitter_Run</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/Jitter/jitter.c</t>
         </is>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Jitter/jitter.h</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
+          <t>اگر رویداد EXTI آمده باشد تریپ را قفل می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Battery24CountsToMv</t>
+          <t>func__McuPowerPath_Init</t>
         </is>
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
+          <t>مسیر خودتغذیهٔ MCU را به حالت امن بوت می‌برد: کلید باتری روی «وصل» رانده می‌شود و تایمر احراز صفر می‌شود. «وصل» تنها حالت درست روشن‌شدن است، چون برد باید بتواند پیش از آنکه کسی حاضر و سالم‌بودن ورودی DC را ثابت کند از باتری کار کند. این تابع یک‌بار پیش از شروع تسک‌های محصول صدا زده می‌شود و عمداً هرگز به PB11 دست نمی‌زند که فقط مال Changeover است. /</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_BenchTableMa</t>
+          <t>func__McuPowerPath_OnInputIrq</t>
         </is>
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>جستجوی جدول بنچ. جدول و افزایش بالای آخرین نقطه بر حسب دهم mA هستند. درون‌یابی دقیق است (بدون گرد میانی) و خروجی فقط یک بار به بالا به mA صحیح گرد می‌شود. /</t>
+          <t>مدیریت‌کنندهٔ لبه‌های حضور ورودی روی PB4 در بافت وقفه. وقتی PB4 می‌گوید ورودی DC رفته، مسیر باتری فوراً وصل و هر تایمر قطعِ در انتظار لغو می‌شود؛ منتظرماندن تا پاس دوره‌ای بعدی می‌تواند MCU را بی‌برق کند. بدنه به یک نوشتن GPIO و دو پرچم volatile محدود است: بدون فراخوانی RTOS، بدون ADC، بدون میوتکس و بدون تأخیر، پس از داخل وقفه امن است. لبهٔ صعودی اینجا قطع نمی‌کند؛ آن تصمیم به احراز 5 ثانیه و باند هیسترزیس نیاز دارد که فقط مال Run دوره‌ای است. /</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CeilDivU32</t>
+          <t>func__McuPowerPath_Run</t>
         </is>
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.c</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.c</t>
         </is>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/McuPowerPath/mcu_power_path.h</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>سقف ‎n / d (d &gt; 0)‎. جدول در CalLut به CAL_LUT_BATTERY_TENTHS_MAX محدود است، پس همهٔ صورت‌ها در 32 بیت جا می‌شوند. /</t>
+          <t>سنجش دوره‌ای (~10ms) روی مجوز مشترک اشمیت ورودی فالت. تا وقتی مجوز مشترک درست است تایمر 5 ثانیه می‌چرخد و سپس Q1 باز می‌شود؛ وقتی نادرست است Q1 دوباره بسته می‌شود. snapshot نامعتبر Q1 را حفظ و تایمر را لغو می‌کند. لبهٔ نزولی PB4 همچنان فوری در ISR مدیریت می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CountsToMv</t>
+          <t>func__Measurement_ApplyCurrentFilters</t>
         </is>
       </c>
       <c r="B311" s="5" t="inlineStr">
@@ -12379,24 +12379,24 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>364</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>زنجیرهٔ فیلتر جریان فعال کانال را با ترتیب ثابت اجرا می‌کند: اول مدین (حذف پرش تکی) بعد میانگین متحرک (صاف‌کردن) - دقیقاً طبق دو کلید کامپایل. هر دو خاموش = عبور بدون تغییر.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMa</t>
+          <t>func__Measurement_ApplyVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B312" s="5" t="inlineStr">
@@ -12406,24 +12406,24 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>جمع علامتدارِ اشباع‌شوندهٔ یک آفست کالیبراسیون زمان اجرا به ولتاژ بر حسب mV؛ نتیجه هرگز زیر 0mV نمی‌رود. آفست در setter خودش به ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV گیره می‌شود، پس جمع در int32_t سرریز نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current1CountsToMaLocked</t>
+          <t>func__Measurement_Battery24CountsToMv</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
@@ -12433,24 +12433,24 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>کانال باتری‌پک 24 ولت را با ضریب مقسم «کاربر» تبدیل می‌کند (2026-09-25): مسیر سنس پک تا پایه ‎6.8k/69.2k‎ تضعیف دارد، نه ‎6.8k/76k‎ مثل نت ورودی.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMa</t>
+          <t>func__Measurement_BenchTableMa</t>
         </is>
       </c>
       <c r="B314" s="5" t="inlineStr">
@@ -12460,24 +12460,24 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
+          <t>جستجوی جدول بنچ. جدول و افزایش بالای آخرین نقطه بر حسب دهم mA هستند. درون‌یابی دقیق است (بدون گرد میانی) و خروجی فقط یک بار به بالا به mA صحیح گرد می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Current2CountsToMaLocked</t>
+          <t>func__Measurement_CeilDivU32</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
@@ -12492,19 +12492,19 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
+          <t>سقف ‎n / d (d &gt; 0)‎. جدول در CalLut به CAL_LUT_BATTERY_TENTHS_MAX محدود است، پس همهٔ صورت‌ها در 32 بیت جا می‌شوند. /</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentCountsToShuntUv</t>
+          <t>func__Measurement_CountsToMv</t>
         </is>
       </c>
       <c r="B316" s="5" t="inlineStr">
@@ -12519,19 +12519,19 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
+          <t>شمارش استاندارد ADC را از طریق پورت کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
+          <t>func__Measurement_Current1CountsToMa</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
@@ -12546,19 +12546,19 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>819</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید هیچ تبدیل دوم دیگری اعمال کند.</t>
+          <t>شمارش کانال 1 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMedian</t>
+          <t>func__Measurement_Current1CountsToMaLocked</t>
         </is>
       </c>
       <c r="B318" s="5" t="inlineStr">
@@ -12573,19 +12573,19 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>783</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_CurrentMovingAverage</t>
+          <t>func__Measurement_Current2CountsToMa</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
@@ -12595,24 +12595,24 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
+          <t>شمارش کانال 2 به mA باتری، زیر قفل کرنل؛ commit جدول CalLut نمی‌تواند وسط جستجو جدول را عوض کند. /</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterAverageWindow</t>
+          <t>func__Measurement_Current2CountsToMaLocked</t>
         </is>
       </c>
       <c r="B320" s="5" t="inlineStr">
@@ -12622,24 +12622,24 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>849</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
+          <t>شمارش کانال 2 به mA باتری 2. با جدول: جدول بنچ روی محور شمارش. بدون جدول: خط کامل گین/آفست BSPfull.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetFilterMedianSize</t>
+          <t>func__Measurement_CurrentCountsToShuntUv</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
@@ -12654,19 +12654,19 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>931</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
+          <t>شمارش خام جریان به ولتاژ شانتِ فقط-سخت‌افزاری بر حسب uV از طریق BSP (بدون آفست صفر، بدون اصلاح بنچ) - دیاگ زندهٔ بررسی زنجیرهٔ جریان (دستور کاربر 2026-09-22).</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetSnapshot</t>
+          <t>func__Measurement_CurrentIsBatteryCalibrated</t>
         </is>
       </c>
       <c r="B322" s="5" t="inlineStr">
@@ -12681,19 +12681,19 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>907</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
+          <t>اعلام می‌کند که خروجی جریان کانال همین حالا سمت باتری است (جدول جریان پنل، یا خط گین و آفست وقتی جدولی نیست). وقتی true است، کد بعدی شارژر نباید هیچ تبدیل دوم دیگری اعمال کند.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_GetVoltageOffsetMv</t>
+          <t>func__Measurement_CurrentMedian</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
@@ -12703,24 +12703,24 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
+          <t>نمونهٔ خام جدید را در تاریخچهٔ مدین کانال جابه‌جا و مقدار میانی را برمی‌گرداند. اندازهٔ پنجره = اندازهٔ مدین زمان اجرا (هر 1..15، زوج هم)؛ پرش تک‌نمونه‌ای بدون تأخیر اضافه دور داده می‌شود. مرتب‌سازی درجی روی کپی محلی، تاریخچهٔ زنده دست نمی‌خورد (الگوی مدین-5 ولتاژ).</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Init</t>
+          <t>func__Measurement_CurrentMovingAverage</t>
         </is>
       </c>
       <c r="B324" s="5" t="inlineStr">
@@ -12730,24 +12730,24 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
+          <t>نمونهٔ خام جدید را در پنجرهٔ میانگین متحرک کانال می‌نویسد و میانگین را برمی‌گرداند. تا پرشدن پنجره، میانگین فقط روی نمونه‌های جمع‌شده اجرا می‌شود (بدون کشیده‌شدن به صفرِ خانه‌های خالی).</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Median5</t>
+          <t>func__Measurement_GetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
@@ -12757,24 +12757,24 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ میانگین متحرک.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_MedianFilterVoltageSample</t>
+          <t>func__Measurement_GetFilterMedianSize</t>
         </is>
       </c>
       <c r="B326" s="5" t="inlineStr">
@@ -12784,24 +12784,24 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
+          <t>اندازهٔ زندهٔ پنجرهٔ مدین فیلتر جریان.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_ResetCurrentFilters</t>
+          <t>func__Measurement_GetSnapshot</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -12811,24 +12811,24 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
+          <t>آخرین نمونه را کپی می‌کند. اگر اشاره‌گر NULL یا داده نامعتبر باشد false برمی‌گرداند.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_Run</t>
+          <t>func__Measurement_GetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B328" s="5" t="inlineStr">
@@ -12843,19 +12843,19 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا را می‌خواند.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterAverageWindow</t>
+          <t>func__Measurement_Init</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
@@ -12870,19 +12870,19 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
+          <t>آخرین نمونه را صفر می‌کند (‎valid = false)‎. /</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetFilterMedianSize</t>
+          <t>func__Measurement_Median5</t>
         </is>
       </c>
       <c r="B330" s="5" t="inlineStr">
@@ -12892,24 +12892,24 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SetVoltageOffsetMv</t>
+          <t>func__Measurement_MedianFilterVoltageSample</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
@@ -12919,24 +12919,24 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>453</t>
         </is>
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
+          <t>نمونهٔ خام کانال ADC باتری را در تاریخچهٔ مدین-5 جابه‌جا و شمارش فیلترشده را برمی‌گرداند. شارژر و آشکارساز قطع باتری از ولتاژهای مشتق‌شده از همین تبدیل‌ها استفاده می‌کنند تا ترکیدگی کوتاه «باتری رفت» را جعل نکند.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_SuperviseAdc</t>
+          <t>func__Measurement_ResetCurrentFilters</t>
         </is>
       </c>
       <c r="B332" s="5" t="inlineStr">
@@ -12946,24 +12946,24 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Measurement/measurement.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>نظارت بر زنده‌بودن ‎ADC1+DMA‎ در هر پاس اندازه‌گیری: تلاش بی‌صدای بازیابی درجا به مدت 60 ثانیه، حداکثر یک ریست برد، تلاش 60 ثانیهٔ دیگر پس از ریست، و ثبت خطای ‎FAULT_ADC‎ فقط در صورت عدم بهبود.</t>
+          <t>تاریخچهٔ هر دو فیلتر جریان را صفر و شیب هر دو میانگین را از نو شروع می‌کند؛ از Init و هر بار که تسک اندازه‌گیری تغییر پیکربندی زمان اجرا را ببیند صدا زده می‌شود تا تغییر پنجره هرگز خانه‌های قدیمی را داخل میانگین نیامیزد. فقط تسک اندازه‌گیری اجازهٔ صدا زدن دارد. /</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V12CountsToMv</t>
+          <t>func__Measurement_Run</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
@@ -12978,19 +12978,19 @@
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>975</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>یک فریم خام پایدار را از BSP می‌گیرد، همهٔ کانال‌های ADC را تبدیل می‌کند و یک snapshot مشترک منسجم منتشر می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
         <is>
-          <t>func__Measurement_V24CountsToMv</t>
+          <t>func__Measurement_SetFilterAverageWindow</t>
         </is>
       </c>
       <c r="B334" s="5" t="inlineStr">
@@ -13005,478 +13005,478 @@
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
+          <t>اندازهٔ پنجرهٔ میانگین متحرک در زمان اجرا، گیره در 1..MEASUREMENT_CURRENT_AVERAGE_WINDOW (اندازهٔ حلقهٔ کامپایل سقف قطعی است). تسک اندازه‌گیری پس از تغییر در فریم بعدی وضعیت فیلتر را ریست می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Init</t>
+          <t>func__Measurement_SetFilterMedianSize</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
+          <t>اندازهٔ پنجرهٔ مدین فیلتر جریان در زمان اجرا (یک پارامتر اندازه؛ 1 = عبور مستقیم). هر اندازهٔ 1..MAX مجاز است (زوج هم، بدون گرد به فرد؛ 1..2 عبور مستقیم‌اند). کلید کامپایل ظرفیت را تعیین می‌کند: 0 یعنی درخواست به 1 گیره می‌شود. روی فلش می‌ماند (شناسهٔ NVM 7).</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>func__Protection_Run</t>
+          <t>func__Measurement_SetVoltageOffsetMv</t>
         </is>
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Protection/protection.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
+          <t>یک آفست کالیبراسیون ولتاژ زمان اجرا، گیره در ±MEASUREMENT_VOLTAGE_OFFSET_LIMIT_MV. اندیس 0 = ورودی 24V، 1 = باتری 24V، 2 = باتری 12V (نود میانی). پیش‌فرض 0 همان رفتار فعلی؛ روی فلش می‌ماند (NVM نسخهٔ 1.14).</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_DelayMilliseconds</t>
+          <t>func__Measurement_SuperviseAdc</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
+          <t>نظارت بر زنده‌بودن ‎ADC1+DMA‎ در هر پاس اندازه‌گیری: تلاش بی‌صدای بازیابی درجا به مدت 60 ثانیه، حداکثر یک ریست برد، تلاش 60 ثانیهٔ دیگر پس از ریست، و ثبت خطای ‎FAULT_ADC‎ فقط در صورت عدم بهبود.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Fatal</t>
+          <t>func__Measurement_V12CountsToMv</t>
         </is>
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
+          <t>کانال استاندارد 12 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_MillisecondsToTicks</t>
+          <t>func__Measurement_V24CountsToMv</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Measurement/measurement.c</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Measurement/measurement.h</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>637</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
+          <t>کانال استاندارد 24 ولت را از طریق کالیبراسیون برد تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_Start</t>
+          <t>func__Protection_Init</t>
         </is>
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_app.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_app.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
-          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
+          <t>حالتی برای مقداردهی اولیه نیست - ناظر بهطراحی بی‌حالت است؛ نقطهٔ ورود برای یکدستماندن چرخهٔ عمر ماژولها نگه داشته شده است. /</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>func__Rtos_TicksToMilliseconds</t>
+          <t>func__Protection_Run</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/rtos_time.c</t>
+          <t>Firmware/Modules/Protection/protection.c</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_time.h</t>
+          <t>Firmware/Modules/Protection/protection.h</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
+          <t>تا نبودِ نمونهٔ معتبر ‎FAULT_ADC‎ را نگه می‌دارد و با اولین نمونهٔ معتبر پاکش می‌کند؛ عمداً هرگز قفل نمی‌کند (قفل زمان بوت تا پایان همین دورهٔ برق می‌ماند و حالتهای امن را بر همیشه پارک می‌کرد).</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
         <is>
-          <t>func__TaskComm</t>
+          <t>func__Rtos_DelayMilliseconds</t>
         </is>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_comm.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>133</t>
         </is>
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>تسک ‎UART/ESP‎.</t>
+          <t>تسک فعلی ‎CMSIS-RTOS2‎ را به مدت میلی‌ثانیه متوقف می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="5" t="inlineStr">
         <is>
-          <t>func__TaskControl</t>
+          <t>func__Rtos_Fatal</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_control.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>تسک Changeover و شارژر.</t>
+          <t>اگر کرنل یا یکی از تسک‌های لازم شروع نشد، در وضعیت مشخص متوقف می‌شود. /</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
         <is>
-          <t>func__TaskMeasurement</t>
+          <t>func__Rtos_MillisecondsToTicks</t>
         </is>
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_measurement.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E344" s="5" t="inlineStr">
         <is>
-          <t>تسک نمونه‌برداری ADC.</t>
+          <t>میلی‌ثانیه را به تعداد تیک فعال ‎CMSIS-RTOS2‎ تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>func__TaskProtection</t>
+          <t>func__Rtos_Start</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_protection.c</t>
+          <t>Firmware/Rtos/Src/rtos_app.c</t>
         </is>
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Rtos/Inc/rtos_app.h</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>تسک حفاظت.</t>
+          <t>تسک‌های ‎CMSIS-RTOS2‎ با حافظهٔ ثابت را می‌سازد و کرنل را شروع می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="5" t="inlineStr">
         <is>
-          <t>func__TaskUi</t>
+          <t>func__Rtos_TicksToMilliseconds</t>
         </is>
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Src/task_ui.c</t>
+          <t>Firmware/Rtos/Src/rtos_time.c</t>
         </is>
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
+          <t>Firmware/Rtos/Inc/rtos_time.h</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E346" s="5" t="inlineStr">
         <is>
-          <t>تسک LED و بازر. در این مرحله فعال است.</t>
+          <t>تعداد تیک سپری‌شده ‎CMSIS-RTOS2‎ را به میلی‌ثانیه تبدیل می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_AlarmParamIndex</t>
+          <t>func__TaskComm</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_comm.c</t>
         </is>
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>تسک ‎UART/ESP‎.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BatteryVoltageToPercent</t>
+          <t>func__TaskControl</t>
         </is>
       </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_control.c</t>
         </is>
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E348" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
+          <t>تسک Changeover و شارژر.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BeepDutyPercent</t>
+          <t>func__TaskMeasurement</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_measurement.c</t>
         </is>
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
+          <t>تسک نمونه‌برداری ADC.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BoardTest_DelayWithWatchdog</t>
+          <t>func__TaskProtection</t>
         </is>
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_protection.c</t>
         </is>
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>تابع کمکی تأخیر تست برد که اسلات واچ‌داگ UI را بین گام‌ها تازه می‌کند بدون آن‌که زمان روشن‌ماندن LED یا بوق تغییر کند.</t>
+          <t>تسک حفاظت.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_BoardTest_Start</t>
+          <t>func__TaskUi</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Rtos/Src/task_ui.c</t>
         </is>
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Rtos/Inc/rtos_tasks.h</t>
         </is>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود و بین گام‌ها واچ‌داگ UI تازه می‌گردد. /</t>
+          <t>تسک LED و بازر. در این مرحله فعال است.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Gated</t>
+          <t>func__Ui_AlarmParamIndex</t>
         </is>
       </c>
       <c r="B352" s="5" t="inlineStr">
@@ -13491,73 +13491,73 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>398</t>
         </is>
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_SetDutyWindowMs</t>
+          <t>func__Ui_BatteryVoltageToPercent</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>693</t>
         </is>
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>ثبت پنجرهٔ دقیق دیوتی بر حسب میلی‌ثانیه برای تیک بعدی بازر. @‎param  uint32_t__windowMs [EN] Exact duty window in ms (0 = use percent)‎ / پنجره بر حسب ms /</t>
+          <t>تبدیل ولتاژ به درصد سمت «دشارژ» از نگاشت 74/75 (از نسخهٔ 1.49 این جفت فقط مال دشارژ است).</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Buzzer_Tick</t>
+          <t>func__Ui_BeepDutyPercent</t>
         </is>
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
+          <t>درصد دیوتی یک الگوی بوق از پنجرهٔ زنده‌اش (سقف‌گرد مثل ماکروهای قدیم) - غیرخطی 3 گام. /</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ChargeVoltageToPercent</t>
+          <t>func__Ui_BoardTest_DelayWithWatchdog</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
@@ -13567,24 +13567,24 @@
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
+          <t>تابع کمکی تأخیر تست برد که اسلات واچ‌داگ UI را بین گام‌ها تازه می‌کند بدون آن‌که زمان روشن‌ماندن LED یا بوق تغییر کند.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampAlarms</t>
+          <t>func__Ui_BoardTest_Start</t>
         </is>
       </c>
       <c r="B356" s="5" t="inlineStr">
@@ -13594,24 +13594,24 @@
       </c>
       <c r="C356" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
+          <t>تست یک‌باره سیم‌کشی: قرمز، زرد، سبز و بوق کوتاه قبلی. بوق با API دوره‌ای جدید و دوره امن اجرا و سپس صریحاً خاموش می‌شود و بین گام‌ها واچ‌داگ UI تازه می‌گردد. /</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampPeriod</t>
+          <t>func__Ui_Buzzer_Gated</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
@@ -13626,73 +13626,73 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
+          <t>سرویس بوق با میوت جلسه‌ای: تا وقتی 76 ست است هر الگوی سناریو با خاموش صریح جایگزین می‌شود (بوق تست برد مستقیم است و همچنان می‌زند). /</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ClampWindow</t>
+          <t>func__Ui_Buzzer_SetDutyWindowMs</t>
         </is>
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E358" s="5" t="inlineStr">
         <is>
-          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
+          <t>ثبت پنجرهٔ دقیق دیوتی بر حسب میلی‌ثانیه برای تیک بعدی بازر. @‎param  uint32_t__windowMs [EN] Exact duty window in ms (0 = use percent)‎ / پنجره بر حسب ms /</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_GetAlarmParam</t>
+          <t>func__Ui_Buzzer_Tick</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.c</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.c</t>
         </is>
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>Firmware/Modules/Ui/ui_buzzer.h</t>
         </is>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
+          <t>یک الگوی دوره‌ای بوق را بدون قفل کردن تسک اجرا می‌کند. پنجره دیوتی ‎period*duty/100‎ است؛ بوق‌ها و گپ‌ها این پنجره را پر می‌کنند و زمان باقی‌مانده تا دوره بعدی خاموش است. زمان پیشنهادی مراجعه بعدی، صفر برای خاموشی معتبر، یا منفی یک برای ورودی نامعتبر. /</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_GetScenarioAlarm</t>
+          <t>func__Ui_ChargeVoltageToPercent</t>
         </is>
       </c>
       <c r="B360" s="5" t="inlineStr">
@@ -13707,19 +13707,19 @@
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E360" s="5" t="inlineStr">
         <is>
-          <t>خواندن کلید هشدار یک سناریو (158..164). @‎param  uint8_t__paramId [EN] 158..164‎ / شناسه @‎param  uint32_t *uint32_t__value [EN] Value out‎ / مقدار</t>
+          <t>تبدیل ولتاژ به درصد سمت «شارژ» از نگاشت 119/120 (دستور کاربر: تکان‌دادن حدهای دشارژ نباید سمت شارژ را تکان بدهد).</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Init</t>
+          <t>func__Ui_ClampAlarms</t>
         </is>
       </c>
       <c r="B361" s="5" t="inlineStr">
@@ -13729,24 +13729,24 @@
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
+          <t>گیرهٔ کل مجموعهٔ UI، یک پاس، ترتیب وابستگی در هر گروه. /</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryCriticalBeep</t>
+          <t>func__Ui_ClampPeriod</t>
         </is>
       </c>
       <c r="B362" s="5" t="inlineStr">
@@ -13761,19 +13761,19 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
+          <t>گیرهٔ دورهٔ بوق: صفر یعنی خاموش، وگرنه 1000..600000. /</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryRunGreenBlink</t>
+          <t>func__Ui_ClampWindow</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
@@ -13788,19 +13788,19 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>153</t>
         </is>
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
+          <t>گیرهٔ یک مقدار در پنجرهٔ بیرونی. /</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetBatteryStablePercent</t>
+          <t>func__Ui_GetAlarmParam</t>
         </is>
       </c>
       <c r="B364" s="5" t="inlineStr">
@@ -13810,24 +13810,24 @@
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E364" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
+          <t>خواندن یک عدد زندهٔ UI (38..82).</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingFullHysteresis</t>
+          <t>func__Ui_GetScenarioAlarm</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
@@ -13837,24 +13837,24 @@
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
+          <t>خواندن کلید هشدار یک سناریو (158..164). @‎param  uint8_t__paramId [EN] 158..164‎ / شناسه @‎param  uint32_t *uint32_t__value [EN] Value out‎ / مقدار</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingStablePercent</t>
+          <t>func__Ui_Init</t>
         </is>
       </c>
       <c r="B366" s="5" t="inlineStr">
@@ -13864,24 +13864,24 @@
       </c>
       <c r="C366" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="E366" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
+          <t>همه خروجی‌های UI خاموش (حالت امن). /</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ResetChargingYellowBlink</t>
+          <t>func__Ui_ResetBatteryCriticalBeep</t>
         </is>
       </c>
       <c r="B367" s="5" t="inlineStr">
@@ -13896,19 +13896,19 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>931</t>
         </is>
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
+          <t>وضعیت بوق بحرانی تک‌باره BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioAlarmOn</t>
+          <t>func__Ui_ResetBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B368" s="5" t="inlineStr">
@@ -13918,24 +13918,24 @@
       </c>
       <c r="C368" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E368" s="5" t="inlineStr">
         <is>
-          <t>آیا چهرهٔ چراغ و بوق این سناریو اجازهٔ نمایش دارد؟ شماره‌ها 1..8 هستند؛ هر عدد بیرون 1..7 «بله» است تا فراخوان با شمارهٔ اشتباه نتواند چهره‌ای را بی‌صدا کند. @‎param  uint8_t__scenario [EN] 1..7‎ / شمارهٔ سناریو</t>
+          <t>زمان‌بندی چشمک غیرمسدودکننده سبز BatteryRun را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatLost_Tick</t>
+          <t>func__Ui_ResetBatteryStablePercent</t>
         </is>
       </c>
       <c r="B369" s="5" t="inlineStr">
@@ -13945,24 +13945,24 @@
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>959</t>
         </is>
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
+          <t>وضعیت هیسترزیس درصد پایدار را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioBatteryRun_Tick</t>
+          <t>func__Ui_ResetChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B370" s="5" t="inlineStr">
@@ -13972,24 +13972,24 @@
       </c>
       <c r="C370" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="E370" s="5" t="inlineStr">
         <is>
-          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
+          <t>وضعیت هیسترزیس فول شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioCharging_Tick</t>
+          <t>func__Ui_ResetChargingStablePercent</t>
         </is>
       </c>
       <c r="B371" s="5" t="inlineStr">
@@ -13999,24 +13999,24 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
+          <t>درصد پایدار شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioDeadBattery_Tick</t>
+          <t>func__Ui_ResetChargingYellowBlink</t>
         </is>
       </c>
       <c r="B372" s="5" t="inlineStr">
@@ -14026,24 +14026,24 @@
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E372" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
+          <t>فاز چشمک زرد شارژ را بازنشانی می‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioImbalance_Tick</t>
+          <t>func__Ui_ScenarioAlarmOn</t>
         </is>
       </c>
       <c r="B373" s="5" t="inlineStr">
@@ -14058,19 +14058,19 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>603</t>
         </is>
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
+          <t>آیا چهرهٔ چراغ و بوق این سناریو اجازهٔ نمایش دارد؟ شماره‌ها 1..8 هستند؛ هر عدد بیرون 1..7 «بله» است تا فراخوان با شمارهٔ اشتباه نتواند چهره‌ای را بی‌صدا کند. @‎param  uint8_t__scenario [EN] 1..7‎ / شمارهٔ سناریو</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOk</t>
+          <t>func__Ui_ScenarioBatLost_Tick</t>
         </is>
       </c>
       <c r="B374" s="5" t="inlineStr">
@@ -14085,19 +14085,19 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="E374" s="5" t="inlineStr">
         <is>
-          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
+          <t>اعلان قطع باتری: قرمز چشمک‌تند (پیش‌فرض 50٪ در دوره یک‌ثانیه؛ 44/45)، سبز ثابت (ورودی حاضر است) و الگوی بوق دوره‌ای (پیش‌فرض سه بیپ کوتاه + مکث؛ 46..49). فاز از تیک مطلق گرفته می‌شود تا وضعیتی لازم نباشد؛ خود پرچم فقط در Fault مدیریت می‌شود. تا وقتی فعال است هر پاس صدا زده شود. /</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
+          <t>func__Ui_ScenarioBatteryRun_Tick</t>
         </is>
       </c>
       <c r="B375" s="5" t="inlineStr">
@@ -14107,24 +14107,24 @@
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
+          <t>سناریو دشارژ: سبز بر اساس نگاشت درصد 74/75 چشمک می‌زند؛ بوق بر اساس چهار بازه درصدی (50..53) اجرا می‌شود. زیر باند بحرانی (53) همهٔ LEDها خاموش و الگوی بحرانی (56/57/58/65) فقط یک‌بار به‌اندازهٔ طول یک‌باره (61) پخش می‌شود، بعد سکوت تا برگشت باتری.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
+          <t>func__Ui_ScenarioCharging_Tick</t>
         </is>
       </c>
       <c r="B376" s="5" t="inlineStr">
@@ -14134,24 +14134,24 @@
       </c>
       <c r="C376" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="E376" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
+          <t>سناریو شارژ: سبز ثابت، زرد مانده تا فول غیرخطی. نسخهٔ 1٫20 (دستور کاربر 2026-09-28): مانده روی کف UI_CHARGING_YELLOW_MIN_REMAINING_PERCENT می‌نشیند و درصد 100 دیگر زرد را خاموش نمی‌کند - این سناریو فقط با پمپِ کانال شارژر اجرا می‌شود پس تا قطع شارژر حداقل یک چشمکِ مرئی در هر دوره می‌ماند.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioThermalRest_Tick</t>
+          <t>func__Ui_ScenarioDeadBattery_Tick</t>
         </is>
       </c>
       <c r="B377" s="5" t="inlineStr">
@@ -14166,19 +14166,19 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>چهره استراحت حرارتی: زرد چشمک 1 ثانیه 50٪ حین استراحت 10 دقیقه بعد از 1 ساعت جریان ماکس. سبز ثابت، قرمز خاموش، بوق خاموش.</t>
+          <t>چهرهٔ سناریوی 6: قرمزِ ثابت (برخلاف چشمکِ قفل عدم‌توازن تا دو چهره روی یک لامپ قرمز قابل تفکیک بمانند) و شکل بوق مستقل خودش. /</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_ScenarioWeakBattery_Tick</t>
+          <t>func__Ui_ScenarioImbalance_Tick</t>
         </is>
       </c>
       <c r="B378" s="5" t="inlineStr">
@@ -14193,19 +14193,19 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="E378" s="5" t="inlineStr">
         <is>
-          <t>چهرهٔ سناریوی 8 (دستور کاربر 2026-10-23: «باتری ضعیفی که زود خالی می‌شود و با برداشتن بار برمی‌گردد باید قابل تشخیص باشد - چراغ قرمز چشمک‌زن و بوق»). قرمز چشمک‌زن با دوره/دیوتی خودش (شناسه‌های 151/152، پیش‌فرض 500 میلی‌ثانیه و 50٪) تا با قفل عدم‌توازن (1000 میلی‌ثانیه) و باتری خرابِ قرمز ثابت اشتباه نشود، به‌همراه شکل بوق مستقل خودش (153..156: سه بوق کوتاه هر 3 ثانیه). سبز و زرد خاموش. خود حکم مال Changeover است و این تابع فقط آن را می‌کشد. /</t>
+          <t>سناریوی قفل عدم‌توازن: قرمز «چشمک‌زن» (به دستور کاربر در 2026-10-05؛ قبلاً ثابت بود) با دوره و duty 123/124 (پیش‌فرض 1000ms و 50٪) — متمایز از چشمک قطع باتری که سبز را روشن نگه می‌دارد — سبز/زرد خاموش، و بوق کوتاه دوره‌ای با الگوی بوق زمان‌مطلق: یک بوق به طول 116 تکرارشونده هر 115 (پیش‌فرض هر ساعت) از لحظهٔ قفل. /</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_SetAlarmParam</t>
+          <t>func__Ui_ScenarioInputOk</t>
         </is>
       </c>
       <c r="B379" s="5" t="inlineStr">
@@ -14220,19 +14220,19 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
+          <t>سناریو ورودی وصل: سبز ثابت، قرمز و زرد خاموش و بوق خاموش. /</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_SetScenarioAlarm</t>
+          <t>func__Ui_ScenarioInputOverVoltage_Tick</t>
         </is>
       </c>
       <c r="B380" s="5" t="inlineStr">
@@ -14242,24 +14242,24 @@
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="E380" s="5" t="inlineStr">
         <is>
-          <t>نوشتن کلید هشدار یک سناریو (158..164 = سناریو 1..7). مقدار به 0/1 گیره می‌خورد و مقدار اعمال‌شده برمی‌گردد. @‎param  uint8_t__paramId [EN] 158..164‎ / شناسه @‎param  uint32_t__value [EN] 0 = face off, 1 = face on‎ / صفر خاموش، یک روشن</t>
+          <t>نمایش اضافه‌ولتاژ ورودی: سبز ثابت، زرد خاموش، قرمز چشمک (38/39) و الگوی بوق دوره‌ای (40..43). پیش‌فرض: قرمز 50٪ و یک بوق یک‌ثانیه‌ای هر 10 ثانیه. این تیک غیرمسدودکننده است. /</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_Tick</t>
+          <t>func__Ui_ScenarioTechnicalFault_Tick</t>
         </is>
       </c>
       <c r="B381" s="5" t="inlineStr">
@@ -14269,24 +14269,24 @@
       </c>
       <c r="C381" s="5" t="inlineStr">
         <is>
-          <t>Firmware/Modules/Ui/ui_led.h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
+          <t>چهرهٔ خطای فنی برد: هر سه LED از یک فاز مطلق استفاده می‌کنند و دقیقاً هم‌زمان روشن/خاموش می‌شوند؛ بوق فقط اعداد زندهٔ خودش را می‌خواند و هرگز از ‎q132..q135‎ استفاده نمی‌کند. /</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
+          <t>func__Ui_ScenarioThermalRest_Tick</t>
         </is>
       </c>
       <c r="B382" s="5" t="inlineStr">
@@ -14296,24 +14296,24 @@
       </c>
       <c r="C382" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="E382" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
+          <t>چهره استراحت حرارتی: زرد چشمک 1 ثانیه 50٪ حین استراحت 10 دقیقه بعد از 1 ساعت جریان ماکس. سبز ثابت، قرمز خاموش، بوق خاموش.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateBatteryStablePercent</t>
+          <t>func__Ui_ScenarioWeakBattery_Tick</t>
         </is>
       </c>
       <c r="B383" s="5" t="inlineStr">
@@ -14323,24 +14323,24 @@
       </c>
       <c r="C383" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
+          <t>چهرهٔ سناریوی 8 (دستور کاربر 2026-10-23: «باتری ضعیفی که زود خالی می‌شود و با برداشتن بار برمی‌گردد باید قابل تشخیص باشد - چراغ قرمز چشمک‌زن و بوق»). قرمز چشمک‌زن با دوره/دیوتی خودش (شناسه‌های 151/152، پیش‌فرض 500 میلی‌ثانیه و 50٪) تا با قفل عدم‌توازن (1000 میلی‌ثانیه) و باتری خرابِ قرمز ثابت اشتباه نشود، به‌همراه شکل بوق مستقل خودش (153..156: سه بوق کوتاه هر 3 ثانیه). سبز و زرد خاموش. خود حکم مال Changeover است و این تابع فقط آن را می‌کشد. /</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingFullHysteresis</t>
+          <t>func__Ui_SetAlarmParam</t>
         </is>
       </c>
       <c r="B384" s="5" t="inlineStr">
@@ -14350,24 +14350,24 @@
       </c>
       <c r="C384" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>440</t>
         </is>
       </c>
       <c r="E384" s="5" t="inlineStr">
         <is>
-          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
+          <t>نوشتن یک عدد UI (38..82): ذخیره، گیرهٔ کل مجموعه، گزارش مقدار اعمال‌شده.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingStablePercent</t>
+          <t>func__Ui_SetScenarioAlarm</t>
         </is>
       </c>
       <c r="B385" s="5" t="inlineStr">
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C385" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>566</t>
         </is>
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
+          <t>نوشتن کلید هشدار یک سناریو (158..164 = سناریو 1..7). مقدار به 0/1 گیره می‌خورد و مقدار اعمال‌شده برمی‌گردد. @‎param  uint8_t__paramId [EN] 158..164‎ / شناسه @‎param  uint32_t__value [EN] 0 = face off, 1 = face on‎ / صفر خاموش، یک روشن</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateChargingYellowBlink</t>
+          <t>func__Ui_Tick</t>
         </is>
       </c>
       <c r="B386" s="5" t="inlineStr">
@@ -14404,24 +14404,24 @@
       </c>
       <c r="C386" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Firmware/Modules/Ui/ui_led.h</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="E386" s="5" t="inlineStr">
         <is>
-          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
+          <t>تیک اصلی UI - تصمیم سناریو را از snapshot واقعی Measurement می‌گیرد.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_UpdateInputState</t>
+          <t>func__Ui_UpdateBatteryRunGreenBlink</t>
         </is>
       </c>
       <c r="B387" s="5" t="inlineStr">
@@ -14436,19 +14436,19 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>وضعیت اتصال و خطای اضافه‌ولتاژ ورودی را با هیسترزیس به‌روز می‌کند. وصل: ورودی حداقل 21 ولت. قطع: ورودی حداکثر 20 ولت (باند ثابت). خطا: بالاتر از 70 فعال و در 70−71 یا پایین‌تر پاک می‌شود (پیش‌فرض 28/27 ولت).</t>
+          <t>چشمک غیرمسدودکننده سبز BatteryRun و زمان‌بندی فاز آن را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
         <is>
-          <t>func__Ui_VoltageToPercentMap</t>
+          <t>func__Ui_UpdateBatteryStablePercent</t>
         </is>
       </c>
       <c r="B388" s="5" t="inlineStr">
@@ -14463,19 +14463,19 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>974</t>
         </is>
       </c>
       <c r="E388" s="5" t="inlineStr">
         <is>
-          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+          <t>درصد پایدار را از درصد خام با هیسترزیس 2٪ و رفتار خاص 0/1 به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="inlineStr">
         <is>
-          <t>func__all_off</t>
+          <t>func__Ui_UpdateChargingFullHysteresis</t>
         </is>
       </c>
       <c r="B389" s="5" t="inlineStr">
@@ -14490,19 +14490,19 @@
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="E389" s="5" t="inlineStr">
         <is>
-          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
+          <t>هیسترزیس ورود/خروج InputOk را به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="5" t="inlineStr">
         <is>
-          <t>func__green</t>
+          <t>func__Ui_UpdateChargingStablePercent</t>
         </is>
       </c>
       <c r="B390" s="5" t="inlineStr">
@@ -14517,19 +14517,19 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="E390" s="5" t="inlineStr">
         <is>
-          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
+          <t>درصد پایدار شارژ را با هیسترزیس 5٪ به‌روز می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="5" t="inlineStr">
         <is>
-          <t>func__red</t>
+          <t>func__Ui_UpdateChargingYellowBlink</t>
         </is>
       </c>
       <c r="B391" s="5" t="inlineStr">
@@ -14544,37 +14544,172 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
+          <t>چشمک غیرمسدودکننده زرد شارژ را به‌روز می‌کند و فاز را حفظ می‌کند.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="inlineStr">
         <is>
+          <t>func__Ui_UpdateInputState</t>
+        </is>
+      </c>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="inlineStr">
+        <is>
+          <t>وضعیت حضور و اضافه‌ولتاژ ورودی را به‌روز می‌کند. حضور از پنجرهٔ مشترک ورودی سالم ‎q33/q34 (Fault)‎ استفاده می‌کند. آستانهٔ اضافه‌ولتاژ = q34 زنده؛ فقط هیسترزیس q71 تنظیم‌شدنی است.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>func__Ui_VoltageToPercentMap</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="inlineStr">
+        <is>
+          <t>یک نگاشت ولتاژ به درصد برای هر دو جفت - فرمول 4 گام: بازه، فاصله، مقیاس، درصد. قبلاً مستقیم 74/75 را می‌خواند؛ حالا هر نگاشت اعداد خودش را می‌دهد و ریاضی فقط یک‌بار وجود دارد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="inlineStr">
+        <is>
+          <t>func__all_off</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="inlineStr">
+        <is>
+          <t>همه ال‌ای‌دی‌ها را خاموش می‌کند و سرویس بوق را به حالت خاموش امن می‌برد. /</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>func__green</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="inlineStr">
+        <is>
+          <t>ال‌ای‌دی سبز را روشن/خاموش می‌کند - سطح پایین.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t>func__red</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="inlineStr">
+        <is>
+          <t>Firmware/Modules/Ui/ui_led.c</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="inlineStr">
+        <is>
+          <t>ال‌ای‌دی قرمز را روشن/خاموش می‌کند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
           <t>func__yellow</t>
         </is>
       </c>
-      <c r="B392" s="5" t="inlineStr">
+      <c r="B397" s="5" t="inlineStr">
         <is>
           <t>Firmware/Modules/Ui/ui_led.c</t>
         </is>
       </c>
-      <c r="C392" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D392" s="5" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="E392" s="5" t="inlineStr">
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="inlineStr">
         <is>
           <t>ال‌ای‌دی زرد را روشن/خاموش می‌کند.</t>
         </is>
@@ -14595,7 +14730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17554,42 +17689,34 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>UI_OV_THRESH_MV</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>u32</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>24000..32000</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>read-only mirror of shared q34; writes rejected</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>not persisted</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>مشتق (ذخیره نمی‌شود)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>NVM v12</t>
         </is>
@@ -21672,84 +21799,84 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>SLOT (runtime)</t>
-        </is>
-      </c>
-      <c r="C172" s="8" t="inlineStr">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>FAULT_INPUT_HYST_LOW_MV</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
         <is>
           <t>u32</t>
         </is>
       </c>
-      <c r="D172" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>اسلات زمان‌اجرا</t>
-        </is>
-      </c>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>0..3000 and &lt;= (q34-q33)/4</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
       </c>
-      <c r="H172" s="8" t="inlineStr">
+      <c r="H172" s="6" t="inlineStr">
         <is>
           <t>NVM v12</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
-        <is>
-          <t>SLOT (runtime)</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>FAULT_INPUT_HYST_HIGH_MV</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t>u32</t>
         </is>
       </c>
-      <c r="D173" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E173" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>اسلات زمان‌اجرا</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>0..3000 and &lt;= (q34-q33)/4</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
       </c>
-      <c r="H173" s="8" t="inlineStr">
+      <c r="H173" s="6" t="inlineStr">
         <is>
           <t>NVM v12</t>
         </is>
@@ -21758,7 +21885,7 @@
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
@@ -21800,40 +21927,124 @@
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>SLOT (runtime)</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>u32</t>
+        </is>
+      </c>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>اسلات زمان‌اجرا</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>NVM v12</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>SLOT (runtime)</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>u32</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="8" t="inlineStr">
+        <is>
+          <t>اسلات زمان‌اجرا</t>
+        </is>
+      </c>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="H176" s="8" t="inlineStr">
+        <is>
+          <t>NVM v12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>SLOT (runtime)</t>
         </is>
       </c>
-      <c r="C175" s="8" t="inlineStr">
+      <c r="C177" s="8" t="inlineStr">
         <is>
           <t>u32</t>
         </is>
       </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F175" s="8" t="inlineStr">
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
         <is>
           <t>اسلات زمان‌اجرا</t>
         </is>
       </c>
-      <c r="G175" s="8" t="inlineStr">
+      <c r="G177" s="8" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
       </c>
-      <c r="H175" s="8" t="inlineStr">
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>NVM v12</t>
         </is>
@@ -22615,7 +22826,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>102 فایل · 390 تابع · 173 شناسه · 11 سیگنال</t>
+          <t>102 فایل · 395 تابع · 175 شناسه · 11 سیگنال</t>
         </is>
       </c>
     </row>
